--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdowns" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Named Contacts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ProjectStage">'Dropdowns'!$A$7:INDEX('Dropdowns'!$A$7:$A$106,COUNTA('Dropdowns'!$A$7:$A$106))</definedName>
@@ -1993,7 +1994,7 @@
         <v>48213</v>
       </c>
       <c r="X7" s="44" t="n">
-        <v>46843</v>
+        <v>47299</v>
       </c>
       <c r="Y7" s="45" t="n"/>
       <c r="Z7" s="37" t="inlineStr">
@@ -2048,12 +2049,12 @@
       </c>
       <c r="AJ7" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 2030 COD; public filings point to Dec 2031 (construction start Q4 2027). Cost not disclosed. Local opposition (water use). EPC not yet selected. Data-center tie not confirmed.</t>
+          <t>CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="AK7" s="38" t="inlineStr">
         <is>
-          <t>Contact Daniel Birmingham (Invenergy); track WI PSC CPCN filing for EPC selection; bundle with Union Depot CC.</t>
+          <t>Build relationship with Daniel Birmingham (Invenergy); watch PSC 5-CE-162 CPCN for EPC; get on EPC approved-vendor list in 2027.</t>
         </is>
       </c>
       <c r="AL7" s="38" t="inlineStr">
@@ -2115,7 +2116,7 @@
       </c>
       <c r="F8" s="36" t="inlineStr">
         <is>
-          <t>Eliecer Viamontes, President &amp; CEO</t>
+          <t>Keith Pollock, Project Director, OCAPS</t>
         </is>
       </c>
       <c r="G8" s="36" t="inlineStr">
@@ -2170,7 +2171,7 @@
         <v>46309</v>
       </c>
       <c r="X8" s="44" t="n">
-        <v>46387</v>
+        <v>46507</v>
       </c>
       <c r="Y8" s="45" t="n"/>
       <c r="Z8" s="37" t="inlineStr">
@@ -2225,12 +2226,12 @@
       </c>
       <c r="AJ8" s="38" t="inlineStr">
         <is>
-          <t>Plant is now operating; new-build cable window closed. Keep for MRO/aftermarket and relationship with TIC / Sargent &amp; Lundy for next Entergy builds. Yes Energy MW (1,306) differs from Entergy (1,215).</t>
+          <t>In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="AK8" s="38" t="inlineStr">
         <is>
-          <t>Reclassify as aftermarket/MRO; use TIC &amp; S&amp;L relationship for Entergy pipeline (Titanium, Waterford 5/6).</t>
+          <t>Aftermarket/spares with Keith Pollock and Entergy fossil ops supply chain; use TIC/S&amp;L relationship for Entergy program plants.</t>
         </is>
       </c>
       <c r="AL8" s="38" t="inlineStr">
@@ -2282,7 +2283,7 @@
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jim Burke, President &amp; CEO</t>
         </is>
       </c>
       <c r="G9" s="36" t="inlineStr">
@@ -2337,7 +2338,7 @@
         <v>46874</v>
       </c>
       <c r="X9" s="44" t="n">
-        <v>46477</v>
+        <v>46418</v>
       </c>
       <c r="Y9" s="45" t="n"/>
       <c r="Z9" s="37" t="inlineStr">
@@ -2392,12 +2393,12 @@
       </c>
       <c r="AJ9" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 2030; ERCOT/Cleanview show May 2028 COD. Link of ERCOT IDs to Vistra project based on GEM aliases + site/MW match. EPC and OEM not public. Urgent: procurement likely now-2027.</t>
+          <t>CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="AK9" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC via Vistra/TCEQ permit 178462; find Vistra Luminant project/procurement contact; quote both units (880 MW).</t>
+          <t>URGENT: identify EPC via TCEQ 178462 NAPD / Industrial Info; find Luminant project contact; quote both units (880 MW).</t>
         </is>
       </c>
       <c r="AL9" s="38" t="inlineStr">
@@ -2447,9 +2448,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>Rick Anderson, SVP &amp; Senior Production Officer</t>
         </is>
       </c>
       <c r="G10" s="36" t="inlineStr">
@@ -2460,7 +2461,7 @@
       <c r="H10" s="39" t="n"/>
       <c r="I10" s="37" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="J10" s="40" t="n"/>
@@ -2504,7 +2505,7 @@
         <v>46568</v>
       </c>
       <c r="X10" s="44" t="n">
-        <v>46387</v>
+        <v>46371</v>
       </c>
       <c r="Y10" s="45" t="n"/>
       <c r="Z10" s="37" t="inlineStr">
@@ -2559,17 +2560,17 @@
       </c>
       <c r="AJ10" s="38" t="inlineStr">
         <is>
-          <t>Late stage - Unit 8 cable likely bought; Units 9/10 BOP and commissioning needs may still be open. Load growth driven largely by data centers (no named customer). EPC not public.</t>
+          <t>LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="AK10" s="38" t="inlineStr">
         <is>
-          <t>Confirm EPC/electrical contractor at Yates; position for Units 9-10 and Southern Co. future IRP gas units.</t>
+          <t>Relationship/spares play via B&amp;V site procurement; position with Mitsubishi/B&amp;V for next Georgia Power CT/CC builds.</t>
         </is>
       </c>
       <c r="AL10" s="38" t="inlineStr">
         <is>
-          <t>Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. Cost: Not public; PSC staff ~$1B for 3 units. EPC: Not public. OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE).</t>
+          <t>Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. Cost: Not public; PSC staff ~$1B for 3 units. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE).</t>
         </is>
       </c>
       <c r="AM10" s="40" t="n"/>
@@ -2614,9 +2615,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Laura Landreaux, President &amp; CEO</t>
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz, VP, Power Development - New Generation</t>
         </is>
       </c>
       <c r="G11" s="36" t="inlineStr">
@@ -2627,7 +2628,7 @@
       <c r="H11" s="39" t="n"/>
       <c r="I11" s="37" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="J11" s="40" t="n"/>
@@ -2668,7 +2669,7 @@
       </c>
       <c r="V11" s="40" t="n"/>
       <c r="W11" s="44" t="n">
-        <v>46935</v>
+        <v>47118</v>
       </c>
       <c r="X11" s="44" t="n">
         <v>46477</v>
@@ -2726,17 +2727,17 @@
       </c>
       <c r="AJ11" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 467.3 MW (EIA nameplate) and 2029; Entergy says 446 MW, late 2028. Vendor fair held Mar 2026 - subcontract procurement open; Entergy prioritizing Arkansas contractors. EPC not public (TIC possible).</t>
+          <t>CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="AK11" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC/GC (check TIC Entergy program); engage Arkansas electrical contractors from vendor fair.</t>
+          <t>Get on TSL Power Partners bidder list (Kiewit/TIC Lenexa) and S&amp;L approved-manufacturer list; register with Entergy supplier program.</t>
         </is>
       </c>
       <c r="AL11" s="38" t="inlineStr">
         <is>
-          <t>446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). Cost: Not disclosed (GAJA rider). EPC: Not public. OEM: Not found. Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). Cost: Not disclosed (GAJA rider). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM11" s="40" t="n"/>
@@ -2781,9 +2782,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>Bill Norton, Spokesman</t>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>John Robert Smith Jr., General Manager, New Gas Generation Development</t>
         </is>
       </c>
       <c r="G12" s="38" t="inlineStr">
@@ -2835,10 +2836,10 @@
       </c>
       <c r="V12" s="40" t="n"/>
       <c r="W12" s="44" t="n">
-        <v>47119</v>
+        <v>47118</v>
       </c>
       <c r="X12" s="44" t="n">
-        <v>46477</v>
+        <v>46416</v>
       </c>
       <c r="Y12" s="45" t="n"/>
       <c r="Z12" s="37" t="inlineStr">
@@ -2893,12 +2894,12 @@
       </c>
       <c r="AJ12" s="38" t="inlineStr">
         <is>
-          <t>Utility is Duke Energy Progress (not DEC as in Yes Energy). CC1 COD ~late 2028/early 2029; 2030 is CC2. Microsoft bought nearby Person County Mega Park (supply tie not confirmed by Duke). BOP electrical peak 2027.</t>
+          <t>CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="AK12" s="38" t="inlineStr">
         <is>
-          <t>Engage Zachry procurement for CC1 + CC2 as one pursuit; ZIP 27343 to be confirmed.</t>
+          <t>Engage Zachry procurement now for CC1 (+CC2 combined buy); contact John Robert Smith Jr. (Duke PM&amp;C).</t>
         </is>
       </c>
       <c r="AL12" s="38" t="inlineStr">
@@ -2956,9 +2957,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>Haley Fisackerly, President &amp; CEO</t>
+      <c r="F13" s="38" t="inlineStr">
+        <is>
+          <t>Ernest Rufus, Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
         </is>
       </c>
       <c r="G13" s="36" t="inlineStr">
@@ -3013,7 +3014,7 @@
         <v>46874</v>
       </c>
       <c r="X13" s="44" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="Y13" s="45" t="n"/>
       <c r="Z13" s="37" t="inlineStr">
@@ -3068,12 +3069,12 @@
       </c>
       <c r="AJ13" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 879 MW / $651M; Entergy says 754 MW / $1.2B. Cable pulls likely 2026-early 2027 - window closing. Indirect tie to AWS Mississippi buildout.</t>
+          <t>MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="AK13" s="38" t="inlineStr">
         <is>
-          <t>Contact TSL Power Partners / Kiewit Power Constructors electrical procurement now; leverage for Vicksburg.</t>
+          <t>Contact Ernest Rufus and TSL/TIC procurement now - target program buy for Vicksburg/Ironwood/Waterford.</t>
         </is>
       </c>
       <c r="AL13" s="38" t="inlineStr">
@@ -3133,9 +3134,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>Haley Fisackerly, President &amp; CEO</t>
+      <c r="F14" s="38" t="inlineStr">
+        <is>
+          <t>Ernest Rufus, Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
         </is>
       </c>
       <c r="G14" s="36" t="inlineStr">
@@ -3146,7 +3147,7 @@
       <c r="H14" s="39" t="n"/>
       <c r="I14" s="37" t="inlineStr">
         <is>
-          <t>IOU</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="J14" s="40" t="n"/>
@@ -3190,7 +3191,7 @@
         <v>46966</v>
       </c>
       <c r="X14" s="44" t="n">
-        <v>46477</v>
+        <v>46371</v>
       </c>
       <c r="Y14" s="45" t="n"/>
       <c r="Z14" s="37" t="inlineStr">
@@ -3245,17 +3246,17 @@
       </c>
       <c r="AJ14" s="38" t="inlineStr">
         <is>
-          <t>Best-timed Mississippi lead - ~1 year behind Delta Blues; procurement now-2027. EPC and turbine OEM not confirmed. AWS link contextual, not dedicated.</t>
+          <t>URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="AK14" s="38" t="inlineStr">
         <is>
-          <t>Confirm EPC (check if TSL/Kiewit again) via MS PSC certificate / MDEQ air permit; position early.</t>
+          <t>Engage TSL/TIC procurement and Ernest Rufus immediately.</t>
         </is>
       </c>
       <c r="AL14" s="38" t="inlineStr">
         <is>
-          <t>754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. Cost: ~$1.2B (Entergy); Yes Energy $700M not confirmed. EPC: Not public. OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. Cost: ~$1.2B (Entergy); Yes Energy $700M not confirmed. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM14" s="40" t="n"/>
@@ -3300,9 +3301,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
-        <is>
-          <t>Steve Baker, President &amp; COO</t>
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>John E. Niland, VP, New Technology &amp; Thermal Development</t>
         </is>
       </c>
       <c r="G15" s="36" t="inlineStr">
@@ -3359,7 +3360,7 @@
         <v>47208</v>
       </c>
       <c r="X15" s="44" t="n">
-        <v>46660</v>
+        <v>46568</v>
       </c>
       <c r="Y15" s="45" t="n"/>
       <c r="Z15" s="37" t="inlineStr">
@@ -3414,17 +3415,17 @@
       </c>
       <c r="AJ15" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy record outdated: RTO is PJM (not MISO), 918 MW simple cycle (not 1,150 MW CC), COD 2029 (not 2027), not yet under construction. I&amp;M load growth driven by AWS/Google/Microsoft data centers. Do not confuse with Maple Creek Energy (same county).</t>
+          <t>CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="AK15" s="38" t="inlineStr">
         <is>
-          <t>Engage Invenergy Thermal now (EPC not awarded/public); track IURC Cause 46389 final order.</t>
+          <t>Engage Boldt procurement and Invenergy thermal construction now (Q4 2026-Q1 2027) for MV/600V/tray bid lists.</t>
         </is>
       </c>
       <c r="AL15" s="38" t="inlineStr">
         <is>
-          <t>~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. Cost: ~$500M capital investment (Invenergy). EPC: Not public. OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM).</t>
+          <t>~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. Cost: ~$500M capital investment (Invenergy). EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM).</t>
         </is>
       </c>
       <c r="AM15" s="40" t="n"/>
@@ -3469,9 +3470,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>Phillip May, President &amp; CEO</t>
+      <c r="F16" s="38" t="inlineStr">
+        <is>
+          <t>Nicholas D. Pressler, Director, Power Development</t>
         </is>
       </c>
       <c r="G16" s="38" t="inlineStr">
@@ -3528,7 +3529,7 @@
         <v>47088</v>
       </c>
       <c r="X16" s="44" t="n">
-        <v>46477</v>
+        <v>46416</v>
       </c>
       <c r="Y16" s="45" t="n"/>
       <c r="Z16" s="37" t="inlineStr">
@@ -3583,12 +3584,12 @@
       </c>
       <c r="AJ16" s="38" t="inlineStr">
         <is>
-          <t>COD late 2028 (2030 in Yes Energy is Hyperion full operation). Related ~100 mi 500 kV transmission program (~$1.2B) is a separate opportunity; ~7 more Hyperion plants (5.2 GW) up for LPSC vote Dec 2026.</t>
+          <t>CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="AK16" s="38" t="inlineStr">
         <is>
-          <t>Engage TIC / TSL Power Partners procurement; open separate opportunity for Entergy 500 kV transmission lines.</t>
+          <t>Engage TSL/TIC procurement now; contact Nicholas Pressler; open separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="AL16" s="38" t="inlineStr">
@@ -3638,9 +3639,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>Phillip May, President &amp; CEO</t>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>Nicholas D. Pressler, Director, Power Development</t>
         </is>
       </c>
       <c r="G17" s="36" t="inlineStr">
@@ -3697,7 +3698,7 @@
         <v>47270</v>
       </c>
       <c r="X17" s="44" t="n">
-        <v>46568</v>
+        <v>46660</v>
       </c>
       <c r="Y17" s="45" t="n"/>
       <c r="Z17" s="37" t="inlineStr">
@@ -3752,17 +3753,17 @@
       </c>
       <c r="AJ17" s="38" t="inlineStr">
         <is>
-          <t>Waterford 6 (754 MW, ~Jul 2030) uses the same EPC - follow-on opportunity. MW varies by source (750-820). EPC name not yet public (possibly TIC/S&amp;L team).</t>
+          <t>CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="AK17" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC from LPSC Waterford 6 filing; pursue Waterford 5 + 6 together.</t>
+          <t>Pitch combined Waterford 5+6 cable package to TSL; contact Nicholas Pressler.</t>
         </is>
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. Cost: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. EPC: Not public. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. Cost: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -14836,12 +14837,12 @@
       <c r="CF7" s="39" t="n"/>
       <c r="CG7" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 2030 COD; public filings point to Dec 2031 (construction start Q4 2027). Cost not disclosed. Local opposition (water use). EPC not yet selected. Data-center tie not confirmed.</t>
+          <t>CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="CH7" s="38" t="inlineStr">
         <is>
-          <t>Contact Daniel Birmingham (Invenergy); track WI PSC CPCN filing for EPC selection; bundle with Union Depot CC.</t>
+          <t>Build relationship with Daniel Birmingham (Invenergy); watch PSC 5-CE-162 CPCN for EPC; get on EPC approved-vendor list in 2027.</t>
         </is>
       </c>
       <c r="CI7" s="38" t="inlineStr">
@@ -14858,12 +14859,12 @@
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>Viamontes</t>
+          <t>Pollock</t>
         </is>
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>Eliecer</t>
+          <t>Keith</t>
         </is>
       </c>
       <c r="C8" s="36" t="inlineStr">
@@ -14889,7 +14890,7 @@
       <c r="G8" s="40" t="n"/>
       <c r="H8" s="36" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>Project Director, OCAPS</t>
         </is>
       </c>
       <c r="I8" s="37" t="inlineStr">
@@ -15126,12 +15127,12 @@
       <c r="CF8" s="39" t="n"/>
       <c r="CG8" s="38" t="inlineStr">
         <is>
-          <t>Plant is now operating; new-build cable window closed. Keep for MRO/aftermarket and relationship with TIC / Sargent &amp; Lundy for next Entergy builds. Yes Energy MW (1,306) differs from Entergy (1,215).</t>
+          <t>In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="CH8" s="38" t="inlineStr">
         <is>
-          <t>Reclassify as aftermarket/MRO; use TIC &amp; S&amp;L relationship for Entergy pipeline (Titanium, Waterford 5/6).</t>
+          <t>Aftermarket/spares with Keith Pollock and Entergy fossil ops supply chain; use TIC/S&amp;L relationship for Entergy program plants.</t>
         </is>
       </c>
       <c r="CI8" s="38" t="inlineStr">
@@ -15148,13 +15149,17 @@
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="n"/>
+          <t>Burke</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>Vistra Corp (Luminant)</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="D9" s="37" t="inlineStr">
@@ -15175,7 +15180,7 @@
       <c r="G9" s="40" t="n"/>
       <c r="H9" s="36" t="inlineStr">
         <is>
-          <t>Project / Procurement contact</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="I9" s="37" t="inlineStr">
@@ -15408,12 +15413,12 @@
       <c r="CF9" s="39" t="n"/>
       <c r="CG9" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 2030; ERCOT/Cleanview show May 2028 COD. Link of ERCOT IDs to Vistra project based on GEM aliases + site/MW match. EPC and OEM not public. Urgent: procurement likely now-2027.</t>
+          <t>CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="CH9" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC via Vistra/TCEQ permit 178462; find Vistra Luminant project/procurement contact; quote both units (880 MW).</t>
+          <t>URGENT: identify EPC via TCEQ 178462 NAPD / Industrial Info; find Luminant project contact; quote both units (880 MW).</t>
         </is>
       </c>
       <c r="CI9" s="38" t="inlineStr">
@@ -15430,10 +15435,14 @@
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="n"/>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Georgia Power</t>
@@ -15457,7 +15466,7 @@
       <c r="G10" s="40" t="n"/>
       <c r="H10" s="36" t="inlineStr">
         <is>
-          <t>Project / Procurement contact</t>
+          <t>SVP &amp; Senior Production Officer</t>
         </is>
       </c>
       <c r="I10" s="37" t="inlineStr">
@@ -15613,7 +15622,11 @@
           <t>Georgia Power</t>
         </is>
       </c>
-      <c r="BF10" s="39" t="n"/>
+      <c r="BF10" s="38" t="inlineStr">
+        <is>
+          <t>Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024)</t>
+        </is>
+      </c>
       <c r="BG10" s="36" t="inlineStr">
         <is>
           <t>Georgia Power</t>
@@ -15694,12 +15707,12 @@
       <c r="CF10" s="39" t="n"/>
       <c r="CG10" s="38" t="inlineStr">
         <is>
-          <t>Late stage - Unit 8 cable likely bought; Units 9/10 BOP and commissioning needs may still be open. Load growth driven largely by data centers (no named customer). EPC not public.</t>
+          <t>LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="CH10" s="38" t="inlineStr">
         <is>
-          <t>Confirm EPC/electrical contractor at Yates; position for Units 9-10 and Southern Co. future IRP gas units.</t>
+          <t>Relationship/spares play via B&amp;V site procurement; position with Mitsubishi/B&amp;V for next Georgia Power CT/CC builds.</t>
         </is>
       </c>
       <c r="CI10" s="38" t="inlineStr">
@@ -15716,17 +15729,17 @@
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>Landreaux</t>
+          <t>Ruiz</t>
         </is>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>Entergy Arkansas</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="D11" s="37" t="inlineStr">
@@ -15747,7 +15760,7 @@
       <c r="G11" s="40" t="n"/>
       <c r="H11" s="36" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>VP, Power Development - New Generation</t>
         </is>
       </c>
       <c r="I11" s="37" t="inlineStr">
@@ -15811,7 +15824,7 @@
       <c r="AI11" s="41" t="n"/>
       <c r="AJ11" s="49" t="n"/>
       <c r="AK11" s="44" t="n">
-        <v>46935</v>
+        <v>47118</v>
       </c>
       <c r="AL11" s="43" t="n">
         <v>446</v>
@@ -15899,14 +15912,22 @@
           <t>Entergy Arkansas</t>
         </is>
       </c>
-      <c r="BF11" s="39" t="n"/>
+      <c r="BF11" s="38" t="inlineStr">
+        <is>
+          <t>TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page)</t>
+        </is>
+      </c>
       <c r="BG11" s="36" t="inlineStr">
         <is>
           <t>Entergy Arkansas</t>
         </is>
       </c>
       <c r="BH11" s="39" t="n"/>
-      <c r="BI11" s="39" t="n"/>
+      <c r="BI11" s="38" t="inlineStr">
+        <is>
+          <t>Mitsubishi Power (implied by TSL/MPWA program)</t>
+        </is>
+      </c>
       <c r="BJ11" s="39" t="n"/>
       <c r="BK11" s="39" t="n"/>
       <c r="BL11" s="38" t="inlineStr">
@@ -15976,12 +15997,12 @@
       <c r="CF11" s="39" t="n"/>
       <c r="CG11" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 467.3 MW (EIA nameplate) and 2029; Entergy says 446 MW, late 2028. Vendor fair held Mar 2026 - subcontract procurement open; Entergy prioritizing Arkansas contractors. EPC not public (TIC possible).</t>
+          <t>CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="CH11" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC/GC (check TIC Entergy program); engage Arkansas electrical contractors from vendor fair.</t>
+          <t>Get on TSL Power Partners bidder list (Kiewit/TIC Lenexa) and S&amp;L approved-manufacturer list; register with Entergy supplier program.</t>
         </is>
       </c>
       <c r="CI11" s="38" t="inlineStr">
@@ -15998,12 +16019,12 @@
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>Norton</t>
+          <t>Smith Jr.</t>
         </is>
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>John Robert</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
@@ -16027,9 +16048,9 @@
         </is>
       </c>
       <c r="G12" s="40" t="n"/>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>Spokesman</t>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>General Manager, New Gas Generation Development</t>
         </is>
       </c>
       <c r="I12" s="37" t="inlineStr">
@@ -16093,7 +16114,7 @@
       <c r="AI12" s="41" t="n"/>
       <c r="AJ12" s="49" t="n"/>
       <c r="AK12" s="44" t="n">
-        <v>47119</v>
+        <v>47118</v>
       </c>
       <c r="AL12" s="43" t="n">
         <v>1360</v>
@@ -16278,12 +16299,12 @@
       <c r="CF12" s="39" t="n"/>
       <c r="CG12" s="38" t="inlineStr">
         <is>
-          <t>Utility is Duke Energy Progress (not DEC as in Yes Energy). CC1 COD ~late 2028/early 2029; 2030 is CC2. Microsoft bought nearby Person County Mega Park (supply tie not confirmed by Duke). BOP electrical peak 2027.</t>
+          <t>CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="CH12" s="38" t="inlineStr">
         <is>
-          <t>Engage Zachry procurement for CC1 + CC2 as one pursuit; ZIP 27343 to be confirmed.</t>
+          <t>Engage Zachry procurement now for CC1 (+CC2 combined buy); contact John Robert Smith Jr. (Duke PM&amp;C).</t>
         </is>
       </c>
       <c r="CI12" s="38" t="inlineStr">
@@ -16300,17 +16321,17 @@
     <row r="13" ht="23" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>Fisackerly</t>
+          <t>Rufus</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Ernest</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Entergy Mississippi</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="D13" s="37" t="inlineStr">
@@ -16329,9 +16350,9 @@
         </is>
       </c>
       <c r="G13" s="40" t="n"/>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t>President &amp; CEO</t>
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
         </is>
       </c>
       <c r="I13" s="37" t="inlineStr">
@@ -16582,12 +16603,12 @@
       <c r="CF13" s="39" t="n"/>
       <c r="CG13" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy shows 879 MW / $651M; Entergy says 754 MW / $1.2B. Cable pulls likely 2026-early 2027 - window closing. Indirect tie to AWS Mississippi buildout.</t>
+          <t>MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="CH13" s="38" t="inlineStr">
         <is>
-          <t>Contact TSL Power Partners / Kiewit Power Constructors electrical procurement now; leverage for Vicksburg.</t>
+          <t>Contact Ernest Rufus and TSL/TIC procurement now - target program buy for Vicksburg/Ironwood/Waterford.</t>
         </is>
       </c>
       <c r="CI13" s="38" t="inlineStr">
@@ -16604,17 +16625,17 @@
     <row r="14" ht="23" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>Fisackerly</t>
+          <t>Rufus</t>
         </is>
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Ernest</t>
         </is>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>Entergy Mississippi</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="D14" s="37" t="inlineStr">
@@ -16633,9 +16654,9 @@
         </is>
       </c>
       <c r="G14" s="40" t="n"/>
-      <c r="H14" s="36" t="inlineStr">
-        <is>
-          <t>President &amp; CEO</t>
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
         </is>
       </c>
       <c r="I14" s="37" t="inlineStr">
@@ -16757,7 +16778,7 @@
       </c>
       <c r="AX14" s="38" t="inlineStr">
         <is>
-          <t>Former Baxter Wilson Steam Electric Station site</t>
+          <t>770 Kemp Bottom Rd (former Baxter Wilson site)</t>
         </is>
       </c>
       <c r="AY14" s="36" t="inlineStr">
@@ -16787,7 +16808,11 @@
           <t>Entergy Mississippi</t>
         </is>
       </c>
-      <c r="BF14" s="39" t="n"/>
+      <c r="BF14" s="38" t="inlineStr">
+        <is>
+          <t>TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page)</t>
+        </is>
+      </c>
       <c r="BG14" s="36" t="inlineStr">
         <is>
           <t>Entergy Mississippi</t>
@@ -16868,12 +16893,12 @@
       <c r="CF14" s="39" t="n"/>
       <c r="CG14" s="38" t="inlineStr">
         <is>
-          <t>Best-timed Mississippi lead - ~1 year behind Delta Blues; procurement now-2027. EPC and turbine OEM not confirmed. AWS link contextual, not dedicated.</t>
+          <t>URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="CH14" s="38" t="inlineStr">
         <is>
-          <t>Confirm EPC (check if TSL/Kiewit again) via MS PSC certificate / MDEQ air permit; position early.</t>
+          <t>Engage TSL/TIC procurement and Ernest Rufus immediately.</t>
         </is>
       </c>
       <c r="CI14" s="38" t="inlineStr">
@@ -16890,17 +16915,17 @@
     <row r="15" ht="23" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Niland</t>
         </is>
       </c>
       <c r="B15" s="36" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>John E.</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>Indiana Michigan Power (AEP)</t>
+          <t>Invenergy</t>
         </is>
       </c>
       <c r="D15" s="37" t="inlineStr">
@@ -16921,12 +16946,12 @@
       <c r="G15" s="40" t="n"/>
       <c r="H15" s="36" t="inlineStr">
         <is>
-          <t>President &amp; COO</t>
+          <t>VP, New Technology &amp; Thermal Development</t>
         </is>
       </c>
       <c r="I15" s="37" t="inlineStr">
         <is>
-          <t>End User</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="J15" s="37" t="inlineStr">
@@ -17075,7 +17100,11 @@
           <t>Invenergy (to be acquired by I&amp;M at COD)</t>
         </is>
       </c>
-      <c r="BF15" s="39" t="n"/>
+      <c r="BF15" s="38" t="inlineStr">
+        <is>
+          <t>The Boldt Company (constructor per Boldt project page - role to confirm)</t>
+        </is>
+      </c>
       <c r="BG15" s="36" t="inlineStr">
         <is>
           <t>Invenergy</t>
@@ -17156,12 +17185,12 @@
       <c r="CF15" s="39" t="n"/>
       <c r="CG15" s="38" t="inlineStr">
         <is>
-          <t>Yes Energy record outdated: RTO is PJM (not MISO), 918 MW simple cycle (not 1,150 MW CC), COD 2029 (not 2027), not yet under construction. I&amp;M load growth driven by AWS/Google/Microsoft data centers. Do not confuse with Maple Creek Energy (same county).</t>
+          <t>CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="CH15" s="38" t="inlineStr">
         <is>
-          <t>Engage Invenergy Thermal now (EPC not awarded/public); track IURC Cause 46389 final order.</t>
+          <t>Engage Boldt procurement and Invenergy thermal construction now (Q4 2026-Q1 2027) for MV/600V/tray bid lists.</t>
         </is>
       </c>
       <c r="CI15" s="38" t="inlineStr">
@@ -17178,17 +17207,17 @@
     <row r="16" ht="23" customHeight="1">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Pressler</t>
         </is>
       </c>
       <c r="B16" s="36" t="inlineStr">
         <is>
-          <t>Phillip</t>
+          <t>Nicholas D.</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>Entergy Louisiana</t>
+          <t>Entergy Services LLC</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
@@ -17209,7 +17238,7 @@
       <c r="G16" s="40" t="n"/>
       <c r="H16" s="36" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>Director, Power Development</t>
         </is>
       </c>
       <c r="I16" s="37" t="inlineStr">
@@ -17448,12 +17477,12 @@
       <c r="CF16" s="39" t="n"/>
       <c r="CG16" s="38" t="inlineStr">
         <is>
-          <t>COD late 2028 (2030 in Yes Energy is Hyperion full operation). Related ~100 mi 500 kV transmission program (~$1.2B) is a separate opportunity; ~7 more Hyperion plants (5.2 GW) up for LPSC vote Dec 2026.</t>
+          <t>CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="CH16" s="38" t="inlineStr">
         <is>
-          <t>Engage TIC / TSL Power Partners procurement; open separate opportunity for Entergy 500 kV transmission lines.</t>
+          <t>Engage TSL/TIC procurement now; contact Nicholas Pressler; open separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="CI16" s="38" t="inlineStr">
@@ -17470,17 +17499,17 @@
     <row r="17" ht="23" customHeight="1">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Pressler</t>
         </is>
       </c>
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>Phillip</t>
+          <t>Nicholas D.</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>Entergy Louisiana</t>
+          <t>Entergy Services LLC</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
@@ -17501,7 +17530,7 @@
       <c r="G17" s="40" t="n"/>
       <c r="H17" s="36" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>Director, Power Development</t>
         </is>
       </c>
       <c r="I17" s="37" t="inlineStr">
@@ -17655,7 +17684,11 @@
           <t>Entergy Louisiana</t>
         </is>
       </c>
-      <c r="BF17" s="39" t="n"/>
+      <c r="BF17" s="38" t="inlineStr">
+        <is>
+          <t>TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing</t>
+        </is>
+      </c>
       <c r="BG17" s="36" t="inlineStr">
         <is>
           <t>Entergy Louisiana</t>
@@ -17746,12 +17779,12 @@
       <c r="CF17" s="39" t="n"/>
       <c r="CG17" s="38" t="inlineStr">
         <is>
-          <t>Waterford 6 (754 MW, ~Jul 2030) uses the same EPC - follow-on opportunity. MW varies by source (750-820). EPC name not yet public (possibly TIC/S&amp;L team).</t>
+          <t>CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="CH17" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC from LPSC Waterford 6 filing; pursue Waterford 5 + 6 together.</t>
+          <t>Pitch combined Waterford 5+6 cable package to TSL; contact Nicholas Pressler.</t>
         </is>
       </c>
       <c r="CI17" s="38" t="inlineStr">
@@ -44417,4 +44450,1538 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B1" s="52" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="52" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="52" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="E1" s="52" t="inlineStr">
+        <is>
+          <t>Role on project</t>
+        </is>
+      </c>
+      <c r="F1" s="52" t="inlineStr">
+        <is>
+          <t>Published business contact</t>
+        </is>
+      </c>
+      <c r="G1" s="52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="52" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="inlineStr">
+        <is>
+          <t>Daniel Birmingham</t>
+        </is>
+      </c>
+      <c r="C2" s="53" t="inlineStr">
+        <is>
+          <t>Lead Developer</t>
+        </is>
+      </c>
+      <c r="D2" s="53" t="inlineStr">
+        <is>
+          <t>Invenergy</t>
+        </is>
+      </c>
+      <c r="E2" s="53" t="inlineStr">
+        <is>
+          <t>Developer lead</t>
+        </is>
+      </c>
+      <c r="F2" s="53" t="inlineStr"/>
+      <c r="G2" s="53" t="inlineStr">
+        <is>
+          <t>https://www.nbc26.com/lakeshore/two-natural-gas-power-plants-proposed-in-brillion</t>
+        </is>
+      </c>
+      <c r="H2" s="53" t="inlineStr">
+        <is>
+          <t>News quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>Brendan Conway</t>
+        </is>
+      </c>
+      <c r="C3" s="53" t="inlineStr">
+        <is>
+          <t>Spokesperson</t>
+        </is>
+      </c>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t>We Energies</t>
+        </is>
+      </c>
+      <c r="E3" s="53" t="inlineStr">
+        <is>
+          <t>Possible acquirer</t>
+        </is>
+      </c>
+      <c r="F3" s="53" t="inlineStr"/>
+      <c r="G3" s="53" t="inlineStr">
+        <is>
+          <t>https://www.wpr.org/news/energy-developer-planning-2-gigawatt-natural-gas-plants-northeast-wisconsin</t>
+        </is>
+      </c>
+      <c r="H3" s="53" t="inlineStr">
+        <is>
+          <t>News quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>Keith Pollock</t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>Project Director, OCAPS</t>
+        </is>
+      </c>
+      <c r="D4" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Texas</t>
+        </is>
+      </c>
+      <c r="E4" s="53" t="inlineStr">
+        <is>
+          <t>Owner project lead</t>
+        </is>
+      </c>
+      <c r="F4" s="53" t="inlineStr"/>
+      <c r="G4" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/construction-nears-completion-on-entergy-texas-orange-county-advanced-power-station</t>
+        </is>
+      </c>
+      <c r="H4" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>David Borde</t>
+        </is>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Texas</t>
+        </is>
+      </c>
+      <c r="E5" s="53" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="F5" s="53" t="inlineStr"/>
+      <c r="G5" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-texas-orange-county-advanced-power-station-begins-delivering-reliable-power-to-southeast-texas</t>
+        </is>
+      </c>
+      <c r="H5" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>James Malone</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>Director of Business Development</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>Sargent &amp; Lundy</t>
+        </is>
+      </c>
+      <c r="E6" s="53" t="inlineStr">
+        <is>
+          <t>Engineer of record</t>
+        </is>
+      </c>
+      <c r="F6" s="53" t="inlineStr"/>
+      <c r="G6" s="53" t="inlineStr">
+        <is>
+          <t>https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+        </is>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Kendra James</t>
+        </is>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Texas</t>
+        </is>
+      </c>
+      <c r="E7" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>Media line 281-297-2353</t>
+        </is>
+      </c>
+      <c r="G7" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/media-kit</t>
+        </is>
+      </c>
+      <c r="H7" s="53" t="inlineStr">
+        <is>
+          <t>Official website</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Jim Burke</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D8" s="53" t="inlineStr">
+        <is>
+          <t>Vistra Corp</t>
+        </is>
+      </c>
+      <c r="E8" s="53" t="inlineStr">
+        <is>
+          <t>Executive (no project contact public)</t>
+        </is>
+      </c>
+      <c r="F8" s="53" t="inlineStr"/>
+      <c r="G8" s="53" t="inlineStr">
+        <is>
+          <t>https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas</t>
+        </is>
+      </c>
+      <c r="H8" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Rick Anderson</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>SVP &amp; Senior Production Officer</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>Georgia Power</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>Owner executive</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr">
+        <is>
+          <t>https://www.georgiapower.com/news-hub/press-releases/first-new-natural-gas-turbine-delivered-to-georgia-power-plant-yates.html</t>
+        </is>
+      </c>
+      <c r="H9" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Cheryl Boddiford</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>SVP, North American Manufacturing &amp; Supply Chain Mgmt</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>Mitsubishi Power</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="inlineStr">
+        <is>
+          <t>EPC consortium (OEM)</t>
+        </is>
+      </c>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr">
+        <is>
+          <t>https://power.mhi.com/regions/amer/news/250819</t>
+        </is>
+      </c>
+      <c r="H10" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Rick Janik</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>Project Manager (Plant Barry Unit 8)</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>Black &amp; Veatch</t>
+        </is>
+      </c>
+      <c r="E11" s="53" t="inlineStr">
+        <is>
+          <t>Same EPC pairing at Southern Co. - not confirmed for Yates</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr">
+        <is>
+          <t>https://www.bv.com/en-US/projects/gas-fired-power-plant-project-defies-challenges-to-deliver-safe-reliable-power</t>
+        </is>
+      </c>
+      <c r="H11" s="53" t="inlineStr">
+        <is>
+          <t>Company website - indirect</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="inlineStr">
+        <is>
+          <t>VP, Power Development - New Generation</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E12" s="53" t="inlineStr">
+        <is>
+          <t>Owner new-generation executive</t>
+        </is>
+      </c>
+      <c r="F12" s="53" t="inlineStr"/>
+      <c r="G12" s="53" t="inlineStr">
+        <is>
+          <t>https://apps.apsc.arkansas.gov/pdf/24/24-072-U_67_1.pdf</t>
+        </is>
+      </c>
+      <c r="H12" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Laura Landreaux</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Arkansas</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="inlineStr"/>
+      <c r="G13" s="53" t="inlineStr">
+        <is>
+          <t>https://www.arkansasonline.com/news/2026/aug/21/entergy-breaks-ground-on-ironwood-power-station/</t>
+        </is>
+      </c>
+      <c r="H13" s="53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>Louise Duncan</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="inlineStr">
+        <is>
+          <t>VP, Power Plant Operations</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Arkansas</t>
+        </is>
+      </c>
+      <c r="E14" s="53" t="inlineStr">
+        <is>
+          <t>Plant operations</t>
+        </is>
+      </c>
+      <c r="F14" s="53" t="inlineStr"/>
+      <c r="G14" s="53" t="inlineStr">
+        <is>
+          <t>https://adeq.state.ar.us/downloads/WebDatabases/PermitsOnline/NPDES/PermitInformation/AR0001147_Certificate%20of%20Service%20Letter_20260430.pdf</t>
+        </is>
+      </c>
+      <c r="H14" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory document</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>Clay McMaster</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="inlineStr">
+        <is>
+          <t>Environmental/permit contact, Lake Catherine</t>
+        </is>
+      </c>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="inlineStr">
+        <is>
+          <t>Permitting</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr">
+        <is>
+          <t>wmcmast@entergy.com (ADEQ permit)</t>
+        </is>
+      </c>
+      <c r="G15" s="53" t="inlineStr">
+        <is>
+          <t>https://adeq.state.ar.us/downloads/WebDatabases/PermitsOnline/Air/1717-AOP-R9.pdf</t>
+        </is>
+      </c>
+      <c r="H15" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory document</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>Kendall Thornton</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>Stakeholder Engagement Coordinator</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Arkansas</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="inlineStr">
+        <is>
+          <t>Groundbreaking organizer</t>
+        </is>
+      </c>
+      <c r="F16" s="53" t="inlineStr"/>
+      <c r="G16" s="53" t="inlineStr">
+        <is>
+          <t>https://arkansasstatechamber.com/team-member/kendall-thornton/</t>
+        </is>
+      </c>
+      <c r="H16" s="53" t="inlineStr">
+        <is>
+          <t>Org website</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>Jason Rees</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>Director of Procurement</t>
+        </is>
+      </c>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E17" s="53" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="inlineStr"/>
+      <c r="G17" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reesjason/</t>
+        </is>
+      </c>
+      <c r="H17" s="53" t="inlineStr">
+        <is>
+          <t>LinkedIn - verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Supplier Registration</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E18" s="53" t="inlineStr">
+        <is>
+          <t>Supplier onboarding</t>
+        </is>
+      </c>
+      <c r="F18" s="53" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com; 844-387-9675</t>
+        </is>
+      </c>
+      <c r="G18" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/suppliers/how</t>
+        </is>
+      </c>
+      <c r="H18" s="53" t="inlineStr">
+        <is>
+          <t>Official website</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>John Robert Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>GM, New Gas Generation Development (PM&amp;C)</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>Duke Energy</t>
+        </is>
+      </c>
+      <c r="E19" s="53" t="inlineStr">
+        <is>
+          <t>Owner project development lead</t>
+        </is>
+      </c>
+      <c r="F19" s="53" t="inlineStr"/>
+      <c r="G19" s="53" t="inlineStr">
+        <is>
+          <t>https://starw1.ncuc.gov/NCUC/ViewFile.aspx?Id=5552fef5-9b1f-4e88-b9ca-0e649dafdbb5</t>
+        </is>
+      </c>
+      <c r="H19" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Ralph Biediger</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="inlineStr">
+        <is>
+          <t>EPC Group President</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>Zachry Group</t>
+        </is>
+      </c>
+      <c r="E20" s="53" t="inlineStr">
+        <is>
+          <t>EPC executive</t>
+        </is>
+      </c>
+      <c r="F20" s="53" t="inlineStr"/>
+      <c r="G20" s="53" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html</t>
+        </is>
+      </c>
+      <c r="H20" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>Bill Norton</t>
+        </is>
+      </c>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>Spokesperson</t>
+        </is>
+      </c>
+      <c r="D21" s="53" t="inlineStr">
+        <is>
+          <t>Duke Energy</t>
+        </is>
+      </c>
+      <c r="E21" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F21" s="53" t="inlineStr"/>
+      <c r="G21" s="53" t="inlineStr">
+        <is>
+          <t>https://www.cbs17.com/news/local-news/duke-energy-planning-for-natural-gas-plants-in-roxboro/</t>
+        </is>
+      </c>
+      <c r="H21" s="53" t="inlineStr">
+        <is>
+          <t>News quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>Stacy Hickman</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>Zachry Group</t>
+        </is>
+      </c>
+      <c r="E22" s="53" t="inlineStr">
+        <is>
+          <t>Site hiring</t>
+        </is>
+      </c>
+      <c r="F22" s="53" t="inlineStr"/>
+      <c r="G22" s="53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stacy-hickman/</t>
+        </is>
+      </c>
+      <c r="H22" s="53" t="inlineStr">
+        <is>
+          <t>LinkedIn - verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>Ernest Rufus</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E23" s="53" t="inlineStr">
+        <is>
+          <t>Owner project lead</t>
+        </is>
+      </c>
+      <c r="F23" s="53" t="inlineStr"/>
+      <c r="G23" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction</t>
+        </is>
+      </c>
+      <c r="H23" s="53" t="inlineStr">
+        <is>
+          <t>Official blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>Haley Fisackerly</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Mississippi</t>
+        </is>
+      </c>
+      <c r="E24" s="53" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="F24" s="53" t="inlineStr">
+        <is>
+          <t>Media line 769-262-0745</t>
+        </is>
+      </c>
+      <c r="G24" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-mississippi-breaks-ground-on-delta-blues-advanced-power-station</t>
+        </is>
+      </c>
+      <c r="H24" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>Vicksburg Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>Ernest Rufus</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>Senior Manager, Capital Projects</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E25" s="53" t="inlineStr">
+        <is>
+          <t>Owner project lead</t>
+        </is>
+      </c>
+      <c r="F25" s="53" t="inlineStr"/>
+      <c r="G25" s="53" t="inlineStr">
+        <is>
+          <t>https://www.vicksburgpost.com/news/vicksburg-board-grants-conditional-fee-waiver-for-new-entergy-power-plant-3320f9d2</t>
+        </is>
+      </c>
+      <c r="H25" s="53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>John E. Niland</t>
+        </is>
+      </c>
+      <c r="C26" s="53" t="inlineStr">
+        <is>
+          <t>VP, New Technology &amp; Thermal Development</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="inlineStr">
+        <is>
+          <t>Invenergy</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>Developer lead (IURC witness)</t>
+        </is>
+      </c>
+      <c r="F26" s="53" t="inlineStr"/>
+      <c r="G26" s="53" t="inlineStr">
+        <is>
+          <t>https://www.in.gov/iurc/files/ord_46295_123025.pdf</t>
+        </is>
+      </c>
+      <c r="H26" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>Daniel Runyan</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>SVP Development</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>Invenergy</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
+        <is>
+          <t>Developer executive</t>
+        </is>
+      </c>
+      <c r="F27" s="53" t="inlineStr"/>
+      <c r="G27" s="53" t="inlineStr">
+        <is>
+          <t>https://www.insideindianabusiness.com/articles/indiana-michigan-power-seeks-to-acquire-sullivan-county-natural-gas-plant</t>
+        </is>
+      </c>
+      <c r="H27" s="53" t="inlineStr">
+        <is>
+          <t>News quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>Steve Baker</t>
+        </is>
+      </c>
+      <c r="C28" s="53" t="inlineStr">
+        <is>
+          <t>President &amp; COO</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="inlineStr">
+        <is>
+          <t>Indiana Michigan Power (AEP)</t>
+        </is>
+      </c>
+      <c r="E28" s="53" t="inlineStr">
+        <is>
+          <t>Acquirer executive</t>
+        </is>
+      </c>
+      <c r="F28" s="53" t="inlineStr"/>
+      <c r="G28" s="53" t="inlineStr">
+        <is>
+          <t>https://www.aep.com/news/stories/view/11850/</t>
+        </is>
+      </c>
+      <c r="H28" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B29" s="53" t="inlineStr">
+        <is>
+          <t>Timothy B. Gaul</t>
+        </is>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>Director, Regulated Infrastructure Development</t>
+        </is>
+      </c>
+      <c r="D29" s="53" t="inlineStr">
+        <is>
+          <t>AEP Service Corp</t>
+        </is>
+      </c>
+      <c r="E29" s="53" t="inlineStr">
+        <is>
+          <t>Utility-side project lead (witness)</t>
+        </is>
+      </c>
+      <c r="F29" s="53" t="inlineStr"/>
+      <c r="G29" s="53" t="inlineStr">
+        <is>
+          <t>https://www.in.gov/iurc/files/ord_46238_091025.pdf</t>
+        </is>
+      </c>
+      <c r="H29" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B30" s="53" t="inlineStr">
+        <is>
+          <t>Timothy C. Kerns</t>
+        </is>
+      </c>
+      <c r="C30" s="53" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="inlineStr">
+        <is>
+          <t>Sterling Industrial LLC</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="inlineStr">
+        <is>
+          <t>Owner's engineer / technical witness</t>
+        </is>
+      </c>
+      <c r="F30" s="53" t="inlineStr"/>
+      <c r="G30" s="53" t="inlineStr">
+        <is>
+          <t>IURC Cause 46389 Petitioner's Exhibit 4</t>
+        </is>
+      </c>
+      <c r="H30" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="53" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B31" s="53" t="inlineStr">
+        <is>
+          <t>The Boldt Company</t>
+        </is>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>Constructor (role to confirm)</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="inlineStr">
+        <is>
+          <t>Boldt (Appleton, WI)</t>
+        </is>
+      </c>
+      <c r="E31" s="53" t="inlineStr">
+        <is>
+          <t>Construction Sep 2026-Feb 2029</t>
+        </is>
+      </c>
+      <c r="F31" s="53" t="inlineStr"/>
+      <c r="G31" s="53" t="inlineStr">
+        <is>
+          <t>https://www.boldt.com/discover/sycamore-riverside-energy-center/</t>
+        </is>
+      </c>
+      <c r="H31" s="53" t="inlineStr">
+        <is>
+          <t>Company website</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>Nicholas D. Pressler</t>
+        </is>
+      </c>
+      <c r="C32" s="53" t="inlineStr">
+        <is>
+          <t>Director, Power Development</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Services LLC</t>
+        </is>
+      </c>
+      <c r="E32" s="53" t="inlineStr">
+        <is>
+          <t>EPC/TSL selection witness</t>
+        </is>
+      </c>
+      <c r="F32" s="53" t="inlineStr"/>
+      <c r="G32" s="53" t="inlineStr">
+        <is>
+          <t>https://lpscpubvalence.lpsc.louisiana.gov/portal/PSC/ViewFile?fileId=hsljNiQroZw%3D</t>
+        </is>
+      </c>
+      <c r="H32" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B33" s="53" t="inlineStr">
+        <is>
+          <t>Phillip May</t>
+        </is>
+      </c>
+      <c r="C33" s="53" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Louisiana</t>
+        </is>
+      </c>
+      <c r="E33" s="53" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="F33" s="53" t="inlineStr"/>
+      <c r="G33" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
+        </is>
+      </c>
+      <c r="H33" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="53" t="inlineStr">
+        <is>
+          <t>Jim Niemiec</t>
+        </is>
+      </c>
+      <c r="C34" s="53" t="inlineStr">
+        <is>
+          <t>VP &amp; Chief Supply Chain Officer</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E34" s="53" t="inlineStr">
+        <is>
+          <t>Corporate procurement</t>
+        </is>
+      </c>
+      <c r="F34" s="53" t="inlineStr"/>
+      <c r="G34" s="53" t="inlineStr">
+        <is>
+          <t>https://nudc.com/staff-and-executive-leadership/board-directors/james-nbsp-w.-nbsp-niemiec-nbsp/</t>
+        </is>
+      </c>
+      <c r="H34" s="53" t="inlineStr">
+        <is>
+          <t>Org website</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>Kimberly Cook-Nelson</t>
+        </is>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>EVP &amp; Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="inlineStr">
+        <is>
+          <t>Generation &amp; capital projects executive</t>
+        </is>
+      </c>
+      <c r="F35" s="53" t="inlineStr"/>
+      <c r="G35" s="53" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/leadership/kimberly-cook-nelson</t>
+        </is>
+      </c>
+      <c r="H35" s="53" t="inlineStr">
+        <is>
+          <t>Official website</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>Brandon Scardigli</t>
+        </is>
+      </c>
+      <c r="C36" s="53" t="inlineStr">
+        <is>
+          <t>Media contact</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Louisiana</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F36" s="53" t="inlineStr">
+        <is>
+          <t>bscardi@entergy.com; 504-576-4132</t>
+        </is>
+      </c>
+      <c r="G36" s="53" t="inlineStr">
+        <is>
+          <t>https://www.opportunitylouisiana.gov/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
+        </is>
+      </c>
+      <c r="H36" s="53" t="inlineStr">
+        <is>
+          <t>Official release</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="53" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B37" s="53" t="inlineStr">
+        <is>
+          <t>Nicholas D. Pressler</t>
+        </is>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>Director, Power Development</t>
+        </is>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>Entergy Services LLC</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="inlineStr">
+        <is>
+          <t>EPC witness (Waterford 6 filing)</t>
+        </is>
+      </c>
+      <c r="F37" s="53" t="inlineStr"/>
+      <c r="G37" s="53" t="inlineStr">
+        <is>
+          <t>https://lpscpubvalence.lpsc.louisiana.gov/portal/PSC/ViewFile?fileId=hsljNiQroZw%3D</t>
+        </is>
+      </c>
+      <c r="H37" s="53" t="inlineStr">
+        <is>
+          <t>Regulatory filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="53" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t>Michelle Berg</t>
+        </is>
+      </c>
+      <c r="C38" s="53" t="inlineStr">
+        <is>
+          <t>Entergy representative</t>
+        </is>
+      </c>
+      <c r="D38" s="53" t="inlineStr">
+        <is>
+          <t>Entergy</t>
+        </is>
+      </c>
+      <c r="E38" s="53" t="inlineStr">
+        <is>
+          <t>Parish council briefing</t>
+        </is>
+      </c>
+      <c r="F38" s="53" t="inlineStr"/>
+      <c r="G38" s="53" t="inlineStr">
+        <is>
+          <t>https://citizenportal.ai/articles/6476185/Louisiana/St-Charles-Parish/Entergy-announces-plans-for-two-new-combined-cycle-units-at-Waterford-site-cites-2B-plus-investment-and-local-jobs</t>
+        </is>
+      </c>
+      <c r="H38" s="53" t="inlineStr">
+        <is>
+          <t>Secondary source - verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="53" t="inlineStr">
+        <is>
+          <t>All Entergy program plants</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="inlineStr">
+        <is>
+          <t>TSL Power Partners (JV TIC/Kiewit + Sargent &amp; Lundy)</t>
+        </is>
+      </c>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>EPC procurement</t>
+        </is>
+      </c>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>TSL Power Partners</t>
+        </is>
+      </c>
+      <c r="E39" s="53" t="inlineStr">
+        <is>
+          <t>Buys cable for Entergy CC/CT program</t>
+        </is>
+      </c>
+      <c r="F39" s="53" t="inlineStr">
+        <is>
+          <t>8900 Renner Blvd, Lenexa, KS 66219</t>
+        </is>
+      </c>
+      <c r="G39" s="53" t="inlineStr">
+        <is>
+          <t>https://www.ticus.com/entergy-program/</t>
+        </is>
+      </c>
+      <c r="H39" s="53" t="inlineStr">
+        <is>
+          <t>Company website / customs record</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AJ7" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="AK7" s="38" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AL7" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. EPC: Not public. OEM: GE Vernova (5x 7F.05 CTs, H35 generators). Utility: American Transmission Co (ATC); possible offtaker We Energies. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. EPC: Not public. OEM: GE Vernova (5x 7F.05 CTs, H35 generators). Utility: American Transmission Co (ATC); possible offtaker We Energies. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM7" s="40" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AJ8" s="38" t="inlineStr">
         <is>
-          <t>In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="AK8" s="38" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AL8" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. EPC: Mitsubishi Power / TIC / Sargent &amp; Lundy (EPC consortium). OEM: Mitsubishi Power (2x M501JAC GT, ST, HRSG). Utility: Entergy Texas. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. EPC: Mitsubishi Power / TIC / Sargent &amp; Lundy (EPC consortium). OEM: Mitsubishi Power (2x M501JAC GT, ST, HRSG). Utility: Entergy Texas. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM8" s="40" t="n"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AJ9" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="AK9" s="38" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AL9" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. EPC: Not public. OEM: Not found. Utility: ERCOT (West Texas). RTO: Electric Reliability Council of Texas (ERCOT).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. EPC: Not public. OEM: Not found. Utility: ERCOT (West Texas). RTO: Electric Reliability Council of Texas (ERCOT).</t>
         </is>
       </c>
       <c r="AM9" s="40" t="n"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AJ10" s="38" t="inlineStr">
         <is>
-          <t>LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="AK10" s="38" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AL10" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE).</t>
         </is>
       </c>
       <c r="AM10" s="40" t="n"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AJ11" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="AK11" s="38" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AL11" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM11" s="40" t="n"/>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AJ12" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="AK12" s="38" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AL12" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. EPC: Zachry Group. OEM: GE Vernova (advanced-class GTs). Utility: Duke Energy Progress. RTO: Southeast (SE).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. EPC: Zachry Group. OEM: GE Vernova (advanced-class GTs). Utility: Duke Energy Progress. RTO: Southeast (SE).</t>
         </is>
       </c>
       <c r="AM12" s="40" t="n"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AJ13" s="38" t="inlineStr">
         <is>
-          <t>MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="AK13" s="38" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AL13" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. EPC: TSL Power Partners (Kiewit / TIC). OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. EPC: TSL Power Partners (Kiewit / TIC). OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM13" s="40" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AJ14" s="38" t="inlineStr">
         <is>
-          <t>URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="AK14" s="38" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AL14" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM14" s="40" t="n"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AJ15" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="AK15" s="38" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AL15" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM).</t>
         </is>
       </c>
       <c r="AM15" s="40" t="n"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AJ16" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="AK16" s="38" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AL16" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. EPC: TSL Power Partners (TIC / Sargent &amp; Lundy) with Mitsubishi Power Americas. OEM: Mitsubishi Power M501JAC (2x 1x1 CC). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. EPC: TSL Power Partners (TIC / Sargent &amp; Lundy) with Mitsubishi Power Americas. OEM: Mitsubishi Power M501JAC (2x 1x1 CC). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM16" s="40" t="n"/>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AJ17" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="AK17" s="38" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -14843,7 +14843,7 @@
       <c r="CF7" s="39" t="n"/>
       <c r="CG7" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="CH7" s="38" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="CI7" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation.</t>
         </is>
       </c>
       <c r="CJ7" s="38" t="inlineStr">
@@ -15135,7 +15135,7 @@
       <c r="CF8" s="39" t="n"/>
       <c r="CG8" s="38" t="inlineStr">
         <is>
-          <t>In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="CH8" s="38" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="CI8" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026.</t>
         </is>
       </c>
       <c r="CJ8" s="38" t="inlineStr">
@@ -15423,7 +15423,7 @@
       <c r="CF9" s="39" t="n"/>
       <c r="CG9" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="CH9" s="38" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="CI9" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth.</t>
         </is>
       </c>
       <c r="CJ9" s="38" t="inlineStr">
@@ -15719,7 +15719,7 @@
       <c r="CF10" s="39" t="n"/>
       <c r="CG10" s="38" t="inlineStr">
         <is>
-          <t>LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="CH10" s="38" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="CI10" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027.</t>
         </is>
       </c>
       <c r="CJ10" s="38" t="inlineStr">
@@ -16011,7 +16011,7 @@
       <c r="CF11" s="39" t="n"/>
       <c r="CG11" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="CH11" s="38" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="CI11" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027).</t>
         </is>
       </c>
       <c r="CJ11" s="38" t="inlineStr">
@@ -16315,7 +16315,7 @@
       <c r="CF12" s="39" t="n"/>
       <c r="CG12" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="CH12" s="38" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="CI12" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind.</t>
         </is>
       </c>
       <c r="CJ12" s="38" t="inlineStr">
@@ -16621,7 +16621,7 @@
       <c r="CF13" s="39" t="n"/>
       <c r="CG13" s="38" t="inlineStr">
         <is>
-          <t>MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="CH13" s="38" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="CI13" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation.</t>
         </is>
       </c>
       <c r="CJ13" s="38" t="inlineStr">
@@ -16913,7 +16913,7 @@
       <c r="CF14" s="39" t="n"/>
       <c r="CG14" s="38" t="inlineStr">
         <is>
-          <t>URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="CH14" s="38" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="CI14" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus.</t>
         </is>
       </c>
       <c r="CJ14" s="38" t="inlineStr">
@@ -17207,7 +17207,7 @@
       <c r="CF15" s="39" t="n"/>
       <c r="CG15" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="CH15" s="38" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="CI15" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station.</t>
         </is>
       </c>
       <c r="CJ15" s="38" t="inlineStr">
@@ -17501,7 +17501,7 @@
       <c r="CF16" s="39" t="n"/>
       <c r="CG16" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="CH16" s="38" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="CI16" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years.</t>
         </is>
       </c>
       <c r="CJ16" s="38" t="inlineStr">
@@ -17805,7 +17805,7 @@
       <c r="CF17" s="39" t="n"/>
       <c r="CG17" s="38" t="inlineStr">
         <is>
-          <t>CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="CH17" s="38" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="CI17" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load.</t>
         </is>
       </c>
       <c r="CJ17" s="38" t="inlineStr">

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AL7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. EPC: Not public. OEM: GE Vernova (5x 7F.05 CTs, H35 generators). Utility: American Transmission Co (ATC); possible offtaker We Energies. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. EPC: Not public. OEM: GE Vernova (5x 7F.05 CTs, H35 generators). Utility: American Transmission Co (ATC); possible offtaker We Energies. RTO: Midcontinent Independent System Operator (MISO). Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="AM7" s="40" t="n"/>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AL8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. EPC: Mitsubishi Power / TIC / Sargent &amp; Lundy (EPC consortium). OEM: Mitsubishi Power (2x M501JAC GT, ST, HRSG). Utility: Entergy Texas. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. EPC: Mitsubishi Power / TIC / Sargent &amp; Lundy (EPC consortium). OEM: Mitsubishi Power (2x M501JAC GT, ST, HRSG). Utility: Entergy Texas. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="AM8" s="40" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AL9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. EPC: Not public. OEM: Not found. Utility: ERCOT (West Texas). RTO: Electric Reliability Council of Texas (ERCOT).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. EPC: Not public. OEM: Not found. Utility: ERCOT (West Texas). RTO: Electric Reliability Council of Texas (ERCOT). Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="AM9" s="40" t="n"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AL10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE). Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="AM10" s="40" t="n"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AL11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="AM11" s="40" t="n"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AL12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. EPC: Zachry Group. OEM: GE Vernova (advanced-class GTs). Utility: Duke Energy Progress. RTO: Southeast (SE).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. EPC: Zachry Group. OEM: GE Vernova (advanced-class GTs). Utility: Duke Energy Progress. RTO: Southeast (SE). Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="AM12" s="40" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AL13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. EPC: TSL Power Partners (Kiewit / TIC). OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. EPC: TSL Power Partners (Kiewit / TIC). OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="AM13" s="40" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AL14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="AM14" s="40" t="n"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AL15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM). Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="AM15" s="40" t="n"/>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AL16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. EPC: TSL Power Partners (TIC / Sargent &amp; Lundy) with Mitsubishi Power Americas. OEM: Mitsubishi Power M501JAC (2x 1x1 CC). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. EPC: TSL Power Partners (TIC / Sargent &amp; Lundy) with Mitsubishi Power Americas. OEM: Mitsubishi Power M501JAC (2x 1x1 CC). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="AM16" s="40" t="n"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -13502,10 +13502,23 @@
       <formula1>YesNo</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL17" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14853,7 +14866,7 @@
       </c>
       <c r="CI7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="CJ7" s="38" t="inlineStr">
@@ -15145,7 +15158,7 @@
       </c>
       <c r="CI8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="CJ8" s="38" t="inlineStr">
@@ -15433,7 +15446,7 @@
       </c>
       <c r="CI9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="CJ9" s="38" t="inlineStr">
@@ -15729,7 +15742,7 @@
       </c>
       <c r="CI10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="CJ10" s="38" t="inlineStr">
@@ -16021,7 +16034,7 @@
       </c>
       <c r="CI11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027).</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="CJ11" s="38" t="inlineStr">
@@ -16325,7 +16338,7 @@
       </c>
       <c r="CI12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="CJ12" s="38" t="inlineStr">
@@ -16631,7 +16644,7 @@
       </c>
       <c r="CI13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="CJ13" s="38" t="inlineStr">
@@ -16923,7 +16936,7 @@
       </c>
       <c r="CI14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="CJ14" s="38" t="inlineStr">
@@ -17217,7 +17230,7 @@
       </c>
       <c r="CI15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="CJ15" s="38" t="inlineStr">
@@ -17511,7 +17524,7 @@
       </c>
       <c r="CI16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="CJ16" s="38" t="inlineStr">
@@ -17815,7 +17828,7 @@
       </c>
       <c r="CI17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load.</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="CJ17" s="38" t="inlineStr">
@@ -34948,10 +34961,23 @@
       <formula1>YesNo</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI17" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AL7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. EPC: Not public. OEM: GE Vernova (5x 7F.05 CTs, H35 generators). Utility: American Transmission Co (ATC); possible offtaker We Energies. RTO: Midcontinent Independent System Operator (MISO). Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. RTO: Midcontinent Independent System Operator (MISO). Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="AM7" s="40" t="n"/>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AL8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. EPC: Mitsubishi Power / TIC / Sargent &amp; Lundy (EPC consortium). OEM: Mitsubishi Power (2x M501JAC GT, ST, HRSG). Utility: Entergy Texas. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="AM8" s="40" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AL9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. EPC: Not public. OEM: Not found. Utility: ERCOT (West Texas). RTO: Electric Reliability Council of Texas (ERCOT). Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. RTO: Electric Reliability Council of Texas (ERCOT). Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="AM9" s="40" t="n"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AL10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. EPC: Mitsubishi Power Americas + Black &amp; Veatch Construction (EPC consortium, contract 1/12/2024). OEM: Mitsubishi Power M501JAC CTs; Mitsubishi Electric VP-X generators. Utility: Georgia Power. RTO: Southeast (SE). Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. RTO: Southeast (SE). Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="AM10" s="40" t="n"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AL11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Mitsubishi Power (implied by TSL/MPWA program). Utility: Entergy Arkansas. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="AM11" s="40" t="n"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AL12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. EPC: Zachry Group. OEM: GE Vernova (advanced-class GTs). Utility: Duke Energy Progress. RTO: Southeast (SE). Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. RTO: Southeast (SE). Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="AM12" s="40" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AL13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. EPC: TSL Power Partners (Kiewit / TIC). OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="AM13" s="40" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AL14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. EPC: TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). OEM: Unverified (Yes Energy: Mitsubishi). Utility: Entergy Mississippi. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="AM14" s="40" t="n"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AL15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. EPC: The Boldt Company (constructor per Boldt project page - role to confirm). OEM: GE Vernova (4x 7F.05 CTs). Utility: Indiana Michigan Power (AEP). RTO: PJM Interconnection (PJM). Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. RTO: PJM Interconnection (PJM). Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="AM15" s="40" t="n"/>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AL16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. EPC: TSL Power Partners (TIC / Sargent &amp; Lundy) with Mitsubishi Power Americas. OEM: Mitsubishi Power M501JAC (2x 1x1 CC). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="AM16" s="40" t="n"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. EPC: TSL Power Partners (TIC + Sargent &amp; Lundy) - implied by LPSC Waterford 6 filing. OEM: Mitsubishi Power M501JAC (per GEM). Utility: Entergy Louisiana. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="CI7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. ~1.2 GW simple-cycle peaker (5x GE 7F.05) next to the proposed 750 MW Union Depot CC (~1.95 GW combined). Three 345 kV overhead gen-ties to ATC Forest Junction substation. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="CJ7" s="38" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="CI8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. 1,215 MW hydrogen-capable 2x1 combined cycle at the Sabine site, built by Mitsubishi/TIC/S&amp;L consortium. Online Oct 2026. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="CJ8" s="38" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CI9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. Two dual-fuel simple-cycle CTs (~860 MW total; Unit I ~440 MW) at the existing Permian Basin Power Plant, raising site to 1,185 MW. Serves Permian oil &amp; gas load growth. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="CJ9" s="38" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="CI10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. Three simple-cycle dual-fuel M501JAC units (~1.3 GW) at existing Plant Yates; Unit 8 Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="CJ10" s="38" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="CI11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. 446 MW hydrogen-capable simple-cycle CT on ~20 acres of the Lake Catherine site, replacing Lake Catherine Unit 4 (retiring end-2027). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="CJ11" s="38" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="CI12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. 1,360 MW 2x1 hydrogen-capable GE Vernova combined cycle at Duke's Roxboro coal site, full EPC by Zachry; identical CC2 ~1 year behind. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="CJ12" s="38" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="CI13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable combined cycle replacing the 1950s Andrus plant in Greenville; ~1.5 mi new transmission line to existing substation. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="CJ13" s="38" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="CI14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. 754 MW hydrogen-capable, carbon-capture-enabled combined cycle on the demolished Baxter Wilson site; tied contextually to the AWS $3B Vicksburg data center campus. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="CJ14" s="38" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="CI15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. ~918-935 MW simple-cycle peaker (4x GE 7F.05) developed by Invenergy, acquired by I&amp;M at COD (Mar 2029); interconnects at AEP Sullivan 345 kV station. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="CJ15" s="38" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="CI16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. Two 1x1 hydrogen-capable combined-cycle units (~1.5 GW) serving Meta's Hyperion AI data center campus; Meta pays full revenue requirement for 15 years. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="CJ16" s="38" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="CI17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. 1x1 Mitsubishi M501JAC combined cycle on Entergy's existing Waterford site (Waterford 1-3), 500 kV interconnection; supports Meta Hyperion load. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="CJ17" s="38" t="inlineStr">

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -49,7 +49,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -84,6 +84,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -132,10 +139,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -293,9 +301,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -13502,23 +13515,10 @@
       <formula1>YesNo</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL17" r:id="rId11"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -34961,23 +34961,10 @@
       <formula1>YesNo</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI17" r:id="rId11"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -44348,11 +44335,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="160" customWidth="1" min="2" max="2"/>
+    <col width="140" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44363,143 +44350,507 @@
       </c>
       <c r="B1" s="53" t="inlineStr">
         <is>
-          <t>Key sources (web research 10/29/2026)</t>
+          <t>Source link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Forest Junction Energy Center</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
-        <is>
-          <t>https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ ; https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot ; https://forestjunctionenergycenter.invenergy.com/ ; https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="54" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>https://forestjunctionenergycenter.invenergy.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Orange County Advanced Power Station (OCAPS)</t>
         </is>
       </c>
-      <c r="B3" s="54" t="inlineStr">
-        <is>
-          <t>https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ ; https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ ; https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr">
-        <is>
-          <t>https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas ; https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin ; https://www.gem.wiki/Permian_Power_power_station ; https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/Permian_Power_power_station</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
-        <is>
-          <t>https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html ; https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf ; https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Ironwood Power Station</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
-        <is>
-          <t>https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station ; https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ ; https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Person County Combined Cycle 1 (CC1)</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
-        <is>
-          <t>https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html ; https://www.duke-energy.com/info/person ; https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>https://www.duke-energy.com/info/person</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Delta Blues Advanced Power Station</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
-        <is>
-          <t>https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ ; https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction ; https://www.gem.wiki/Delta_Blues_Advanced_Power_Station ; https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="54" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/Delta_Blues_Advanced_Power_Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Vicksburg Advanced Power Station</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
-        <is>
-          <t>https://www.entergymississippi.com/generation/vicksburg ; https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ ; https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergymississippi.com/generation/vicksburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Vicksburg Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Vicksburg Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Sycamore Riverside Energy Center</t>
         </is>
       </c>
-      <c r="B10" s="54" t="inlineStr">
-        <is>
-          <t>https://www.aep.com/news/stories/view/11850/ ; https://sycamoreriverside.invenergy.com/about-project ; https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf ; https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>https://www.aep.com/news/stories/view/11850/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>https://sycamoreriverside.invenergy.com/about-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
         </is>
       </c>
-      <c r="B11" s="54" t="inlineStr">
-        <is>
-          <t>https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation ; https://www.ticus.com/entergy-program/ ; https://www.gem.wiki/Franklin_Farms_power_station ; https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>https://www.ticus.com/entergy-program/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t>https://www.gem.wiki/Franklin_Farms_power_station</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Waterford 5 Power Station</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
-        <is>
-          <t>https://www.entergylouisiana.com/waterford5-6 ; https://www.interconnection.fyi/project/miso-e0029 ; https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergylouisiana.com/waterford5-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>https://www.interconnection.fyi/project/miso-e0029</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44592,7 +44943,7 @@
         </is>
       </c>
       <c r="F2" s="54" t="inlineStr"/>
-      <c r="G2" s="54" t="inlineStr">
+      <c r="G2" s="56" t="inlineStr">
         <is>
           <t>https://www.nbc26.com/lakeshore/two-natural-gas-power-plants-proposed-in-brillion</t>
         </is>
@@ -44630,7 +44981,7 @@
         </is>
       </c>
       <c r="F3" s="54" t="inlineStr"/>
-      <c r="G3" s="54" t="inlineStr">
+      <c r="G3" s="56" t="inlineStr">
         <is>
           <t>https://www.wpr.org/news/energy-developer-planning-2-gigawatt-natural-gas-plants-northeast-wisconsin</t>
         </is>
@@ -44668,7 +45019,7 @@
         </is>
       </c>
       <c r="F4" s="54" t="inlineStr"/>
-      <c r="G4" s="54" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/news/construction-nears-completion-on-entergy-texas-orange-county-advanced-power-station</t>
         </is>
@@ -44706,7 +45057,7 @@
         </is>
       </c>
       <c r="F5" s="54" t="inlineStr"/>
-      <c r="G5" s="54" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/news/entergy-texas-orange-county-advanced-power-station-begins-delivering-reliable-power-to-southeast-texas</t>
         </is>
@@ -44744,7 +45095,7 @@
         </is>
       </c>
       <c r="F6" s="54" t="inlineStr"/>
-      <c r="G6" s="54" t="inlineStr">
+      <c r="G6" s="56" t="inlineStr">
         <is>
           <t>https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
@@ -44786,7 +45137,7 @@
           <t>Media line 281-297-2353</t>
         </is>
       </c>
-      <c r="G7" s="54" t="inlineStr">
+      <c r="G7" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/news/media-kit</t>
         </is>
@@ -44824,7 +45175,7 @@
         </is>
       </c>
       <c r="F8" s="54" t="inlineStr"/>
-      <c r="G8" s="54" t="inlineStr">
+      <c r="G8" s="56" t="inlineStr">
         <is>
           <t>https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas</t>
         </is>
@@ -44862,7 +45213,7 @@
         </is>
       </c>
       <c r="F9" s="54" t="inlineStr"/>
-      <c r="G9" s="54" t="inlineStr">
+      <c r="G9" s="56" t="inlineStr">
         <is>
           <t>https://www.georgiapower.com/news-hub/press-releases/first-new-natural-gas-turbine-delivered-to-georgia-power-plant-yates.html</t>
         </is>
@@ -44900,7 +45251,7 @@
         </is>
       </c>
       <c r="F10" s="54" t="inlineStr"/>
-      <c r="G10" s="54" t="inlineStr">
+      <c r="G10" s="56" t="inlineStr">
         <is>
           <t>https://power.mhi.com/regions/amer/news/250819</t>
         </is>
@@ -44938,7 +45289,7 @@
         </is>
       </c>
       <c r="F11" s="54" t="inlineStr"/>
-      <c r="G11" s="54" t="inlineStr">
+      <c r="G11" s="56" t="inlineStr">
         <is>
           <t>https://www.bv.com/en-US/projects/gas-fired-power-plant-project-defies-challenges-to-deliver-safe-reliable-power</t>
         </is>
@@ -44976,7 +45327,7 @@
         </is>
       </c>
       <c r="F12" s="54" t="inlineStr"/>
-      <c r="G12" s="54" t="inlineStr">
+      <c r="G12" s="56" t="inlineStr">
         <is>
           <t>https://apps.apsc.arkansas.gov/pdf/24/24-072-U_67_1.pdf</t>
         </is>
@@ -45014,7 +45365,7 @@
         </is>
       </c>
       <c r="F13" s="54" t="inlineStr"/>
-      <c r="G13" s="54" t="inlineStr">
+      <c r="G13" s="56" t="inlineStr">
         <is>
           <t>https://www.arkansasonline.com/news/2026/aug/21/entergy-breaks-ground-on-ironwood-power-station/</t>
         </is>
@@ -45052,7 +45403,7 @@
         </is>
       </c>
       <c r="F14" s="54" t="inlineStr"/>
-      <c r="G14" s="54" t="inlineStr">
+      <c r="G14" s="56" t="inlineStr">
         <is>
           <t>https://adeq.state.ar.us/downloads/WebDatabases/PermitsOnline/NPDES/PermitInformation/AR0001147_Certificate%20of%20Service%20Letter_20260430.pdf</t>
         </is>
@@ -45094,7 +45445,7 @@
           <t>wmcmast@entergy.com (ADEQ permit)</t>
         </is>
       </c>
-      <c r="G15" s="54" t="inlineStr">
+      <c r="G15" s="56" t="inlineStr">
         <is>
           <t>https://adeq.state.ar.us/downloads/WebDatabases/PermitsOnline/Air/1717-AOP-R9.pdf</t>
         </is>
@@ -45132,7 +45483,7 @@
         </is>
       </c>
       <c r="F16" s="54" t="inlineStr"/>
-      <c r="G16" s="54" t="inlineStr">
+      <c r="G16" s="56" t="inlineStr">
         <is>
           <t>https://arkansasstatechamber.com/team-member/kendall-thornton/</t>
         </is>
@@ -45170,7 +45521,7 @@
         </is>
       </c>
       <c r="F17" s="54" t="inlineStr"/>
-      <c r="G17" s="54" t="inlineStr">
+      <c r="G17" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/reesjason/</t>
         </is>
@@ -45212,7 +45563,7 @@
           <t>esupplier@entergy.com; 844-387-9675</t>
         </is>
       </c>
-      <c r="G18" s="54" t="inlineStr">
+      <c r="G18" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/suppliers/how</t>
         </is>
@@ -45250,7 +45601,7 @@
         </is>
       </c>
       <c r="F19" s="54" t="inlineStr"/>
-      <c r="G19" s="54" t="inlineStr">
+      <c r="G19" s="56" t="inlineStr">
         <is>
           <t>https://starw1.ncuc.gov/NCUC/ViewFile.aspx?Id=5552fef5-9b1f-4e88-b9ca-0e649dafdbb5</t>
         </is>
@@ -45288,7 +45639,7 @@
         </is>
       </c>
       <c r="F20" s="54" t="inlineStr"/>
-      <c r="G20" s="54" t="inlineStr">
+      <c r="G20" s="56" t="inlineStr">
         <is>
           <t>https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html</t>
         </is>
@@ -45326,7 +45677,7 @@
         </is>
       </c>
       <c r="F21" s="54" t="inlineStr"/>
-      <c r="G21" s="54" t="inlineStr">
+      <c r="G21" s="56" t="inlineStr">
         <is>
           <t>https://www.cbs17.com/news/local-news/duke-energy-planning-for-natural-gas-plants-in-roxboro/</t>
         </is>
@@ -45364,7 +45715,7 @@
         </is>
       </c>
       <c r="F22" s="54" t="inlineStr"/>
-      <c r="G22" s="54" t="inlineStr">
+      <c r="G22" s="56" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/stacy-hickman/</t>
         </is>
@@ -45402,7 +45753,7 @@
         </is>
       </c>
       <c r="F23" s="54" t="inlineStr"/>
-      <c r="G23" s="54" t="inlineStr">
+      <c r="G23" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction</t>
         </is>
@@ -45444,7 +45795,7 @@
           <t>Media line 769-262-0745</t>
         </is>
       </c>
-      <c r="G24" s="54" t="inlineStr">
+      <c r="G24" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/news/entergy-mississippi-breaks-ground-on-delta-blues-advanced-power-station</t>
         </is>
@@ -45482,7 +45833,7 @@
         </is>
       </c>
       <c r="F25" s="54" t="inlineStr"/>
-      <c r="G25" s="54" t="inlineStr">
+      <c r="G25" s="56" t="inlineStr">
         <is>
           <t>https://www.vicksburgpost.com/news/vicksburg-board-grants-conditional-fee-waiver-for-new-entergy-power-plant-3320f9d2</t>
         </is>
@@ -45520,7 +45871,7 @@
         </is>
       </c>
       <c r="F26" s="54" t="inlineStr"/>
-      <c r="G26" s="54" t="inlineStr">
+      <c r="G26" s="56" t="inlineStr">
         <is>
           <t>https://www.in.gov/iurc/files/ord_46295_123025.pdf</t>
         </is>
@@ -45558,7 +45909,7 @@
         </is>
       </c>
       <c r="F27" s="54" t="inlineStr"/>
-      <c r="G27" s="54" t="inlineStr">
+      <c r="G27" s="56" t="inlineStr">
         <is>
           <t>https://www.insideindianabusiness.com/articles/indiana-michigan-power-seeks-to-acquire-sullivan-county-natural-gas-plant</t>
         </is>
@@ -45596,7 +45947,7 @@
         </is>
       </c>
       <c r="F28" s="54" t="inlineStr"/>
-      <c r="G28" s="54" t="inlineStr">
+      <c r="G28" s="56" t="inlineStr">
         <is>
           <t>https://www.aep.com/news/stories/view/11850/</t>
         </is>
@@ -45634,7 +45985,7 @@
         </is>
       </c>
       <c r="F29" s="54" t="inlineStr"/>
-      <c r="G29" s="54" t="inlineStr">
+      <c r="G29" s="56" t="inlineStr">
         <is>
           <t>https://www.in.gov/iurc/files/ord_46238_091025.pdf</t>
         </is>
@@ -45710,7 +46061,7 @@
         </is>
       </c>
       <c r="F31" s="54" t="inlineStr"/>
-      <c r="G31" s="54" t="inlineStr">
+      <c r="G31" s="56" t="inlineStr">
         <is>
           <t>https://www.boldt.com/discover/sycamore-riverside-energy-center/</t>
         </is>
@@ -45748,7 +46099,7 @@
         </is>
       </c>
       <c r="F32" s="54" t="inlineStr"/>
-      <c r="G32" s="54" t="inlineStr">
+      <c r="G32" s="56" t="inlineStr">
         <is>
           <t>https://lpscpubvalence.lpsc.louisiana.gov/portal/PSC/ViewFile?fileId=hsljNiQroZw%3D</t>
         </is>
@@ -45786,7 +46137,7 @@
         </is>
       </c>
       <c r="F33" s="54" t="inlineStr"/>
-      <c r="G33" s="54" t="inlineStr">
+      <c r="G33" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
         </is>
@@ -45824,7 +46175,7 @@
         </is>
       </c>
       <c r="F34" s="54" t="inlineStr"/>
-      <c r="G34" s="54" t="inlineStr">
+      <c r="G34" s="56" t="inlineStr">
         <is>
           <t>https://nudc.com/staff-and-executive-leadership/board-directors/james-nbsp-w.-nbsp-niemiec-nbsp/</t>
         </is>
@@ -45862,7 +46213,7 @@
         </is>
       </c>
       <c r="F35" s="54" t="inlineStr"/>
-      <c r="G35" s="54" t="inlineStr">
+      <c r="G35" s="56" t="inlineStr">
         <is>
           <t>https://www.entergy.com/leadership/kimberly-cook-nelson</t>
         </is>
@@ -45904,7 +46255,7 @@
           <t>bscardi@entergy.com; 504-576-4132</t>
         </is>
       </c>
-      <c r="G36" s="54" t="inlineStr">
+      <c r="G36" s="56" t="inlineStr">
         <is>
           <t>https://www.opportunitylouisiana.gov/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
         </is>
@@ -45942,7 +46293,7 @@
         </is>
       </c>
       <c r="F37" s="54" t="inlineStr"/>
-      <c r="G37" s="54" t="inlineStr">
+      <c r="G37" s="56" t="inlineStr">
         <is>
           <t>https://lpscpubvalence.lpsc.louisiana.gov/portal/PSC/ViewFile?fileId=hsljNiQroZw%3D</t>
         </is>
@@ -45980,7 +46331,7 @@
         </is>
       </c>
       <c r="F38" s="54" t="inlineStr"/>
-      <c r="G38" s="54" t="inlineStr">
+      <c r="G38" s="56" t="inlineStr">
         <is>
           <t>https://citizenportal.ai/articles/6476185/Louisiana/St-Charles-Parish/Entergy-announces-plans-for-two-new-combined-cycle-units-at-Waterford-site-cites-2B-plus-investment-and-local-jobs</t>
         </is>
@@ -46022,7 +46373,7 @@
           <t>8900 Renner Blvd, Lenexa, KS 66219</t>
         </is>
       </c>
-      <c r="G39" s="54" t="inlineStr">
+      <c r="G39" s="56" t="inlineStr">
         <is>
           <t>https://www.ticus.com/entergy-program/</t>
         </is>
@@ -46034,6 +46385,45 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AJ7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*RPBD* CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="AK7" s="38" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AL7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. RTO: Midcontinent Independent System Operator (MISO). Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+          <t>*RPBD* OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. INVESTMENT: Total project investment Not disclosed; est. W&amp;C value $9,624,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="AM7" s="40" t="n"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AJ8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="AK8" s="38" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AL8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+          <t>*RPBD* OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. INVESTMENT: Total project investment ~$1.2B (power-eng.com); Yes Energy $555M not confirmed; est. W&amp;C value $9,720,000 ($8/kW). W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="AM8" s="40" t="n"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AJ9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*RPBD* CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="AK9" s="38" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="AL9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. RTO: Electric Reliability Council of Texas (ERCOT). Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
+          <t>*RPBD* OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. INVESTMENT: Total project investment Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026); est. W&amp;C value $3,520,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="AM9" s="40" t="n"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AJ10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="AK10" s="38" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AL10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. RTO: Southeast (SE). Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
+          <t>*RPBD* OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. INVESTMENT: Total project investment Not public; PSC staff ~$1B for 3 units; est. W&amp;C value $3,862,400 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="AM10" s="40" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AJ11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*RPBD* CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="AK11" s="38" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AL11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
+          <t>*RPBD* OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). INVESTMENT: Total project investment Not disclosed (GAJA rider); est. W&amp;C value $3,568,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="AM11" s="40" t="n"/>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AJ12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*RPBD* CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="AK12" s="38" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AL12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. RTO: Southeast (SE). Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
+          <t>*RPBD* OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. INVESTMENT: Total project investment ~$2.13B (CC1, DEP Class 3 estimate); est. W&amp;C value $10,880,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="AM12" s="40" t="n"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AJ13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
+          <t>*RPBD* MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="AK13" s="38" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AL13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="AM13" s="40" t="n"/>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AJ14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
+          <t>*RPBD* URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="AK14" s="38" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AL14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $700M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="AM14" s="40" t="n"/>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AJ15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*RPBD* CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="AK15" s="38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AL15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. RTO: PJM Interconnection (PJM). Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
+          <t>*RPBD* OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). INVESTMENT: Total project investment ~$500M capital investment (Invenergy); est. W&amp;C value $7,344,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="AM15" s="40" t="n"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AJ16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*RPBD* CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="AK16" s="38" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="AL16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*RPBD* OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,000,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="AM16" s="40" t="n"/>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AJ17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*RPBD* CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="AK17" s="38" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. RTO: Midcontinent Independent System Operator (MISO). Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,560,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -14856,7 +14856,7 @@
       <c r="CF7" s="39" t="n"/>
       <c r="CG7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*RPBD* CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="CH7" s="38" t="inlineStr">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="CI7" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019673557). Total project investment: Not disclosed. W&amp;C value (est. $8/kW): $9,624,000. OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
+          <t>*RPBD* OVERVIEW: Proposed ~1,203 MW natural-gas simple-cycle PEAKING plant by Invenergy, planned alongside the 750 MW Union Depot Energy Center combined cycle on an adjacent site (~1.95 GW total campus). Alternate site identified in Town of Woodville. TECHNOLOGY &amp; EQUIPMENT: 5x GE 7F.05 combustion turbines with GE H35 generators, each with generator step-up transformer; designed for continuous duty but expected to run mainly at peak. SITE: GREENFIELD - privately owned agricultural land east of WI-57, north of US-10, Town of Brillion, Calumet County (acreage not yet published; see PSC engineering plan). INTERCONNECTION: three 345 kV overhead gen-tie lines to ATC's Forest Junction 345 kV substation (ATC also expanding 345 kV lines south to new Sheboygan River substation). OWNERSHIP/STATUS: Developer Invenergy; We Energies listed it in rate-case planning (possible acquirer, needs PSC approval). Engineering plan filed Aug 2026; CPCN application expected fall 2026 (PSC docket 5-CE-162); construction start targeted Q4 2027; COD ~Dec 2031. EPC not yet selected. INVESTMENT: Total project investment Not disclosed; est. W&amp;C value $9,624,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Plus overhead conductor for 3x 345 kV gen-ties; large opportunity if bundled with Union Depot CC. Ref: https://dailyreporter.com/2026/08/31/invenergy-proposes-two-natural-gas-plants-calumet-county/ | https://fox11online.com/news/local/calumet-county-power-plant-proposed-energy-centers-town-of-brillion-power-megawatts-gigawatts-we-energies-invenergy-town-of-woodville-forest-junction-union-depot | https://forestjunctionenergycenter.invenergy.com/ | https://www.nbc26.com/lakeshore/neighbors-push-back-against-proposed-natural-gas-facility-in-town-of-brillion</t>
         </is>
       </c>
       <c r="CJ7" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $9,624,000 ($8/kW x 1,203 MW). Total project investment: Not disclosed.</t>
+          <t>*RPBD* Total project investment: Not disclosed. Est. W&amp;C value: $9,624,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       <c r="CF8" s="39" t="n"/>
       <c r="CG8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="CH8" s="38" t="inlineStr">
@@ -15158,12 +15158,12 @@
       </c>
       <c r="CI8" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017200239). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. W&amp;C value (est. $8/kW): $9,720,000. OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
+          <t>*RPBD* OVERVIEW: 1,215 MW natural-gas COMBINED-CYCLE plant, Entergy Texas' newest unit; entered commercial service Oct 14, 2026; serves ~230,000 homes in industrial Southeast Texas. TECHNOLOGY &amp; EQUIPMENT: Mitsubishi Power powertrain - 2x M501JAC gas turbines, HRSGs and steam turbine (2x1 configuration); dual-fuel, hydrogen-capable (30% H2 at start, designed for up to 100%). SITE: BROWNFIELD - ~26.2-acre footprint inside/adjacent to Entergy Texas' existing Sabine Power Plant in Bridge City, Orange County (existing gas plant with transmission and water infrastructure). OWNERSHIP/EPC: Entergy Texas; EPC consortium Mitsubishi Power (powertrain), Sargent &amp; Lundy (engineer of record), TIC - The Industrial Company (constructor). STATUS: Construction Apr 2023-2026, first fire Apr 2026, in service Oct 2026. INVESTMENT: Total project investment ~$1.2B (power-eng.com); Yes Energy $555M not confirmed; est. W&amp;C value $9,720,000 ($8/kW). W&amp;C NEEDS: New-build cable scope complete. Remaining: MRO/spares (MV, 600V, tray &amp; instrumentation cable), outage and warranty/punch-list work; reference project for the same TIC/S&amp;L/Mitsubishi team now building Entergy's LA/MS/AR plants. Ref: https://www.click2houston.com/news/local/2026/10/14/entergy-texas-orange-county-advanced-power-station-now-delivering-power-to-southeast-texas/ | https://www.power-eng.com/gas/turbines/entergy-texas-1-2-gw-ccgt-plant-is-now-online/ | https://www.sargentlundy.com/projects/orange-county-advanced-power-station/</t>
         </is>
       </c>
       <c r="CJ8" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $9,720,000 ($8/kW x 1,215 MW). Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed.</t>
+          <t>*RPBD* Total project investment: ~$1.2B (power-eng.com); Yes Energy $555M not confirmed. Est. W&amp;C value: $9,720,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15436,7 @@
       <c r="CF9" s="39" t="n"/>
       <c r="CG9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*RPBD* CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="CH9" s="38" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="CI9" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018470514). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). W&amp;C value (est. $8/kW): $3,520,000. OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
+          <t>*RPBD* OVERVIEW: Vistra/Luminant expansion of the existing Permian Basin Power Plant in Monahans - two new large natural-gas SIMPLE-CYCLE units totaling 860 MW (ERCOT queue: Vast Sands Power I 28INR0105 and II 28INR0109, ~440 MW each), taking the site from 325 MW to 1,185 MW. Driven by Permian oil &amp; gas load growth. TECHNOLOGY &amp; EQUIPMENT: 2x dual-fuel (gas/oil) advanced-class combustion turbine generators with SCR and oxidation catalyst (TCEQ permit 178462); ~440 MW per unit implies H/J-class frames (OEM not published). SITE: BROWNFIELD - existing operating gas plant at 600 N Yucca Dr, Monahans, Ward County (existing 5x 65 MW CTs, gas supply and ERCOT interconnection in place); acreage not published. OWNERSHIP/STATUS: Permian Power I LLC (Vistra). FID Sep 29, 2025; $583M Texas Energy Fund loan Jun 2026 ($172M drawn by Jun 30, 2026); COD May/Jun 2028. EPC not public. INVESTMENT: Total project investment Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026); est. W&amp;C value $3,520,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://gov.texas.gov/news/post/governor-abbott-announces-texas-energy-fund-loan-for-860-mw-of-new-power-in-west-texas | https://investor.vistracorp.com/2025-09-29-Vistra-Announces-Plans-to-Build-New-Gas-Fueled-Dispatchable-Power-Units-in-the-Permian-Basin | https://www.gem.wiki/Permian_Power_power_station | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/178462-pls-english.pdf</t>
         </is>
       </c>
       <c r="CJ9" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $3,520,000 ($8/kW x 440 MW). Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026).</t>
+          <t>*RPBD* Total project investment: Not disclosed; financed in part by $583M Texas Energy Fund loan (3.0%, Jun 2026). Est. W&amp;C value: $3,520,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       <c r="CF10" s="39" t="n"/>
       <c r="CG10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="CH10" s="38" t="inlineStr">
@@ -15742,12 +15742,12 @@
       </c>
       <c r="CI10" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018823691). Total project investment: Not public; PSC staff ~$1B for 3 units. W&amp;C value (est. $8/kW): $3,862,400. OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
+          <t>*RPBD* OVERVIEW: Georgia Power's first new gas turbines in a decade - three simple-cycle PEAKING units (~1,300 MW total, ~442-463 MW each) at Plant Yates; this record is Unit 9 (COD Q2 2027). Unit 8 Q4 2026, Unit 10 Q3 2027. ~600 construction jobs. Driven by Georgia load growth (data centers/industrial). TECHNOLOGY &amp; EQUIPMENT: 3x Mitsubishi Power M501JAC air-cooled combustion turbines with Mitsubishi Electric VP-X generators (assembled in Savannah, GA); dual-fuel gas/oil; ~30-minute start; hydrogen-capable with modifications. SITE: BROWNFIELD - existing Plant Yates generating site (former coal/gas station on the Chattahoochee River), Newnan, Coweta County, with existing transmission yard. OWNERSHIP/EPC: Georgia Power (Southern Company); EPC consortium Mitsubishi Power Americas + Black &amp; Veatch Construction (contract Jan 12, 2024). Cost not public (PSC staff ~$1B for 3 units). GA PSC monitoring docket 55931. INVESTMENT: Total project investment Not public; PSC staff ~$1B for 3 units; est. W&amp;C value $3,862,400 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Window: bulk cable for all 3 units most likely purchased 2024-25; remaining top-ups, change orders, spares. Ref: https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://www.energy.gov/sites/default/files/2026-07/20260622_EnvReview_Completion_Yates.pdf | https://www.modernpowersystems.com/news/progress-at-1-3-gw-plant-yates-gas-fired-plant/</t>
         </is>
       </c>
       <c r="CJ10" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $3,862,400 ($8/kW x 482.8 MW). Total project investment: Not public; PSC staff ~$1B for 3 units.</t>
+          <t>*RPBD* Total project investment: Not public; PSC staff ~$1B for 3 units. Est. W&amp;C value: $3,862,400 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16024,7 @@
       <c r="CF11" s="39" t="n"/>
       <c r="CG11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*RPBD* CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="CH11" s="38" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="CI11" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019705142). Total project investment: Not disclosed (GAJA rider). W&amp;C value (est. $8/kW): $3,568,000. OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
+          <t>*RPBD* OVERVIEW: 446 MW natural-gas SIMPLE-CYCLE combustion turbine (Entergy Arkansas 'Next Generation Arkansas'), replacing the 50+ year-old Lake Catherine Unit 4 (retiring end-2027). Formerly 'Lake Catherine 5'. ~260 peak construction jobs; Entergy prioritizing Arkansas contractors (vendor fair Mar 18, 2026). TECHNOLOGY &amp; EQUIPMENT: single advanced-class combustion turbine generator, hydrogen-capable (30% co-fire, future 100% conversion); Mitsubishi implied by the TSL/Mitsubishi Entergy program. SITE: BROWNFIELD - ~20 acres within the existing Lake Catherine Power Generation site, Jones Mill near Malvern, Hot Spring County; reuses existing gas, water and transmission infrastructure. OWNERSHIP/EPC: Entergy Arkansas; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). APSC CCN approved Apr 2025; site construction Q2 2026-Q2 2028; groundbreaking Aug 20, 2026; COD Q4 2028. Cost recovered via GAJA rider (not disclosed). INVESTMENT: Total project investment Not disclosed (GAJA rider); est. W&amp;C value $3,568,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Ref: https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station | https://www.modernpowersystems.com/news/entergy-arkansas-starts-construction-on-446-mw-ironwood-power-station/ | https://www.entergy.com/news/ironwood-power-plant-vendor-fair-for-arkansas-contractors-announced</t>
         </is>
       </c>
       <c r="CJ11" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $3,568,000 ($8/kW x 446 MW). Total project investment: Not disclosed (GAJA rider).</t>
+          <t>*RPBD* Total project investment: Not disclosed (GAJA rider). Est. W&amp;C value: $3,568,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       <c r="CF12" s="39" t="n"/>
       <c r="CG12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*RPBD* CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="CH12" s="38" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="CI12" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10017400436). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). W&amp;C value (est. $8/kW): $10,880,000. OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
+          <t>*RPBD* OVERVIEW: 1,360 MW natural-gas COMBINED-CYCLE block (first of two identical blocks, 2,720 MW total) at Duke's 'Person County Energy Complex' (Roxboro plant), enabling retirement of Roxboro coal units 1 &amp; 4. NCEMC co-owns ~225 MW. Nearby Microsoft-owned Person County Mega Park (~1,350 acres). TECHNOLOGY &amp; EQUIPMENT: 2x1 advanced-class, hydrogen-capable CC - 2x GE Vernova gas turbines, 2x HRSGs, 1x GE Vernova steam turbine generator (~450 tons); first GT on site Jul 23, 2026. SITE: BROWNFIELD - ~50 acres of undeveloped land within the existing Roxboro coal plant property, Semora Road side, Semora/Roxboro, Person County. OWNERSHIP/EPC: Duke Energy Progress (majority) + NCEMC; full EPC Zachry Group (awarded Aug 2025). NCUC CPCN Oct 2025; groundbreaking Feb 13, 2026; COD Q4 2028 (CC2 Q4 2029). Cost ~$2.13B (CC1). Two new tie lines from the site. INVESTMENT: Total project investment ~$2.13B (CC1, DEP Class 3 estimate); est. W&amp;C value $10,880,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. CC2 doubles the scope ~1 year later with the same EPC. Ref: https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html | https://www.duke-energy.com/info/person | https://www.theassemblync.com/news/business/person-county-microsoft-data-center-nondisclosure-agreements/</t>
         </is>
       </c>
       <c r="CJ12" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $10,880,000 ($8/kW x 1,360 MW). Total project investment: ~$2.13B (CC1, DEP Class 3 estimate).</t>
+          <t>*RPBD* Total project investment: ~$2.13B (CC1, DEP Class 3 estimate). Est. W&amp;C value: $10,880,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       <c r="CF13" s="39" t="n"/>
       <c r="CG13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
+          <t>*RPBD* MAIN WINDOW LIKELY PASSED: HRSG erection May 2026 ("anchor bolts up"), COD May 2028 -&gt; bulk cable likely bought; remaining late releases, change orders, I&amp;C top-ups. EPC TSL Power Partners (Kiewit/TIC), Kiewit 200+ on site. Use as entry to TSL Entergy program buy for sister plants. Yes Energy 879 MW/$651M vs Entergy 754 MW/$1.2B.</t>
         </is>
       </c>
       <c r="CH13" s="38" t="inlineStr">
@@ -16644,12 +16644,12 @@
       </c>
       <c r="CI13" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10018299981). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="CJ13" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $6,032,000 ($8/kW x 754 MW). Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed.</t>
+          <t>*RPBD* Total project investment: ~$1.2B (Entergy); Yes Energy $651M not confirmed. Est. W&amp;C value: $6,032,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       <c r="CF14" s="39" t="n"/>
       <c r="CG14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
+          <t>*RPBD* URGENT: groundbreaking Oct 21 2025, Baxter Wilson demolition Dec 2025, COD Aug 2028 -&gt; cable window now through ~Feb 2027; may be partly placed if TSL bought with Delta Blues. Linked contextually to AWS $3B Vicksburg campus. Entergy MS media line 769-262-0745.</t>
         </is>
       </c>
       <c r="CH14" s="38" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="CI14" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019088992). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. W&amp;C value (est. $8/kW): $6,032,000. OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant, next phase of 'Superpower Mississippi'; ~560 construction jobs, 21 permanent. Contextually linked to Amazon/AWS's $3B Vicksburg data-center campus (AWS covers its service-extension costs). TECHNOLOGY &amp; EQUIPMENT: combined cycle (gas turbine + HRSG + steam turbine), hydrogen-blend capable and carbon-capture enabled; turbine OEM not confirmed (Mitsubishi likely via TSL/Mitsubishi Entergy program). SITE: BROWNFIELD - former Baxter Wilson Steam Electric Station (1960s gas/oil plant, retired 2022; large structures demolished Dec 17, 2025), 770 Kemp Bottom Rd, Vicksburg, Warren County, on the Mississippi River; existing transmission/gas corridors (acreage not published). OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power Americas (per TIC Entergy Program page). Groundbreaking Oct 21, 2025; COD Aug 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $700M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Ref: https://www.entergymississippi.com/generation/vicksburg | https://www.powermag.com/entergy-mississippi-adding-third-gas-fired-power-plant-to-superpower-strategy/ | https://www.datacenterdynamics.com/en/news/amazon-to-build-3bn-data-center-campus-in-vicksburg-mississippi/</t>
         </is>
       </c>
       <c r="CJ14" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $6,032,000 ($8/kW x 754 MW). Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed.</t>
+          <t>*RPBD* Total project investment: ~$1.2B (Entergy); Yes Energy $700M not confirmed. Est. W&amp;C value: $6,032,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       <c r="CF15" s="39" t="n"/>
       <c r="CG15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*RPBD* CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="CH15" s="38" t="inlineStr">
@@ -17230,12 +17230,12 @@
       </c>
       <c r="CI15" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019254864). Total project investment: ~$500M capital investment (Invenergy). W&amp;C value (est. $8/kW): $7,344,000. OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
+          <t>*RPBD* OVERVIEW: ~918-935 MW natural-gas SIMPLE-CYCLE PEAKING plant developed by Invenergy and to be acquired by Indiana Michigan Power (AEP) at COD (Mar 31, 2029) to meet data-center-driven load growth (AWS, Google, Microsoft). Formerly queued as Sullivan Generating Station 1 &amp; 2 (1,150 MW CC concept). TECHNOLOGY &amp; EQUIPMENT: 4x GE Vernova 7F.05 combustion turbines (~232 MW each), dual-fuel natural gas with ultra-low-sulfur distillate backup; gas via ~5.5-mile 24-inch ONEOK lateral. SITE: BROWNFIELD-ADJACENT - next to I&amp;M's retired, demolished Breed coal plant, CR 925N, Fairbanks Township, Sullivan County; ~64-acre plant footprint within ~356-acre parcel (local meeting summary - verify). Invenergy holds land under purchase option. INTERCONNECTION: AEP/I&amp;M Sullivan 345 kV station (new 345 kV breakers), PJM. OWNERSHIP/STATUS: Invenergy (developer) -&gt; I&amp;M; IURC Cause 46389 order expected end-2026; constructor The Boldt Company lists construction Sep 2026-Feb 2029; ~$500M capital (Invenergy). INVESTMENT: Total project investment ~$500M capital investment (Invenergy); est. W&amp;C value $7,344,000 ($8/kW). W&amp;C NEEDS (simple-cycle peaker): MV power cable (5-35 kV) for auxiliary transformers, MV switchgear, fuel-gas compressors and black-start/aux systems; 600V power &amp; TC-ER tray cable for turbine packages, MCCs, fuel oil forwarding (if dual fuel) and SCR/ammonia systems; shielded instrumentation &amp; control cable; bare copper grounding grid per unit and switchyard; switchyard control/relay cable; building wire for control/admin buildings. Less cable per MW than a CC (no HRSG/steam cycle). Dual-fuel adds fuel-oil system cabling. Ref: https://www.aep.com/news/stories/view/11850/ | https://sycamoreriverside.invenergy.com/about-project | https://www.pjm.com/pub/planning/project-queues/facilities/ab1087_fac.pdf | https://www.gem.wiki/Sycamore_Riverside_Energy_Center</t>
         </is>
       </c>
       <c r="CJ15" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $7,344,000 ($8/kW x 918 MW). Total project investment: ~$500M capital investment (Invenergy).</t>
+          <t>*RPBD* Total project investment: ~$500M capital investment (Invenergy). Est. W&amp;C value: $7,344,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       <c r="CF16" s="39" t="n"/>
       <c r="CG16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*RPBD* CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="CH16" s="38" t="inlineStr">
@@ -17524,12 +17524,12 @@
       </c>
       <c r="CI16" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019228423). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). W&amp;C value (est. $8/kW): $12,000,000. OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*RPBD* OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,000,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="CJ16" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $12,000,000 ($8/kW x 1,500 MW). Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony).</t>
+          <t>*RPBD* Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). Est. W&amp;C value: $12,000,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -17818,7 +17818,7 @@
       <c r="CF17" s="39" t="n"/>
       <c r="CG17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*RPBD* CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="CH17" s="38" t="inlineStr">
@@ -17828,12 +17828,12 @@
       </c>
       <c r="CI17" s="38" t="inlineStr">
         <is>
-          <t>*Reported Pipeline/BD selection - Source: Yes Energy Generation Projects 08/24/2026, W&amp;C-Filtered Selection (Project ID 10019089005). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. W&amp;C value (est. $8/kW): $6,560,000. OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,560,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="CJ17" s="38" t="inlineStr">
         <is>
-          <t>Source: Yes Energy Generation Projects 08/24/2026 (filtered: NG, Adv. Dev./Under Construction, COD 2027-2030, prob &gt;=0.7), verified by web research 10/29/2026. Est. W&amp;C value $6,560,000 ($8/kW x 820 MW). Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed.</t>
+          <t>*RPBD* Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. Est. W&amp;C value: $6,560,000 ($8/kW).</t>
         </is>
       </c>
     </row>

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Named Contacts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ProjectStage">'Dropdowns'!$A$7:INDEX('Dropdowns'!$A$7:$A$106,COUNTA('Dropdowns'!$A$7:$A$106))</definedName>
@@ -49,7 +50,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -91,6 +92,10 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -143,7 +148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,6 +310,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0"/>
@@ -1975,8 +1981,9 @@
         </is>
       </c>
       <c r="L7" s="40" t="n"/>
-      <c r="M7" s="41" t="n">
-        <v>9624000</v>
+      <c r="M7" s="41">
+        <f>P7*1000*8</f>
+        <v/>
       </c>
       <c r="N7" s="42" t="n"/>
       <c r="O7" s="43" t="n"/>
@@ -2154,8 +2161,9 @@
         </is>
       </c>
       <c r="L8" s="40" t="n"/>
-      <c r="M8" s="41" t="n">
-        <v>9720000</v>
+      <c r="M8" s="41">
+        <f>P8*1000*8</f>
+        <v/>
       </c>
       <c r="N8" s="42" t="n"/>
       <c r="O8" s="43" t="n"/>
@@ -2321,8 +2329,9 @@
         </is>
       </c>
       <c r="L9" s="40" t="n"/>
-      <c r="M9" s="41" t="n">
-        <v>3520000</v>
+      <c r="M9" s="41">
+        <f>P9*1000*8</f>
+        <v/>
       </c>
       <c r="N9" s="42" t="n"/>
       <c r="O9" s="43" t="n"/>
@@ -2488,8 +2497,9 @@
         </is>
       </c>
       <c r="L10" s="40" t="n"/>
-      <c r="M10" s="41" t="n">
-        <v>3862400</v>
+      <c r="M10" s="41">
+        <f>P10*1000*8</f>
+        <v/>
       </c>
       <c r="N10" s="42" t="n"/>
       <c r="O10" s="43" t="n"/>
@@ -2655,8 +2665,9 @@
         </is>
       </c>
       <c r="L11" s="40" t="n"/>
-      <c r="M11" s="41" t="n">
-        <v>3568000</v>
+      <c r="M11" s="41">
+        <f>P11*1000*8</f>
+        <v/>
       </c>
       <c r="N11" s="42" t="n"/>
       <c r="O11" s="43" t="n"/>
@@ -2822,8 +2833,9 @@
         </is>
       </c>
       <c r="L12" s="40" t="n"/>
-      <c r="M12" s="41" t="n">
-        <v>10880000</v>
+      <c r="M12" s="41">
+        <f>P12*1000*8</f>
+        <v/>
       </c>
       <c r="N12" s="42" t="n"/>
       <c r="O12" s="43" t="n"/>
@@ -2997,8 +3009,9 @@
         </is>
       </c>
       <c r="L13" s="40" t="n"/>
-      <c r="M13" s="41" t="n">
-        <v>6032000</v>
+      <c r="M13" s="41">
+        <f>P13*1000*8</f>
+        <v/>
       </c>
       <c r="N13" s="42" t="n"/>
       <c r="O13" s="43" t="n"/>
@@ -3096,7 +3109,7 @@
       </c>
       <c r="AL13" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the aging Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="AM13" s="40" t="n"/>
@@ -3153,7 +3166,7 @@
       </c>
       <c r="F14" s="38" t="inlineStr">
         <is>
-          <t>Ernest Rufus, Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
+          <t>Ernest Rufus, Senior Manager, Capital Projects (Vicksburg role to confirm)</t>
         </is>
       </c>
       <c r="G14" s="36" t="inlineStr">
@@ -3174,8 +3187,9 @@
         </is>
       </c>
       <c r="L14" s="40" t="n"/>
-      <c r="M14" s="41" t="n">
-        <v>6032000</v>
+      <c r="M14" s="41">
+        <f>P14*1000*8</f>
+        <v/>
       </c>
       <c r="N14" s="42" t="n"/>
       <c r="O14" s="43" t="n"/>
@@ -3268,7 +3282,7 @@
       </c>
       <c r="AK14" s="38" t="inlineStr">
         <is>
-          <t>Engage TSL/TIC procurement and Ernest Rufus immediately.</t>
+          <t>Engage TSL/TIC procurement now; confirm Ernest Rufus covers Vicksburg (confirmed on Delta Blues only) and ask for the named project buyer.</t>
         </is>
       </c>
       <c r="AL14" s="38" t="inlineStr">
@@ -3341,8 +3355,9 @@
         </is>
       </c>
       <c r="L15" s="40" t="n"/>
-      <c r="M15" s="41" t="n">
-        <v>7344000</v>
+      <c r="M15" s="41">
+        <f>P15*1000*8</f>
+        <v/>
       </c>
       <c r="N15" s="42" t="n"/>
       <c r="O15" s="43" t="n"/>
@@ -3510,13 +3525,14 @@
         </is>
       </c>
       <c r="L16" s="40" t="n"/>
-      <c r="M16" s="41" t="n">
-        <v>12000000</v>
+      <c r="M16" s="41">
+        <f>P16*1000*8</f>
+        <v/>
       </c>
       <c r="N16" s="42" t="n"/>
       <c r="O16" s="43" t="n"/>
       <c r="P16" s="44" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="Q16" s="44" t="n">
         <v>500</v>
@@ -3611,7 +3627,7 @@
       </c>
       <c r="AL16" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,000,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*RPBD* OVERVIEW: ~1,508 MW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,064,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="AM16" s="40" t="n"/>
@@ -3679,8 +3695,9 @@
         </is>
       </c>
       <c r="L17" s="40" t="n"/>
-      <c r="M17" s="41" t="n">
-        <v>6560000</v>
+      <c r="M17" s="41">
+        <f>P17*1000*8</f>
+        <v/>
       </c>
       <c r="N17" s="42" t="n"/>
       <c r="O17" s="43" t="n"/>
@@ -14622,9 +14639,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="K7" s="39" t="n"/>
+      <c r="K7" s="36" t="inlineStr">
+        <is>
+          <t>+1 312-582-1094</t>
+        </is>
+      </c>
       <c r="L7" s="39" t="n"/>
-      <c r="M7" s="39" t="n"/>
+      <c r="M7" s="36" t="inlineStr">
+        <is>
+          <t>dbirmingham@invenergy.com</t>
+        </is>
+      </c>
       <c r="N7" s="39" t="n"/>
       <c r="O7" s="37" t="inlineStr">
         <is>
@@ -14670,8 +14695,9 @@
           <t>IPP</t>
         </is>
       </c>
-      <c r="AI7" s="49" t="n">
-        <v>9624000</v>
+      <c r="AI7" s="49">
+        <f>AL7*1000*8</f>
+        <v/>
       </c>
       <c r="AJ7" s="50" t="n"/>
       <c r="AK7" s="45" t="n">
@@ -14970,8 +14996,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI8" s="49" t="n">
-        <v>9720000</v>
+      <c r="AI8" s="49">
+        <f>AL8*1000*8</f>
+        <v/>
       </c>
       <c r="AJ8" s="50" t="n"/>
       <c r="AK8" s="45" t="n">
@@ -15262,8 +15289,9 @@
           <t>IPP</t>
         </is>
       </c>
-      <c r="AI9" s="49" t="n">
-        <v>3520000</v>
+      <c r="AI9" s="49">
+        <f>AL9*1000*8</f>
+        <v/>
       </c>
       <c r="AJ9" s="50" t="n"/>
       <c r="AK9" s="45" t="n">
@@ -15550,8 +15578,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI10" s="49" t="n">
-        <v>3862400</v>
+      <c r="AI10" s="49">
+        <f>AL10*1000*8</f>
+        <v/>
       </c>
       <c r="AJ10" s="50" t="n"/>
       <c r="AK10" s="45" t="n">
@@ -15846,8 +15875,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI11" s="49" t="n">
-        <v>3568000</v>
+      <c r="AI11" s="49">
+        <f>AL11*1000*8</f>
+        <v/>
       </c>
       <c r="AJ11" s="50" t="n"/>
       <c r="AK11" s="45" t="n">
@@ -16138,8 +16168,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI12" s="49" t="n">
-        <v>10880000</v>
+      <c r="AI12" s="49">
+        <f>AL12*1000*8</f>
+        <v/>
       </c>
       <c r="AJ12" s="50" t="n"/>
       <c r="AK12" s="45" t="n">
@@ -16442,8 +16473,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI13" s="49" t="n">
-        <v>6032000</v>
+      <c r="AI13" s="49">
+        <f>AL13*1000*8</f>
+        <v/>
       </c>
       <c r="AJ13" s="50" t="n"/>
       <c r="AK13" s="45" t="n">
@@ -16644,7 +16676,7 @@
       </c>
       <c r="CI13" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the 1950s-era Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
+          <t>*RPBD* OVERVIEW: 754 MW natural-gas COMBINED-CYCLE plant ('Superpower Mississippi'), replacing the aging Gerald Andrus Steam Electric Station; serves ~385,000 homes across Entergy Mississippi's 45 counties. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine (per GEM), HRSG (modules being lifted May 2026), steam turbine; dual-fuel, hydrogen-blend capable. SITE: BROWNFIELD-ADJACENT - new footprint within ~1 mile of the Andrus plant, 85 Stokes King Road, Greenville, Washington County; reuses Andrus transmission and gas infrastructure (acreage not published). INTERCONNECTION: ~1.5 miles of new transmission line to the existing substation next to Andrus; new Delta Blues substation. OWNERSHIP/EPC: Entergy Mississippi; EPC TSL Power Partners (Kiewit Power Constructors / TIC; Kiewit 200+ on site). Groundbreaking Nov 2024; COD May 2028; ~$1.2B. INVESTMENT: Total project investment ~$1.2B (Entergy); Yes Energy $651M not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus ~1.5 mi transmission line conductor and substation cable. Status: above-ground erection since May 2026 - bulk cable likely ordered. Ref: https://www.power-eng.com/gas/combined-cycle/entergy-mississippi-breaks-ground-on-754-mw-combined-cycle-plant/ | https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction | https://www.gem.wiki/Delta_Blues_Advanced_Power_Station | https://opcgis.deq.state.ms.us/ensearchonline/ai_info.aspx?ai=86260</t>
         </is>
       </c>
       <c r="CJ13" s="38" t="inlineStr">
@@ -16687,7 +16719,7 @@
       <c r="G14" s="40" t="n"/>
       <c r="H14" s="38" t="inlineStr">
         <is>
-          <t>Senior Manager, Capital Projects (Delta Blues &amp; Vicksburg)</t>
+          <t>Senior Manager, Capital Projects (Vicksburg role to confirm)</t>
         </is>
       </c>
       <c r="I14" s="37" t="inlineStr">
@@ -16748,8 +16780,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI14" s="49" t="n">
-        <v>6032000</v>
+      <c r="AI14" s="49">
+        <f>AL14*1000*8</f>
+        <v/>
       </c>
       <c r="AJ14" s="50" t="n"/>
       <c r="AK14" s="45" t="n">
@@ -16931,7 +16964,7 @@
       </c>
       <c r="CH14" s="38" t="inlineStr">
         <is>
-          <t>Engage TSL/TIC procurement and Ernest Rufus immediately.</t>
+          <t>Engage TSL/TIC procurement now; confirm Ernest Rufus covers Vicksburg (confirmed on Delta Blues only) and ask for the named project buyer.</t>
         </is>
       </c>
       <c r="CI14" s="38" t="inlineStr">
@@ -17040,8 +17073,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI15" s="49" t="n">
-        <v>7344000</v>
+      <c r="AI15" s="49">
+        <f>AL15*1000*8</f>
+        <v/>
       </c>
       <c r="AJ15" s="50" t="n"/>
       <c r="AK15" s="45" t="n">
@@ -17334,15 +17368,16 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI16" s="49" t="n">
-        <v>12000000</v>
+      <c r="AI16" s="49">
+        <f>AL16*1000*8</f>
+        <v/>
       </c>
       <c r="AJ16" s="50" t="n"/>
       <c r="AK16" s="45" t="n">
         <v>47088</v>
       </c>
       <c r="AL16" s="44" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="AM16" s="44" t="n">
         <v>500</v>
@@ -17524,12 +17559,12 @@
       </c>
       <c r="CI16" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: ~1.5 GW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,000,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
+          <t>*RPBD* OVERVIEW: ~1,508 MW natural-gas COMBINED-CYCLE station (two units) built to power Meta's Hyperion AI data-center campus; Meta pays the plants' full revenue requirement for 15 years. Air permit name 'Titanium Advanced Power Station'. ~7 more Hyperion plants (~5.2 GW) proposed, LPSC vote Dec 2026. TECHNOLOGY &amp; EQUIPMENT: 2x 1x1 combined-cycle blocks - Mitsubishi Power M501JAC gas turbines, HRSGs, steam turbines (~754-780 MW each); hydrogen-capable (30% co-fire), carbon-capture ready; IMI valve package (Sep 2026). SITE: GREENFIELD - former agricultural land on the state-owned Franklin Farms megasite (~1,400-2,250 acres total incl. Meta campus) along LA Hwy 183 near Holly Ridge, Richland Parish. INTERCONNECTION: Entergy 500 kV system - ~100 miles of new 500 kV lines (~$1.2B), eight new 230 kV lines, Sterlington 500 kV upgrades. OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC/Kiewit + Sargent &amp; Lundy) with Mitsubishi Power. LPSC approval Aug 2025; groundbreaking Dec 1, 2025; COD Dec 2028; ~$2.39B for both units. INVESTMENT: Total project investment ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony); est. W&amp;C value $12,064,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Separate opportunity: HV/500 kV transmission conductor and substation cable. Ref: https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation | https://www.ticus.com/entergy-program/ | https://www.gem.wiki/Franklin_Farms_power_station | https://www.datacenterdynamics.com/en/news/entergy-breaks-ground-on-two-natural-gas-plants-for-metas-2gw-data-center-in-richland-parish-louisiana/</t>
         </is>
       </c>
       <c r="CJ16" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). Est. W&amp;C value: $12,000,000 ($8/kW).</t>
+          <t>*RPBD* Total project investment: ~$2.39B (Franklin Farms 1 &amp; 2, LPSC testimony). Est. W&amp;C value: $12,064,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -17628,8 +17663,9 @@
           <t>IOU</t>
         </is>
       </c>
-      <c r="AI17" s="49" t="n">
-        <v>6560000</v>
+      <c r="AI17" s="49">
+        <f>AL17*1000*8</f>
+        <v/>
       </c>
       <c r="AJ17" s="50" t="n"/>
       <c r="AK17" s="45" t="n">
@@ -35723,7 +35759,7 @@
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $5,040,000</t>
+          <t>MV power cable: 42% of W&amp;C = $5,066,880</t>
         </is>
       </c>
     </row>
@@ -35740,7 +35776,7 @@
       </c>
       <c r="C47" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $5,160,000</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $5,187,520</t>
         </is>
       </c>
     </row>
@@ -35757,7 +35793,7 @@
       </c>
       <c r="C48" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $1,200,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $1,206,400</t>
         </is>
       </c>
     </row>
@@ -35774,7 +35810,7 @@
       </c>
       <c r="C49" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $600,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $603,200</t>
         </is>
       </c>
     </row>
@@ -44335,7 +44371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -44807,6 +44843,210 @@
       <c r="B39" s="55" t="inlineStr">
         <is>
           <t>https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>https://forestjunctionenergycenter.invenergy.com/news-and-resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>https://apps.dnr.wi.gov/warp_ext/am_permittracking2.aspx?id=38822</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-texas-orange-county-advanced-power-station-begins-delivering-reliable-power-to-southeast-texas</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B43" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B44" s="55" t="inlineStr">
+        <is>
+          <t>https://hub.vistracorp.com/vistra-announces-plans-to-build-new-dispatchable-generation-in-texas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B45" s="55" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/how-do-we-source/ | https://vistracorp.com/supply-chain/faq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>https://www.southerncompany.com/contact-us.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B47" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
+          <t>https://s201.q4cdn.com/714390239/files/doc_presentations/2026/Jun/09/Entergy-2026-Investor-Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B49" s="55" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Vicksburg Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B51" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B52" s="55" t="inlineStr">
+        <is>
+          <t>https://sycamoreriverside.invenergy.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B53" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B54" s="55" t="inlineStr">
+        <is>
+          <t>https://s201.q4cdn.com/714390239/files/doc_presentations/2026/Jun/09/Entergy-2026-Investor-Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B55" s="55" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B56" s="55" t="inlineStr">
+        <is>
+          <t>https://s201.q4cdn.com/714390239/files/doc_presentations/2026/Jun/09/Entergy-2026-Investor-Day.pdf</t>
         </is>
       </c>
     </row>
@@ -44850,6 +45090,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44861,7 +45118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -44872,6 +45129,11 @@
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44915,6 +45177,31 @@
           <t>Confidence</t>
         </is>
       </c>
+      <c r="I1" s="53" t="inlineStr">
+        <is>
+          <t>Verified email</t>
+        </is>
+      </c>
+      <c r="J1" s="53" t="inlineStr">
+        <is>
+          <t>Verified phone</t>
+        </is>
+      </c>
+      <c r="K1" s="53" t="inlineStr">
+        <is>
+          <t>Contact note</t>
+        </is>
+      </c>
+      <c r="L1" s="53" t="inlineStr">
+        <is>
+          <t>Contact source</t>
+        </is>
+      </c>
+      <c r="M1" s="53" t="inlineStr">
+        <is>
+          <t>Checked on</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="54" t="inlineStr">
@@ -44953,6 +45240,31 @@
           <t>News quote</t>
         </is>
       </c>
+      <c r="I2" s="54" t="inlineStr">
+        <is>
+          <t>dbirmingham@invenergy.com</t>
+        </is>
+      </c>
+      <c r="J2" s="54" t="inlineStr">
+        <is>
+          <t>+1 312-582-1094</t>
+        </is>
+      </c>
+      <c r="K2" s="54" t="inlineStr">
+        <is>
+          <t>Published business contact; cross-project DNR record. Forest Junction role listed by developer.</t>
+        </is>
+      </c>
+      <c r="L2" s="56" t="inlineStr">
+        <is>
+          <t>https://apps.dnr.wi.gov/warp_ext/am_permittracking2.aspx?id=38822</t>
+        </is>
+      </c>
+      <c r="M2" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="54" t="inlineStr">
@@ -44991,6 +45303,19 @@
           <t>News quote</t>
         </is>
       </c>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="54" t="inlineStr">
@@ -45029,6 +45354,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="54" t="inlineStr">
@@ -45067,6 +45405,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L5" s="54" t="n"/>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="54" t="inlineStr">
@@ -45105,6 +45456,19 @@
           <t>Company website</t>
         </is>
       </c>
+      <c r="I6" s="54" t="n"/>
+      <c r="J6" s="54" t="n"/>
+      <c r="K6" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L6" s="54" t="n"/>
+      <c r="M6" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="54" t="inlineStr">
@@ -45147,6 +45511,19 @@
           <t>Official website</t>
         </is>
       </c>
+      <c r="I7" s="54" t="n"/>
+      <c r="J7" s="54" t="n"/>
+      <c r="K7" s="54" t="inlineStr">
+        <is>
+          <t>Original media line not independently reconfirmed; not a project procurement number.</t>
+        </is>
+      </c>
+      <c r="L7" s="54" t="n"/>
+      <c r="M7" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="54" t="inlineStr">
@@ -45185,6 +45562,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I8" s="54" t="n"/>
+      <c r="J8" s="54" t="n"/>
+      <c r="K8" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L8" s="54" t="n"/>
+      <c r="M8" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="54" t="inlineStr">
@@ -45223,6 +45613,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L9" s="54" t="n"/>
+      <c r="M9" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="54" t="inlineStr">
@@ -45261,6 +45664,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L10" s="54" t="n"/>
+      <c r="M10" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="54" t="inlineStr">
@@ -45299,6 +45715,19 @@
           <t>Company website - indirect</t>
         </is>
       </c>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="54" t="inlineStr">
+        <is>
+          <t>Original source concerns Plant Barry; Yates assignment NOT verified.</t>
+        </is>
+      </c>
+      <c r="L11" s="54" t="n"/>
+      <c r="M11" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="54" t="inlineStr">
@@ -45337,6 +45766,19 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I12" s="54" t="n"/>
+      <c r="J12" s="54" t="n"/>
+      <c r="K12" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L12" s="54" t="n"/>
+      <c r="M12" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="54" t="inlineStr">
@@ -45375,6 +45817,19 @@
           <t>News</t>
         </is>
       </c>
+      <c r="I13" s="54" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="54" t="inlineStr">
@@ -45413,6 +45868,19 @@
           <t>Regulatory document</t>
         </is>
       </c>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="54" t="inlineStr">
@@ -45455,6 +45923,19 @@
           <t>Regulatory document</t>
         </is>
       </c>
+      <c r="I15" s="54" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="54" t="inlineStr">
@@ -45493,6 +45974,19 @@
           <t>Org website</t>
         </is>
       </c>
+      <c r="I16" s="54" t="n"/>
+      <c r="J16" s="54" t="n"/>
+      <c r="K16" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L16" s="54" t="n"/>
+      <c r="M16" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="54" t="inlineStr">
@@ -45531,6 +46025,19 @@
           <t>LinkedIn - verify</t>
         </is>
       </c>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="54" t="inlineStr">
+        <is>
+          <t>LinkedIn-derived suggestion; current procurement assignment not independently confirmed.</t>
+        </is>
+      </c>
+      <c r="L17" s="54" t="n"/>
+      <c r="M17" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="54" t="inlineStr">
@@ -45573,6 +46080,31 @@
           <t>Official website</t>
         </is>
       </c>
+      <c r="I18" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J18" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K18" s="54" t="inlineStr">
+        <is>
+          <t>Shared supplier support; not a project buyer.</t>
+        </is>
+      </c>
+      <c r="L18" s="56" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="M18" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="54" t="inlineStr">
@@ -45611,6 +46143,19 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I19" s="54" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L19" s="54" t="n"/>
+      <c r="M19" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="54" t="inlineStr">
@@ -45649,6 +46194,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I20" s="54" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L20" s="54" t="n"/>
+      <c r="M20" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
@@ -45687,6 +46245,19 @@
           <t>News quote</t>
         </is>
       </c>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="54" t="inlineStr">
@@ -45725,6 +46296,19 @@
           <t>LinkedIn - verify</t>
         </is>
       </c>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="inlineStr">
+        <is>
+          <t>Talent acquisition is not a procurement contact; project purchasing role not confirmed.</t>
+        </is>
+      </c>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="54" t="inlineStr">
@@ -45763,6 +46347,19 @@
           <t>Official blog</t>
         </is>
       </c>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="inlineStr">
+        <is>
+          <t>Entergy confirms Ernest Rufus as senior manager, capital projects on Delta Blues; direct email/phone not found.</t>
+        </is>
+      </c>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="54" t="inlineStr">
@@ -45805,6 +46402,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="54" t="inlineStr">
@@ -45840,7 +46450,20 @@
       </c>
       <c r="H25" s="54" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>News - Vicksburg role to confirm (Entergy confirms Delta Blues only)</t>
+        </is>
+      </c>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="54" t="inlineStr">
+        <is>
+          <t>Delta Blues role confirmed; Vicksburg assignment NOT independently verified.</t>
+        </is>
+      </c>
+      <c r="L25" s="54" t="n"/>
+      <c r="M25" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -45881,6 +46504,19 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="54" t="inlineStr">
@@ -45919,6 +46555,31 @@
           <t>News quote</t>
         </is>
       </c>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>drunyan@invenergy.com</t>
+        </is>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>+1 281-831-9568</t>
+        </is>
+      </c>
+      <c r="K27" s="54" t="inlineStr">
+        <is>
+          <t>Published Invenergy business contact; Sycamore-specific buying authority unconfirmed.</t>
+        </is>
+      </c>
+      <c r="L27" s="56" t="inlineStr">
+        <is>
+          <t>https://apps.dnr.wi.gov/warp_ext/am_permittracking2.aspx?id=38822</t>
+        </is>
+      </c>
+      <c r="M27" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="54" t="inlineStr">
@@ -45957,6 +46618,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="54" t="inlineStr">
@@ -45995,6 +46669,19 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L29" s="54" t="n"/>
+      <c r="M29" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="54" t="inlineStr">
@@ -46033,6 +46720,19 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I30" s="54" t="n"/>
+      <c r="J30" s="54" t="n"/>
+      <c r="K30" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L30" s="54" t="n"/>
+      <c r="M30" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="54" t="inlineStr">
@@ -46071,6 +46771,19 @@
           <t>Company website</t>
         </is>
       </c>
+      <c r="I31" s="54" t="n"/>
+      <c r="J31" s="54" t="n"/>
+      <c r="K31" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L31" s="54" t="n"/>
+      <c r="M31" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="54" t="inlineStr">
@@ -46109,6 +46822,27 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I32" s="54" t="inlineStr">
+        <is>
+          <t>npress1@entergy.com</t>
+        </is>
+      </c>
+      <c r="J32" s="54" t="n"/>
+      <c r="K32" s="54" t="inlineStr">
+        <is>
+          <t>Historical business email: 2022 DOE report; reconfirm before use. Direct phone not found.</t>
+        </is>
+      </c>
+      <c r="L32" s="56" t="inlineStr">
+        <is>
+          <t>https://www.osti.gov/servlets/purl/1884860</t>
+        </is>
+      </c>
+      <c r="M32" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="54" t="inlineStr">
@@ -46147,6 +46881,19 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I33" s="54" t="n"/>
+      <c r="J33" s="54" t="n"/>
+      <c r="K33" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L33" s="54" t="n"/>
+      <c r="M33" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="54" t="inlineStr">
@@ -46185,6 +46932,19 @@
           <t>Org website</t>
         </is>
       </c>
+      <c r="I34" s="54" t="n"/>
+      <c r="J34" s="54" t="n"/>
+      <c r="K34" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L34" s="54" t="n"/>
+      <c r="M34" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="54" t="inlineStr">
@@ -46223,6 +46983,19 @@
           <t>Official website</t>
         </is>
       </c>
+      <c r="I35" s="54" t="n"/>
+      <c r="J35" s="54" t="n"/>
+      <c r="K35" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L35" s="54" t="n"/>
+      <c r="M35" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="54" t="inlineStr">
@@ -46265,6 +47038,23 @@
           <t>Official release</t>
         </is>
       </c>
+      <c r="I36" s="54" t="n"/>
+      <c r="J36" s="54" t="inlineStr">
+        <is>
+          <t>+1 504-576-4132</t>
+        </is>
+      </c>
+      <c r="K36" s="54" t="inlineStr">
+        <is>
+          <t>Media contact only; not procurement. Published media phone confirmed; original email not independently reconfirmed.</t>
+        </is>
+      </c>
+      <c r="L36" s="54" t="n"/>
+      <c r="M36" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="54" t="inlineStr">
@@ -46303,6 +47093,27 @@
           <t>Regulatory filing</t>
         </is>
       </c>
+      <c r="I37" s="54" t="inlineStr">
+        <is>
+          <t>npress1@entergy.com</t>
+        </is>
+      </c>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="54" t="inlineStr">
+        <is>
+          <t>Historical business email: 2022 DOE report; reconfirm before use. Direct phone not found.</t>
+        </is>
+      </c>
+      <c r="L37" s="56" t="inlineStr">
+        <is>
+          <t>https://www.osti.gov/servlets/purl/1884860</t>
+        </is>
+      </c>
+      <c r="M37" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="54" t="inlineStr">
@@ -46341,6 +47152,19 @@
           <t>Secondary source - verify</t>
         </is>
       </c>
+      <c r="I38" s="54" t="n"/>
+      <c r="J38" s="54" t="n"/>
+      <c r="K38" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L38" s="54" t="n"/>
+      <c r="M38" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="54" t="inlineStr">
@@ -46381,48 +47205,884 @@
       <c r="H39" s="54" t="inlineStr">
         <is>
           <t>Company website / customs record</t>
+        </is>
+      </c>
+      <c r="I39" s="54" t="n"/>
+      <c r="J39" s="54" t="n"/>
+      <c r="K39" s="54" t="inlineStr">
+        <is>
+          <t>Original lead suggestion; assignment/contact details not independently confirmed in this review.</t>
+        </is>
+      </c>
+      <c r="L39" s="54" t="n"/>
+      <c r="M39" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="54" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside</t>
+        </is>
+      </c>
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>Sycamore project team</t>
+        </is>
+      </c>
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t>Shared business route</t>
+        </is>
+      </c>
+      <c r="D40" s="54" t="inlineStr">
+        <is>
+          <t>Invenergy</t>
+        </is>
+      </c>
+      <c r="E40" s="54" t="inlineStr">
+        <is>
+          <t>Shared project contact</t>
+        </is>
+      </c>
+      <c r="F40" s="54" t="inlineStr">
+        <is>
+          <t>SycamoreRiverside@invenergy.com; +1 800-341-2319</t>
+        </is>
+      </c>
+      <c r="G40" s="56" t="inlineStr">
+        <is>
+          <t>https://sycamoreriverside.invenergy.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H40" s="54" t="inlineStr">
+        <is>
+          <t>Shared project contact</t>
+        </is>
+      </c>
+      <c r="I40" s="54" t="inlineStr">
+        <is>
+          <t>SycamoreRiverside@invenergy.com</t>
+        </is>
+      </c>
+      <c r="J40" s="54" t="inlineStr">
+        <is>
+          <t>+1 800-341-2319</t>
+        </is>
+      </c>
+      <c r="K40" s="54" t="inlineStr">
+        <is>
+          <t>Shared project contact</t>
+        </is>
+      </c>
+      <c r="L40" s="56" t="inlineStr">
+        <is>
+          <t>https://sycamoreriverside.invenergy.com/contact-us</t>
+        </is>
+      </c>
+      <c r="M40" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="54" t="inlineStr">
+        <is>
+          <t>Vast Sands / Permian Basin</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>Supply chain routing</t>
+        </is>
+      </c>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t>Shared business route</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>Vistra</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="inlineStr">
+        <is>
+          <t>Email: supply chain; phone: supplier diversity. Not CEO direct contact</t>
+        </is>
+      </c>
+      <c r="F41" s="54" t="inlineStr">
+        <is>
+          <t>SupplyChain@Vistracorp.com; +1 214-812-8000</t>
+        </is>
+      </c>
+      <c r="G41" s="56" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/how-do-we-source/ | https://vistracorp.com/supply-chain/faq/</t>
+        </is>
+      </c>
+      <c r="H41" s="54" t="inlineStr">
+        <is>
+          <t>Email: supply chain; phone: supplier diversity. Not CEO direct contact</t>
+        </is>
+      </c>
+      <c r="I41" s="54" t="inlineStr">
+        <is>
+          <t>SupplyChain@Vistracorp.com</t>
+        </is>
+      </c>
+      <c r="J41" s="54" t="inlineStr">
+        <is>
+          <t>+1 214-812-8000</t>
+        </is>
+      </c>
+      <c r="K41" s="54" t="inlineStr">
+        <is>
+          <t>Email: supply chain; phone: supplier diversity. Not CEO direct contact</t>
+        </is>
+      </c>
+      <c r="L41" s="56" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/how-do-we-source/ | https://vistracorp.com/supply-chain/faq/</t>
+        </is>
+      </c>
+      <c r="M41" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId46"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>Stephan Hardt | Power Generation — Verification • 29 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11 records reviewed • 9 have a published email + phone route (direct, shared project or supplier support); 2 still need a suitable contact pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Publication checks only; no calls or emails sent. Exact unsupported commissioning dates cleared. Close dates, cable values and buying windows remain sales assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="53" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>Verified status</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>Timing / precision</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>Capacity reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>Facts checked</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="inlineStr">
+        <is>
+          <t>Required follow-up</t>
+        </is>
+      </c>
+      <c r="G5" s="54" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="H5" s="54" t="inlineStr">
+        <is>
+          <t>Contact route</t>
+        </is>
+      </c>
+      <c r="I5" s="54" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J5" s="54" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>Forest Junction Energy Center</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Proposed / permitting</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>2031 target; no exact day confirmed</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>1203 MW retained; unit figure needs permit/EIA confirmation. Developer publishes 1.9 GW for Forest Junction + Union Depot together.</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>Invenergy proposes gas generation in Calumet County, Wisconsin. Developer timeline shows development 2025–2027, construction 2028–2031 and operation in 2031.</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>Confirm selected site, CPCN status, individual capacity, turbine count and transmission scope.</t>
+        </is>
+      </c>
+      <c r="G6" s="55" t="inlineStr">
+        <is>
+          <t>https://forestjunctionenergycenter.invenergy.com/news-and-resources</t>
+        </is>
+      </c>
+      <c r="H6" s="54" t="inlineStr">
+        <is>
+          <t>Daniel Birmingham — published business contact; Wisconsin DNR listing is for another Invenergy project</t>
+        </is>
+      </c>
+      <c r="I6" s="54" t="inlineStr">
+        <is>
+          <t>dbirmingham@invenergy.com</t>
+        </is>
+      </c>
+      <c r="J6" s="54" t="inlineStr">
+        <is>
+          <t>+1 312-582-1094</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>Orange County Advanced Power Station (OCAPS)</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-14 actual</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>1215 MW confirmed</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>Entergy Texas placed the 1,215 MW combined-cycle OCAPS facility in service on October 14, 2026.</t>
+        </is>
+      </c>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>Treat remaining sales as separately qualified maintenance/spares work; whole-plant cable estimate is not an open order.</t>
+        </is>
+      </c>
+      <c r="G7" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-texas-orange-county-advanced-power-station-begins-delivering-reliable-power-to-southeast-texas</t>
+        </is>
+      </c>
+      <c r="H7" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I7" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J7" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>FID announced; execution status to confirm</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>2028 input target; exact unit date unverified</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
+        <is>
+          <t>440 MW retained for unit I; owner confirms 860 MW for two new units combined. Do not sum two 440 MW estimates as the published total.</t>
+        </is>
+      </c>
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>Vistra announced final investment decision September 29, 2025 for two new Permian Basin gas units totaling 860 MW, expanding the site from 325 to 1,185 MW.</t>
+        </is>
+      </c>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>Resolve Vast Sands unit mapping, gross/net capacity and current construction/COD with developer.</t>
+        </is>
+      </c>
+      <c r="G8" s="55" t="inlineStr">
+        <is>
+          <t>https://hub.vistracorp.com/vistra-announces-plans-to-build-new-dispatchable-generation-in-texas/</t>
+        </is>
+      </c>
+      <c r="H8" s="54" t="inlineStr">
+        <is>
+          <t>Vistra supply chain email / supplier-diversity phone — shared routing, not Jim Burke</t>
+        </is>
+      </c>
+      <c r="I8" s="54" t="inlineStr">
+        <is>
+          <t>SupplyChain@Vistracorp.com</t>
+        </is>
+      </c>
+      <c r="J8" s="54" t="inlineStr">
+        <is>
+          <t>+1 214-812-8000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>Under construction per owner update</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>By end 2027 for all 3 units; Unit 9 day unverified</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>482.8 MW retained as input nameplate; owner release reports approximately 1300 MW across 3 units. Basis needs reconciliation.</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>Georgia Power confirms Unit 9 turbine/generator delivery in December 2025. Units 8–10 use Mitsubishi M501JAC simple-cycle turbines.</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>Confirm Unit 9 commissioning date and nameplate versus operating capacity; do not assume cable purchase status.</t>
+        </is>
+      </c>
+      <c r="G9" s="55" t="inlineStr">
+        <is>
+          <t>https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html</t>
+        </is>
+      </c>
+      <c r="H9" s="54" t="inlineStr">
+        <is>
+          <t>Not found — action required</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>Ironwood Power Station</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Groundbreaking confirmed</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>2028 owner planning target</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>446 MW owner figure; EPC page rounds to 400 MW</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>Entergy Arkansas broke ground August 20, 2026 on Ironwood, a 446 MW simple-cycle plant at the existing Lake Catherine site.</t>
+        </is>
+      </c>
+      <c r="F10" s="54" t="inlineStr">
+        <is>
+          <t>Request project procurement contact and remaining electrical packages through the TSL vendor route.</t>
+        </is>
+      </c>
+      <c r="G10" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-arkansas-breaks-ground-on-ironwood-power-station</t>
+        </is>
+      </c>
+      <c r="H10" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I10" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J10" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>EPC awarded; construction planned/underway</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>2028 target; exact quarter/day unverified</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>1360 MW confirmed</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>Zachry announced the EPC award August 6, 2025 for Duke Energy’s 1,360 MW, 2x1 Person County CC1 at Roxboro.</t>
+        </is>
+      </c>
+      <c r="F11" s="54" t="inlineStr">
+        <is>
+          <t>Use Zachry procurement registration; named buyer email/phone still required. Confirm current bid schedule.</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/press-releases/Duke_Energy_Awards_EPC_Contract_for_the_first_Person_County_Combined_Cycle_Project_to_Zachry_Group.html</t>
+        </is>
+      </c>
+      <c r="H11" s="54" t="inlineStr">
+        <is>
+          <t>Not found — action required</t>
+        </is>
+      </c>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>Delta Blues Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Construction confirmed</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>2028 target; exact month/day unverified</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>754 MW confirmed</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>Entergy’s May 19, 2026 update confirms HRSG erection and combustion-turbine delivery at Delta Blues in Greenville. Ernest Rufus is identified as senior manager, capital projects.</t>
+        </is>
+      </c>
+      <c r="F12" s="54" t="inlineStr">
+        <is>
+          <t>DONE: 1950s Andrus claim removed. Note: construction milestones do not prove cable packages are already purchased.</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/blog/delta-blues-reaches-important-milestone-in-construction</t>
+        </is>
+      </c>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I12" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>Vicksburg Advanced Power Station</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Construction project</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>August 2028 expected completion; no exact day</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>754 MW confirmed</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>Entergy plans Vicksburg Advanced Power Station at the former Baxter Wilson site in Warren County. Baxter Wilson retired in 2022.</t>
+        </is>
+      </c>
+      <c r="F13" s="54" t="inlineStr">
+        <is>
+          <t>Confirm Ernest Rufus covers Vicksburg (Delta Blues role confirmed only); request named project buyer.</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergymississippi.com/generation/vicksburg</t>
+        </is>
+      </c>
+      <c r="H13" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I13" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>Sycamore Riverside Energy Center</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Proposed acquisition; regulatory decision pending</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>March 2029 transfer target; subject to completion/approval</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>918 MW confirmed in acquisition announcement</t>
+        </is>
+      </c>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>I&amp;M announced a request to acquire Invenergy’s Sycamore Riverside facility on completion, subject to IURC approval.</t>
+        </is>
+      </c>
+      <c r="F14" s="54" t="inlineStr">
+        <is>
+          <t>Do not treat acquisition as approved or closed. Verify Niland’s current project assignment and procurement scope.</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="inlineStr">
+        <is>
+          <t>https://www.aep.com/news/stories/view/11850/</t>
+        </is>
+      </c>
+      <c r="H14" s="54" t="inlineStr">
+        <is>
+          <t>Sycamore project team — shared, not John Niland</t>
+        </is>
+      </c>
+      <c r="I14" s="54" t="inlineStr">
+        <is>
+          <t>SycamoreRiverside@invenergy.com</t>
+        </is>
+      </c>
+      <c r="J14" s="54" t="inlineStr">
+        <is>
+          <t>+1 800-341-2319</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>Franklin Farms Power Station (Units 1 &amp; 2)</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Groundbreaking confirmed</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>Late 2028 owner target</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>Changed 1500 rounded to 1508 MW planning/EPC total for two units</t>
+        </is>
+      </c>
+      <c r="E15" s="54" t="inlineStr">
+        <is>
+          <t>Entergy Louisiana broke ground December 1, 2025 on Franklin Farms in Richland Parish. Two combined-cycle units support system growth including Meta demand.</t>
+        </is>
+      </c>
+      <c r="F15" s="54" t="inlineStr">
+        <is>
+          <t>DONE: 1,508 MW used. Confirm land ownership and electrical package status.</t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergy.com/news/entergy-louisiana-breaks-ground-on-new-state-of-the-art-generation-facilities-to-power-reliability-growth-and-innovation</t>
+        </is>
+      </c>
+      <c r="H15" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I15" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="54" t="inlineStr">
+        <is>
+          <t>Waterford 5 Power Station</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Site preparation; main construction scheduled</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>2029 owner target; June date not substantiated</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t>Changed 820 input nameplate to 754 MW owner planning basis; reconcile gross/net before technical sizing</t>
+        </is>
+      </c>
+      <c r="E16" s="54" t="inlineStr">
+        <is>
+          <t>Owner locates Waterford 5 in Taft, St. Charles Parish. Site preparation began November 2025; construction is scheduled for late 2026 with completion in 2029.</t>
+        </is>
+      </c>
+      <c r="F16" s="54" t="inlineStr">
+        <is>
+          <t>Owner location takes precedence over conflicting EPC page label (Big Cajun/Jarreau). Waterford 6 remains a separate project.</t>
+        </is>
+      </c>
+      <c r="G16" s="55" t="inlineStr">
+        <is>
+          <t>https://www.entergylouisiana.com/waterford5-6</t>
+        </is>
+      </c>
+      <c r="H16" s="54" t="inlineStr">
+        <is>
+          <t>Entergy supplier support — shared, not named lead</t>
+        </is>
+      </c>
+      <c r="I16" s="54" t="inlineStr">
+        <is>
+          <t>esupplier@entergy.com</t>
+        </is>
+      </c>
+      <c r="J16" s="54" t="inlineStr">
+        <is>
+          <t>+1 844-387-9675</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2018,9 +2018,11 @@
         <v>48213</v>
       </c>
       <c r="X7" s="45" t="n">
-        <v>47299</v>
-      </c>
-      <c r="Y7" s="46" t="n"/>
+        <v>48395</v>
+      </c>
+      <c r="Y7" s="45" t="n">
+        <v>47483</v>
+      </c>
       <c r="Z7" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2073,7 +2075,7 @@
       </c>
       <c r="AJ7" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030 (award date set to COD-24 mo). EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="AK7" s="38" t="inlineStr">
@@ -2196,9 +2198,11 @@
         <v>46309</v>
       </c>
       <c r="X8" s="45" t="n">
-        <v>46507</v>
-      </c>
-      <c r="Y8" s="46" t="n"/>
+        <v>46491</v>
+      </c>
+      <c r="Y8" s="45" t="n">
+        <v>45944</v>
+      </c>
       <c r="Z8" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2251,7 +2255,7 @@
       </c>
       <c r="AJ8" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). New-build award passed; aftermarket/MRO opportunity (first spring outage ~Apr 2027 - estimate, not sourced). Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="AK8" s="38" t="inlineStr">
@@ -2364,9 +2368,11 @@
         <v>46874</v>
       </c>
       <c r="X9" s="45" t="n">
+        <v>47058</v>
+      </c>
+      <c r="Y9" s="45" t="n">
         <v>46418</v>
       </c>
-      <c r="Y9" s="46" t="n"/>
       <c r="Z9" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2419,7 +2425,7 @@
       </c>
       <c r="AJ9" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="AK9" s="38" t="inlineStr">
@@ -2532,9 +2538,11 @@
         <v>46568</v>
       </c>
       <c r="X10" s="45" t="n">
-        <v>46371</v>
-      </c>
-      <c r="Y10" s="46" t="n"/>
+        <v>46751</v>
+      </c>
+      <c r="Y10" s="45" t="n">
+        <v>46203</v>
+      </c>
       <c r="Z10" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2587,7 +2595,7 @@
       </c>
       <c r="AJ10" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium (award date set to COD-12 mo; already passed). Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="AK10" s="38" t="inlineStr">
@@ -2700,9 +2708,11 @@
         <v>47118</v>
       </c>
       <c r="X11" s="45" t="n">
+        <v>47299</v>
+      </c>
+      <c r="Y11" s="45" t="n">
         <v>46477</v>
       </c>
-      <c r="Y11" s="46" t="n"/>
       <c r="Z11" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2755,7 +2765,7 @@
       </c>
       <c r="AJ11" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="AK11" s="38" t="inlineStr">
@@ -2868,9 +2878,11 @@
         <v>47118</v>
       </c>
       <c r="X12" s="45" t="n">
+        <v>47299</v>
+      </c>
+      <c r="Y12" s="45" t="n">
         <v>46416</v>
       </c>
-      <c r="Y12" s="46" t="n"/>
       <c r="Z12" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -2923,7 +2935,7 @@
       </c>
       <c r="AJ12" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="AK12" s="38" t="inlineStr">
@@ -3044,9 +3056,11 @@
         <v>46874</v>
       </c>
       <c r="X13" s="45" t="n">
+        <v>47058</v>
+      </c>
+      <c r="Y13" s="45" t="n">
         <v>46356</v>
       </c>
-      <c r="Y13" s="46" t="n"/>
       <c r="Z13" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -3222,9 +3236,11 @@
         <v>46966</v>
       </c>
       <c r="X14" s="45" t="n">
+        <v>47150</v>
+      </c>
+      <c r="Y14" s="45" t="n">
         <v>46371</v>
       </c>
-      <c r="Y14" s="46" t="n"/>
       <c r="Z14" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -3392,9 +3408,11 @@
         <v>47208</v>
       </c>
       <c r="X15" s="45" t="n">
+        <v>47391</v>
+      </c>
+      <c r="Y15" s="45" t="n">
         <v>46568</v>
       </c>
-      <c r="Y15" s="46" t="n"/>
       <c r="Z15" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -3447,7 +3465,7 @@
       </c>
       <c r="AJ15" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="AK15" s="38" t="inlineStr">
@@ -3562,9 +3580,11 @@
         <v>47088</v>
       </c>
       <c r="X16" s="45" t="n">
+        <v>47270</v>
+      </c>
+      <c r="Y16" s="45" t="n">
         <v>46416</v>
       </c>
-      <c r="Y16" s="46" t="n"/>
       <c r="Z16" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -3617,7 +3637,7 @@
       </c>
       <c r="AJ16" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="AK16" s="38" t="inlineStr">
@@ -3732,9 +3752,11 @@
         <v>47270</v>
       </c>
       <c r="X17" s="45" t="n">
+        <v>47453</v>
+      </c>
+      <c r="Y17" s="45" t="n">
         <v>46660</v>
       </c>
-      <c r="Y17" s="46" t="n"/>
       <c r="Z17" s="37" t="inlineStr">
         <is>
           <t>Power Generation</t>
@@ -3787,7 +3809,7 @@
       </c>
       <c r="AJ17" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="AK17" s="38" t="inlineStr">
@@ -14882,7 +14904,7 @@
       <c r="CF7" s="39" t="n"/>
       <c r="CG7" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030. EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: CPCN filing expected fall 2026 (PSC docket 5-CE-162), construction start Q4 2027, COD Dec 2031 -&gt; BOP cable likely released in phases Q4 2028-Q2 2030 (award date set to COD-24 mo). EPC not named (Invenergy has used Kiewit elsewhere - unconfirmed). We Energies (Brendan Conway, spokesperson) may acquire; precedent: PSC approved Invenergy Red Oak Ridge/Foundry Ridge for We Energies Oct 15, 2026. Yes Energy shows 2030 COD; public sources Dec 2031.</t>
         </is>
       </c>
       <c r="CH7" s="38" t="inlineStr">
@@ -15175,7 +15197,7 @@
       <c r="CF8" s="39" t="n"/>
       <c r="CG8" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). Close date = estimated first spring maintenance outage (MRO/spares) - estimate, not sourced. Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
+          <t>*RPBD* In service Oct 14, 2026 - new-build window passed (~2023-24). New-build award passed; aftermarket/MRO opportunity (first spring outage ~Apr 2027 - estimate, not sourced). Other contacts: David Borde (CEO, Entergy Texas); James Malone (Dir. Business Development, Sargent &amp; Lundy).</t>
         </is>
       </c>
       <c r="CH8" s="38" t="inlineStr">
@@ -15464,7 +15486,7 @@
       <c r="CF9" s="39" t="n"/>
       <c r="CG9" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: FID Sep 2025; $583M TEF loan (Jun 2026) with $172M drawn by 6/30/26 = heavy early spend; COD May/Jun 2028 -&gt; cable window Dec 2026-Jun 2027, early packages may already be placed. EPC/OEM not public. No project-level contact public - Jim Burke is exec-level only (quoted in releases). TCEQ NAPD for permit 178462 should list applicant contact (Luminant Generation Co).</t>
         </is>
       </c>
       <c r="CH9" s="38" t="inlineStr">
@@ -15761,7 +15783,7 @@
       <c r="CF10" s="39" t="n"/>
       <c r="CG10" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium. Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
+          <t>*RPBD* LOW PROBABILITY: Unit 8 COD Q4 2026, Unit 9 Q2 2027, Unit 10 Q3 2027 (Southern Q2 2026 10-Q). Bulk cable likely bought 2024-25 by Mitsubishi/B&amp;V consortium (award date set to COD-12 mo; already passed). Remaining: Unit 10 top-ups, change orders, spares. Other contacts: Cheryl Boddiford (SVP Mfg &amp; Supply Chain, Mitsubishi Power); Rick Janik (B&amp;V PM on Plant Barry Unit 8 - same EPC pairing, not confirmed for Yates). GA PSC docket 55931.</t>
         </is>
       </c>
       <c r="CH10" s="38" t="inlineStr">
@@ -16054,7 +16076,7 @@
       <c r="CF11" s="39" t="n"/>
       <c r="CG11" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: site construction Q2 2026-Q2 2028, groundbreaking Aug 20 2026, COD Q4 2028 -&gt; bulk cable after underground/foundations ~Q1-Q2 2027. Best new-buy opportunity. TSL procures in its own name; S&amp;L writes cable specs/BOMs. TSL address: 8900 Renner Blvd, Lenexa KS 66219. Other contacts: Laura Landreaux (CEO, Entergy AR); Louise Duncan (VP Power Plant Ops, Entergy AR); Jason Rees (Dir. Procurement, Entergy - LinkedIn, verify). Entergy supplier registration: esupplier@entergy.com.</t>
         </is>
       </c>
       <c r="CH11" s="38" t="inlineStr">
@@ -16359,7 +16381,7 @@
       <c r="CF12" s="39" t="n"/>
       <c r="CG12" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: Zachry EPC Aug 2025, groundbreaking Feb 13 2026, first GE Vernova GT on site Jul 23 2026, Zachry craft hiring from Jul 2026; COD Q4 2028 (SC ORS) -&gt; bulk MV/600V/tray bid likely now; act immediately. CC2 (Q4 2029, likely Zachry) -&gt; separate close ~12/15/2027. Other contacts: Ralph Biediger (EPC Group President, Zachry); Bill Norton (Duke spokesperson). Utility is Duke Energy Progress (not DEC).</t>
         </is>
       </c>
       <c r="CH12" s="38" t="inlineStr">
@@ -17254,7 +17276,7 @@
       <c r="CF15" s="39" t="n"/>
       <c r="CG15" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: Boldt lists construction Sep 2026-Feb 2029 (built at risk before IURC order expected end-2026); COD Mar 31 2029 -&gt; cable window Q1-Q3 2027; Invenergy/Boldt buy, not I&amp;M. Other contacts: Daniel Runyan (SVP Development, Invenergy); Steve Baker (President &amp; COO, I&amp;M); Timothy B. Gaul (Dir. Regulated Infrastructure Development, AEPSC); Timothy C. Kerns (Sterling Industrial - owner's engineer witness). PJM (not MISO), 918 MW SC (not 1,150 MW CC).</t>
         </is>
       </c>
       <c r="CH15" s="38" t="inlineStr">
@@ -17549,7 +17571,7 @@
       <c r="CF16" s="39" t="n"/>
       <c r="CG16" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: groundbreaking Dec 1 2025, COD Dec 2028; IMI valve order Sep 2026 says detailed engineering still active -&gt; cable window Dec 2026-Jun 2027, early MV/grounding packages possibly Q4 2026. EPC TSL Power Partners/Kiewit + Mitsubishi. Other contacts: Phillip May (CEO, Entergy LA); Carlos Ruiz (VP Power Development, Entergy); Jim Niemiec (VP &amp; Chief Supply Chain Officer, Entergy); media Brandon Scardigli 504-576-4132. Separate 500 kV transmission opportunity.</t>
         </is>
       </c>
       <c r="CH16" s="38" t="inlineStr">
@@ -17854,7 +17876,7 @@
       <c r="CF17" s="39" t="n"/>
       <c r="CG17" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* CLOSE DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
+          <t>*RPBD* AWARD (PO) DATE BASIS: site prep since Nov 2025, main construction late 2026, COD 2029 -&gt; cable window mid-2027-mid-2028. Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16 2026, same EPC) - pitch combined WF5+6 buy (~$3.75B program). Other contact: Michelle Berg (Entergy, parish council briefing - secondary source).</t>
         </is>
       </c>
       <c r="CH17" s="38" t="inlineStr">

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -148,7 +148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1982,7 +1985,7 @@
       </c>
       <c r="L7" s="40" t="n"/>
       <c r="M7" s="41">
-        <f>P7*1000*8</f>
+        <f>P7*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N7" s="42" t="n"/>
@@ -2164,7 +2167,7 @@
       </c>
       <c r="L8" s="40" t="n"/>
       <c r="M8" s="41">
-        <f>P8*1000*8</f>
+        <f>P8*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N8" s="42" t="n"/>
@@ -2334,7 +2337,7 @@
       </c>
       <c r="L9" s="40" t="n"/>
       <c r="M9" s="41">
-        <f>P9*1000*8</f>
+        <f>P9*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N9" s="42" t="n"/>
@@ -2504,7 +2507,7 @@
       </c>
       <c r="L10" s="40" t="n"/>
       <c r="M10" s="41">
-        <f>P10*1000*8</f>
+        <f>P10*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N10" s="42" t="n"/>
@@ -2674,7 +2677,7 @@
       </c>
       <c r="L11" s="40" t="n"/>
       <c r="M11" s="41">
-        <f>P11*1000*8</f>
+        <f>P11*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N11" s="42" t="n"/>
@@ -2844,7 +2847,7 @@
       </c>
       <c r="L12" s="40" t="n"/>
       <c r="M12" s="41">
-        <f>P12*1000*8</f>
+        <f>P12*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N12" s="42" t="n"/>
@@ -3022,7 +3025,7 @@
       </c>
       <c r="L13" s="40" t="n"/>
       <c r="M13" s="41">
-        <f>P13*1000*8</f>
+        <f>P13*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N13" s="42" t="n"/>
@@ -3202,7 +3205,7 @@
       </c>
       <c r="L14" s="40" t="n"/>
       <c r="M14" s="41">
-        <f>P14*1000*8</f>
+        <f>P14*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N14" s="42" t="n"/>
@@ -3372,7 +3375,7 @@
       </c>
       <c r="L15" s="40" t="n"/>
       <c r="M15" s="41">
-        <f>P15*1000*8</f>
+        <f>P15*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N15" s="42" t="n"/>
@@ -3544,7 +3547,7 @@
       </c>
       <c r="L16" s="40" t="n"/>
       <c r="M16" s="41">
-        <f>P16*1000*8</f>
+        <f>P16*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N16" s="42" t="n"/>
@@ -3716,13 +3719,13 @@
       </c>
       <c r="L17" s="40" t="n"/>
       <c r="M17" s="41">
-        <f>P17*1000*8</f>
+        <f>P17*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N17" s="42" t="n"/>
       <c r="O17" s="43" t="n"/>
       <c r="P17" s="44" t="n">
-        <v>820</v>
+        <v>754</v>
       </c>
       <c r="Q17" s="44" t="n">
         <v>500</v>
@@ -3819,7 +3822,7 @@
       </c>
       <c r="AL17" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,560,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="AM17" s="40" t="n"/>
@@ -3898,7 +3901,7 @@
       </c>
       <c r="L18" s="40" t="n"/>
       <c r="M18" s="41">
-        <f>P18*1000*8</f>
+        <f>P18*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N18" s="42" t="n"/>
@@ -4064,13 +4067,13 @@
       </c>
       <c r="L19" s="40" t="n"/>
       <c r="M19" s="41">
-        <f>P19*1000*8</f>
+        <f>P19*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N19" s="42" t="n"/>
       <c r="O19" s="43" t="n"/>
       <c r="P19" s="44" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="Q19" s="44" t="n">
         <v>345</v>
@@ -4232,7 +4235,7 @@
       </c>
       <c r="L20" s="40" t="n"/>
       <c r="M20" s="41">
-        <f>P20*1000*8</f>
+        <f>P20*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N20" s="42" t="n"/>
@@ -4398,7 +4401,7 @@
       </c>
       <c r="L21" s="40" t="n"/>
       <c r="M21" s="41">
-        <f>P21*1000*8</f>
+        <f>P21*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N21" s="42" t="n"/>
@@ -4564,13 +4567,13 @@
       </c>
       <c r="L22" s="40" t="n"/>
       <c r="M22" s="41">
-        <f>P22*1000*8</f>
+        <f>P22*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N22" s="42" t="n"/>
       <c r="O22" s="43" t="n"/>
       <c r="P22" s="44" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="Q22" s="43" t="n"/>
       <c r="R22" s="36" t="inlineStr">
@@ -4655,7 +4658,7 @@
       </c>
       <c r="AJ22" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Kiewit on site since Oct 2025, HRSG delivery Sep-Oct 2026, first GT set Oct 2026, first power late 2027/early 2028 -&gt; main power-block cable POs very likely placed; remaining releases/change orders through Q1 2027. Bigger long-tail: Amazon 36-building data-center campus plan (construction from Dec 2026, build-out to 2036; tabled by county Sep 2026). Other contacts: Brian Reinhart (VP, Kiewit Power Constructors); press@homercityredevelopment.com.</t>
+          <t>AWARD (PO) DATE BASIS: Kiewit on site since Oct 2025, HRSG delivery Sep-Oct 2026, first GT set Oct 2026, first power late 2027/early 2028 -&gt; main power-block cable POs very likely placed; remaining releases/change orders through Q1 2027. Bigger long-tail: Amazon 36-building data-center campus plan (construction from Dec 2026, build-out to 2036; tabled by county Sep 2026). Other contacts: Brian Reinhart (VP, Kiewit Power Constructors); Kiewit vendor inbox HomerCity.Info@Kiewit.com; press@homercityredevelopment.com.</t>
         </is>
       </c>
       <c r="AK22" s="38" t="inlineStr">
@@ -4730,7 +4733,7 @@
       </c>
       <c r="L23" s="40" t="n"/>
       <c r="M23" s="41">
-        <f>P23*1000*8</f>
+        <f>P23*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N23" s="42" t="n"/>
@@ -4823,7 +4826,7 @@
       </c>
       <c r="AJ23" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Gemma EPC Feb 2025, NTP Apr 2025, completion 2028 -&gt; cable window Dec 2026-Dec 2027, target ~Q1 2027. RISK: Xebec bio says project sold Apr 2026 (buyer unknown) - confirm owner/schedule. Luminant link only historical (old Sandow coal plant) - merge CRM Luminant duplicates. Other contact: Charles E. Collins IV (CEO, Gemma).</t>
+          <t>AWARD (PO) DATE BASIS: Gemma EPC Feb 2025, NTP Apr 2025, completion 2028 -&gt; cable window Dec 2026-Dec 2027, target ~Q1 2027. RISK: Xebec bio says project sold Apr 2026 (buyer unknown) - confirm owner/schedule. Luminant link only historical (old Sandow coal plant) - merge CRM Luminant duplicates. Other contacts: Tommy Hodges (COO, SL Energy Power Plant I LLC - tommyh@slenergyco.com, TCEQ 2025 filing); Charles E. Collins IV (CEO, Gemma).</t>
         </is>
       </c>
       <c r="AK23" s="38" t="inlineStr">
@@ -4908,13 +4911,13 @@
       </c>
       <c r="L24" s="40" t="n"/>
       <c r="M24" s="41">
-        <f>P24*1000*8</f>
+        <f>P24*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N24" s="42" t="n"/>
       <c r="O24" s="43" t="n"/>
       <c r="P24" s="44" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="Q24" s="43" t="n"/>
       <c r="R24" s="36" t="inlineStr">
@@ -4999,17 +5002,17 @@
       </c>
       <c r="AJ24" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: FID Nov 2025, groundbreaking Apr 2026, concrete pours mid-2026, COD 2028 -&gt; cable window open now, target Dec 2026-Mar 2027 (if COD 2027 per ENR, act immediately). EPC not public - top discovery item. CRM 579 MW not supported; sources say ~600-625 MW. Project contact: info@wolf-summit.com, (304) 576-8717. Other: Chris Cosby (CEO, ODEC); Bilal Khan (SMD, Blackstone).</t>
+          <t>AWARD (PO) DATE BASIS: FID Nov 2025, groundbreaking Apr 2026, concrete pours mid-2026, COD 2028 -&gt; cable window open now, target Dec 2026-Mar 2027 (if COD 2027 per ENR, act immediately). Delivered as Kindle EPCM with four principal contractors (names not published) - identify the electrical contractor. CRM 579 MW not supported; sources say ~600-625 MW (610 MW used). Project contact: info@wolf-summit.com, (304) 576-8717. Other: Chris Cosby (CEO, ODEC); Bilal Khan (SMD, Blackstone).</t>
         </is>
       </c>
       <c r="AK24" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC via Kindle Energy / project line (304) 576-8717 / WV Building Trades; position MV, control &amp; I&amp;C cable before bulk electrical buy.</t>
+          <t>Ask Kindle (EPCM) which principal contractor holds electrical; use Kindle Energy / project line (304) 576-8717 / WV Building Trades; position MV, control &amp; I&amp;C cable before bulk electrical buy.</t>
         </is>
       </c>
       <c r="AL24" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: ~600 MW natural-gas combined-cycle plant - West Virginia's first gas power plant - backed by $1.2B from Blackstone Energy Transition Partners, developed/operated by Kindle Energy, fully contracted to Old Dominion Electric Cooperative; ~500 construction jobs. TECHNOLOGY &amp; EQUIPMENT: GE Vernova 7HA.02 gas turbine in combined cycle (likely 1x1 with HRSG and steam turbine - inferred); GE Vernova Financial Services also financing. SITE: Pinnickinnick Hill area near Clarksburg/Wolf Summit, Harrison County (PILOT/lease Jan 2025); acreage not published. INTERCONNECTION: PJM grid sale to ODEC; substation/voltage not published. OWNERSHIP/STATUS: FID Nov 2025; groundbreaking Apr 22, 2026; site prep and roadwork Jun 2026; COD 2028. EPC not public. INVESTMENT: $1.2B. W&amp;C NEEDS (combined cycle): MV power cable to aux transformers, MV switchgear and large motors; 600V power &amp; TC-ER tray cable for HRSG/ST auxiliaries and BOP; shielded I&amp;C cable; bare copper grounding; switchyard control cable; building wire. Ref: https://www.businesswire.com/news/home/20260422186042/en/Kindle-Energy-Breaks-Ground-on-Blackstone-Backed-$1.2-Billion-Natural-Gas-Power-Generation-Facility-in-West-Virginia | https://wolf-summit.com/ | https://www.powermag.com/blackstone-investing-1-2-billion-for-600-mw-gas-fired-plant-in-west-virginia/</t>
+          <t>OVERVIEW: ~600 MW natural-gas combined-cycle plant - West Virginia's first gas power plant - backed by $1.2B from Blackstone Energy Transition Partners, developed/operated by Kindle Energy, fully contracted to Old Dominion Electric Cooperative; ~500 construction jobs. TECHNOLOGY &amp; EQUIPMENT: GE Vernova 7HA.02 gas turbine in combined cycle (likely 1x1 with HRSG and steam turbine - inferred); GE Vernova Financial Services also financing. SITE: Pinnickinnick Hill area near Clarksburg/Wolf Summit, Harrison County (PILOT/lease Jan 2025); acreage not published. INTERCONNECTION: PJM grid sale to ODEC; substation/voltage not published. OWNERSHIP/STATUS: FID Nov 2025; groundbreaking Apr 22, 2026; site prep and roadwork Jun 2026; COD 2028. Kindle EPCM with four principal contractors (not published). INVESTMENT: $1.2B. W&amp;C NEEDS (combined cycle): MV power cable to aux transformers, MV switchgear and large motors; 600V power &amp; TC-ER tray cable for HRSG/ST auxiliaries and BOP; shielded I&amp;C cable; bare copper grounding; switchyard control cable; building wire. Ref: https://www.businesswire.com/news/home/20260422186042/en/Kindle-Energy-Breaks-Ground-on-Blackstone-Backed-$1.2-Billion-Natural-Gas-Power-Generation-Facility-in-West-Virginia | https://wolf-summit.com/ | https://www.powermag.com/blackstone-investing-1-2-billion-for-600-mw-gas-fired-plant-in-west-virginia/</t>
         </is>
       </c>
       <c r="AM24" s="40" t="n"/>
@@ -5074,7 +5077,7 @@
       </c>
       <c r="L25" s="40" t="n"/>
       <c r="M25" s="41">
-        <f>P25*1000*8</f>
+        <f>P25*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N25" s="42" t="n"/>
@@ -5165,7 +5168,7 @@
       </c>
       <c r="AJ25" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: TEF loan closed Q3 2025, under construction, COD mid-2028 (NRG) -&gt; cable window Jul 2026-Jul 2027, target Nov 2026-Feb 2027. EPC not public (NRG GE Vernova/Kiewit venture is for 7HA units, not this Mitsubishi unit). CRM correction: 689 MW (NRG) vs 721 MW (state), Mitsubishi not GE, COD mid-2028 not 2029.</t>
+          <t>AWARD (PO) DATE BASIS: TEF loan closed Q3 2025, under construction, COD mid-2028 (NRG) -&gt; cable window Jul 2026-Jul 2027, target Nov 2026-Feb 2027. EPC not public (NRG GE Vernova/Kiewit venture is for 7HA units, not this Mitsubishi unit). CRM correction: 689 MW (NRG) vs 721 MW (state), Mitsubishi not GE, COD mid-2028 not 2029. Owner contact on 2026 TDLR project registration: Dudley D. Zahn (NRG / Cedar Bayou 5 LLC, 713-537-3290; email historical).</t>
         </is>
       </c>
       <c r="AK25" s="38" t="inlineStr">
@@ -5240,7 +5243,7 @@
       </c>
       <c r="L26" s="40" t="n"/>
       <c r="M26" s="41">
-        <f>P26*1000*8</f>
+        <f>P26*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N26" s="42" t="n"/>
@@ -5416,13 +5419,13 @@
       </c>
       <c r="L27" s="40" t="n"/>
       <c r="M27" s="41">
-        <f>P27*1000*8</f>
+        <f>P27*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N27" s="42" t="n"/>
       <c r="O27" s="43" t="n"/>
       <c r="P27" s="44" t="n">
-        <v>2060</v>
+        <v>2100</v>
       </c>
       <c r="Q27" s="44" t="n">
         <v>500</v>
@@ -5594,7 +5597,7 @@
       </c>
       <c r="L28" s="40" t="n"/>
       <c r="M28" s="41">
-        <f>P28*1000*8</f>
+        <f>P28*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N28" s="42" t="n"/>
@@ -5762,7 +5765,7 @@
       </c>
       <c r="L29" s="40" t="n"/>
       <c r="M29" s="41">
-        <f>P29*1000*8</f>
+        <f>P29*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N29" s="42" t="n"/>
@@ -5930,7 +5933,7 @@
       </c>
       <c r="L30" s="40" t="n"/>
       <c r="M30" s="41">
-        <f>P30*1000*8</f>
+        <f>P30*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N30" s="42" t="n"/>
@@ -6021,17 +6024,17 @@
       </c>
       <c r="AJ30" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: PPA signed Jun 2026, FID targeted end-2026, first power 2028 with phased ramp to ~2.67 GW (~2029-30) -&gt; award window Jun 2026-Jun 2027, target ~Q1 2027 (early-power Titan 130 units drive first packages). CRM COD 6/30/2027 corrected to 2028. EPC capacity reportedly reserved but unnamed. Other contacts: Jeff Gustavson (President, Chevron New Energies); Chris James (Founder &amp; CEO, Engine No. 1 / Joulent).</t>
+          <t>AWARD (PO) DATE BASIS: PPA signed Jun 2026, FID targeted end-2026, first power 2028 with phased ramp to ~2.67 GW (~2029-30) -&gt; award window Jun 2026-Jun 2027, target ~Q1 2027 (early-power Titan 130 units drive first packages). CRM COD 6/30/2027 corrected to 2028. Bechtel May 2026 Project Opportunity Report lists Kilby job 26776 with procurement (Birju Vasani, bvasani@bechtel.com) and subcontracts (Mark Bingaman, mabingam@bechtel.com, 713-235-1662) prequalification contacts; full NTP not confirmed. Full capacity 2031 per kilby.com. Other contacts: Jeff Gustavson (President, Chevron New Energies); Chris James (Founder &amp; CEO, Engine No. 1 / Joulent).</t>
         </is>
       </c>
       <c r="AK30" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC now and get specified before FID (Dec 2026); engage Chevron Power Solutions (Daniel Droog).</t>
+          <t>Prequalify with Bechtel now: Birju Vasani (procurement) and Mark Bingaman (subcontracts) for Kilby job 26776; get specified before FID (Dec 2026); engage Chevron Power Solutions (Daniel Droog).</t>
         </is>
       </c>
       <c r="AL30" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: ~2.67 GW (permit ~2.87 GW, possible scale to 5 GW) off-grid natural-gas power plant dedicated to Microsoft's up-to-2 GW Pecos AI data-center campus under a 20-year PPA (Jun 22, 2026); developed by Chevron (Energy Forge One) with Engine No. 1's Joulent and National Grid Ventures ($1.75B for 35% of Joulent). TECHNOLOGY &amp; EQUIPMENT: ~46 gas turbines - GE Vernova 7HA (7 reserved; permit analysis 5x 7HA.02) plus Solar Turbines Titan 350 (12) and Titan 130 (29, added Dec 2025 for early power); SCR and oxidation catalysts; combined/simple-cycle split not confirmed. SITE: GREENFIELD - Reeves County, SE of Pecos near Verhalen (Pecos TX 79780), off US-285 / FM 112; Microsoft campus ~7,000 acres (tracker, unverified). INTERCONNECTION: behind-the-meter, co-located with Microsoft campus (ERCOT region, no grid export disclosed). OWNERSHIP/STATUS: pre-FID; TCEQ air permit draft Apr 2026, public meeting Jun 10, 2026, pending; FID end-2026; first power 2028. INVESTMENT: ~$7-9B (analyst estimates). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Very large scope: 46 turbine packages plus data-center campus feeders. Ref: https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/181895-pls-english.pdf | https://blogs.microsoft.com/blog/2026/06/22/powering-the-next-wave-of-ai-expanding-capacity-with-our-new-datacenter-in-pecos/</t>
+          <t>OVERVIEW: ~2.67 GW (permit ~2.87 GW, possible scale to 5 GW) off-grid natural-gas power plant dedicated to Microsoft's up-to-2 GW Pecos AI data-center campus under a 20-year PPA (Jun 22, 2026); developed by Chevron (Energy Forge One) with Engine No. 1's Joulent and National Grid Ventures ($1.75B for 35% of Joulent). TECHNOLOGY &amp; EQUIPMENT: ~46 gas turbines - GE Vernova 7HA (7 reserved; permit analysis 5x 7HA.02) plus Solar Turbines Titan 350 (12) and Titan 130 (29, added Dec 2025 for early power); SCR and oxidation catalysts; combined/simple-cycle split not confirmed. SITE: GREENFIELD - Reeves County, SE of Pecos near Verhalen (Pecos TX 79780), off US-285 / FM 112; Microsoft campus ~7,000 acres (tracker, unverified). INTERCONNECTION: behind-the-meter, co-located with Microsoft campus (ERCOT region, no grid export disclosed). OWNERSHIP/STATUS: Energy Forge One LLC (Chevron/Joulent 50:50); EPC Bechtel (job 26776, procurement/early works); pre-FID; TCEQ air permit draft Apr 2026, public meeting Jun 10, 2026, pending; FID end-2026; first power 2028. INVESTMENT: ~$7-9B (analyst estimates). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Very large scope: 46 turbine packages plus data-center campus feeders. Ref: https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/181895-pls-english.pdf | https://blogs.microsoft.com/blog/2026/06/22/powering-the-next-wave-of-ai-expanding-capacity-with-our-new-datacenter-in-pecos/</t>
         </is>
       </c>
       <c r="AM30" s="40" t="n"/>
@@ -6096,13 +6099,13 @@
       </c>
       <c r="L31" s="40" t="n"/>
       <c r="M31" s="41">
-        <f>P31*1000*8</f>
+        <f>P31*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N31" s="42" t="n"/>
       <c r="O31" s="43" t="n"/>
       <c r="P31" s="44" t="n">
-        <v>2700</v>
+        <v>2550</v>
       </c>
       <c r="Q31" s="44" t="n">
         <v>345</v>
@@ -6189,7 +6192,7 @@
       </c>
       <c r="AJ31" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Frontier targets PJM approval mid-2028 and units online early 2029 with ~3-year construction -&gt; award window Mar 2027-Mar 2028, target ~Q2 2027. CRM COD 12/31/2030 updated to early 2029. Capacity conflicts: 2,550 MW export / 2.7 GW conversion + 900 MW Phase I = 3.6 GW. Aligned Data Centers broke ground on 2 GW Project Phoenix (~$10B) Sep 10, 2026 next door. Other contacts: David Franjoine (Founder &amp; CEO); Robert Zuchlewski (COO).</t>
+          <t>AWARD (PO) DATE BASIS: Frontier targets PJM approval mid-2028 and units online early 2029 with ~3-year construction -&gt; award window Mar 2027-Mar 2028, target ~Q2 2027. CRM COD 12/31/2030 updated to early 2029. Capacity conflicts: 2,550 MW export / 2.7 GW conversion + 900 MW Phase I = 3.6 GW. Aligned Data Centers broke ground on 2 GW Project Phoenix (~$10B) Sep 10, 2026 next door. Other contacts: David Franjoine (Founder &amp; CEO); Robert Zuchlewski (COO); Anthony Basil (Project Manager) and Peter Violante (Dir. Logistics &amp; BD) - Shippingport assignment not confirmed. Owner's engineer: Wood.</t>
         </is>
       </c>
       <c r="AK31" s="38" t="inlineStr">
@@ -6199,7 +6202,7 @@
       </c>
       <c r="AL31" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: conversion of the former 2.5-2.7 GW Bruce Mansfield coal plant (operated 1976-2019) into a natural-gas power station; Phase I adds ~900 MW new simple-cycle gas turbines + switchyard, Phase II (this record) converts the coal units (~2.7 GW) - up to ~3.6 GW total available to the park; EQT gas supply ~800 MMcf/d via new 7.2-mile National Fuel lateral. TECHNOLOGY &amp; EQUIPMENT: refurbish 3x existing GE steam turbine-generators (~850 MW each) re-powered with new gas turbines (repowering), new cooling towers, transformers and switchgear, on-site gas receiving station and 34.5 kV substation; coal handling demolished. SITE: BROWNFIELD - former Bruce Mansfield coal plant in the 660-acre Shippingport Industrial Park, Shippingport Borough, Beaver County; 14.5-acre gas fuel yard. Aligned Data Centers' 2 GW Project Phoenix campus under construction on site. INTERCONNECTION: PJM Cycle 01 (existing Bruce Mansfield 345 kV substation, Penn Power/FirstEnergy) plus behind-the-meter supply to the park. OWNERSHIP/STATUS: Frontier Group (self-performs engineering and construction); permitting underway; PJM approval mid-2028; units online early 2029; &gt;1,500 construction workers. INVESTMENT: &gt;$1.8B. W&amp;C NEEDS (repowered steam units + new GTs): MV power cable for new GT/aux transformers, cooling-tower fans and pumps, 34.5 kV substation feeders; 600V power &amp; TC-ER tray cable; shielded I&amp;C cable for new controls/DCS; grounding; switchyard control cable; data-center park MV distribution. Ref: https://frontier-companies.com/shippingport-power-station-featured-in-energy-oil-gas-magazine/ | https://www.businesswire.com/news/home/20250715103342/en/The-Frontier-Group-of-Companies-to-Transform-Bruce-Mansfield-Power-Plant-into-State-of-the-Art-Natural-Gas-Power-Plant-Supporting-Americas-Energy-Goals-and-Pennsylvanias-Economic-Growth | https://aligneddc.com/press-release/project-phoenix-data-center-shippingport-pa/</t>
+          <t>OVERVIEW: conversion of the former 2.5-2.7 GW Bruce Mansfield coal plant (operated 1976-2019) into a natural-gas power station; Phase I adds ~900 MW new simple-cycle gas turbines + switchyard, Phase II (this record) converts the coal units (~2.7 GW) - up to ~3.6 GW total available to the park; EQT gas supply ~800 MMcf/d via new 7.2-mile National Fuel lateral. TECHNOLOGY &amp; EQUIPMENT: refurbish 3x existing GE steam turbine-generators (~850 MW each) re-powered with new gas turbines (repowering), new cooling towers, transformers and switchgear, on-site gas receiving station and 34.5 kV substation; coal handling demolished. SITE: BROWNFIELD - former Bruce Mansfield coal plant in the 660-acre Shippingport Industrial Park, Shippingport Borough, Beaver County; 14.5-acre gas fuel yard. Aligned Data Centers' 2 GW Project Phoenix campus under construction on site. INTERCONNECTION: PJM Cycle 01 (existing Bruce Mansfield 345 kV substation, Penn Power/FirstEnergy) plus behind-the-meter supply to the park. OWNERSHIP/STATUS: Frontier Group (self-performs engineering and construction; Wood owner's engineer); permitting underway; PJM approval mid-2028; units online early 2029; &gt;1,500 construction workers. INVESTMENT: &gt;$1.8B. W&amp;C NEEDS (repowered steam units + new GTs): MV power cable for new GT/aux transformers, cooling-tower fans and pumps, 34.5 kV substation feeders; 600V power &amp; TC-ER tray cable; shielded I&amp;C cable for new controls/DCS; grounding; switchyard control cable; data-center park MV distribution. Ref: https://frontier-companies.com/shippingport-power-station-featured-in-energy-oil-gas-magazine/ | https://www.businesswire.com/news/home/20250715103342/en/The-Frontier-Group-of-Companies-to-Transform-Bruce-Mansfield-Power-Plant-into-State-of-the-Art-Natural-Gas-Power-Plant-Supporting-Americas-Energy-Goals-and-Pennsylvanias-Economic-Growth | https://aligneddc.com/press-release/project-phoenix-data-center-shippingport-pa/</t>
         </is>
       </c>
       <c r="AM31" s="40" t="n"/>
@@ -6240,9 +6243,9 @@
           <t>IPP</t>
         </is>
       </c>
-      <c r="F32" s="36" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="F32" s="38" t="inlineStr">
+        <is>
+          <t>Mark Siffin, CEO / project business contact</t>
         </is>
       </c>
       <c r="G32" s="36" t="inlineStr">
@@ -6264,7 +6267,7 @@
       </c>
       <c r="L32" s="40" t="n"/>
       <c r="M32" s="41">
-        <f>P32*1000*8</f>
+        <f>P32*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="N32" s="42" t="n"/>
@@ -6355,7 +6358,7 @@
       </c>
       <c r="AJ32" s="38" t="inlineStr">
         <is>
-          <t>LOW PROBABILITY: Chapter 313 agreement executed Dec 19, 2022 ($1B, 10 jobs); 2023 report showed no jobs/investment; no TCEQ air permit found; Maefield Development link not found publicly. Tentative award 6/30/2029. Same county has stronger leads: Project Kilby (Chevron/Microsoft), Prometheus Hyperscale + Istmo (1.5-2.5 GW, Aug 2026), LandBridge/NRG (1.1 GW), LandBridge/PowerBridge (2 GW).</t>
+          <t>LOW PROBABILITY: Chapter 313 agreement executed Dec 19, 2022 ($1B, 10 jobs); 2023 report showed no jobs/investment; no TCEQ air permit found. Maefield link established via Chapter 313 filings (2024 compliance report posted 2026 lists Mark Siffin). Tentative award 6/30/2029. Same county has stronger leads: Project Kilby (Chevron/Microsoft), Prometheus Hyperscale + Istmo (1.5-2.5 GW, Aug 2026), LandBridge/NRG (1.1 GW), LandBridge/PowerBridge (2 GW).</t>
         </is>
       </c>
       <c r="AK32" s="38" t="inlineStr">
@@ -6365,7 +6368,7 @@
       </c>
       <c r="AL32" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: proposed Phase 1 technology campus (~6 million sq ft of data centers and semiconductor manufacturing) in Reeves County powered by up to three on-site natural-gas trigeneration plants (power, heating, cooling) totaling ~1.54 GW with CO2 capture equipment. TECHNOLOGY &amp; EQUIPMENT: on-site gas trigeneration plants with CO2 capture (OEMs not published). SITE: GREENFIELD - Pecos-Barstow-Toyah ISD area, Reeves County (acreage not published). INTERCONNECTION: on-site / behind the meter. OWNERSHIP/STATUS: VPN 4420 LLC; Chapter 313 agreement Dec 2022; no reported investment or permits as of latest filings - likely stalled. INVESTMENT: $1B qualified investment (313). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Ref: https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993 | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-agmt.pdf</t>
+          <t>OVERVIEW: proposed Phase 1 technology campus (~6 million sq ft of data centers and semiconductor manufacturing) in Reeves County powered by up to three on-site natural-gas trigeneration plants (power, heating, cooling) totaling ~1.54 GW with CO2 capture equipment. TECHNOLOGY &amp; EQUIPMENT: on-site gas trigeneration plants with CO2 capture (OEMs not published). SITE: GREENFIELD - Pecos-Barstow-Toyah ISD area, Reeves County (acreage not published). INTERCONNECTION: on-site / behind the meter. OWNERSHIP/STATUS: VPN 4420 LLC / Maefield Development (Mark Siffin); Chapter 313 agreement Dec 2022; no reported investment or permits as of latest filings - likely stalled. INVESTMENT: $1B qualified investment (313). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Ref: https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993 | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-agmt.pdf</t>
         </is>
       </c>
       <c r="AM32" s="40" t="n"/>
@@ -16485,7 +16488,7 @@
         </is>
       </c>
       <c r="AI7" s="49">
-        <f>AL7*1000*8</f>
+        <f>AL7*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ7" s="50" t="n"/>
@@ -16786,7 +16789,7 @@
         </is>
       </c>
       <c r="AI8" s="49">
-        <f>AL8*1000*8</f>
+        <f>AL8*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ8" s="50" t="n"/>
@@ -17079,7 +17082,7 @@
         </is>
       </c>
       <c r="AI9" s="49">
-        <f>AL9*1000*8</f>
+        <f>AL9*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ9" s="50" t="n"/>
@@ -17368,7 +17371,7 @@
         </is>
       </c>
       <c r="AI10" s="49">
-        <f>AL10*1000*8</f>
+        <f>AL10*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ10" s="50" t="n"/>
@@ -17665,7 +17668,7 @@
         </is>
       </c>
       <c r="AI11" s="49">
-        <f>AL11*1000*8</f>
+        <f>AL11*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ11" s="50" t="n"/>
@@ -17958,7 +17961,7 @@
         </is>
       </c>
       <c r="AI12" s="49">
-        <f>AL12*1000*8</f>
+        <f>AL12*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ12" s="50" t="n"/>
@@ -18263,7 +18266,7 @@
         </is>
       </c>
       <c r="AI13" s="49">
-        <f>AL13*1000*8</f>
+        <f>AL13*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ13" s="50" t="n"/>
@@ -18570,7 +18573,7 @@
         </is>
       </c>
       <c r="AI14" s="49">
-        <f>AL14*1000*8</f>
+        <f>AL14*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ14" s="50" t="n"/>
@@ -18863,7 +18866,7 @@
         </is>
       </c>
       <c r="AI15" s="49">
-        <f>AL15*1000*8</f>
+        <f>AL15*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ15" s="50" t="n"/>
@@ -19158,7 +19161,7 @@
         </is>
       </c>
       <c r="AI16" s="49">
-        <f>AL16*1000*8</f>
+        <f>AL16*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ16" s="50" t="n"/>
@@ -19453,7 +19456,7 @@
         </is>
       </c>
       <c r="AI17" s="49">
-        <f>AL17*1000*8</f>
+        <f>AL17*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ17" s="50" t="n"/>
@@ -19461,7 +19464,7 @@
         <v>47270</v>
       </c>
       <c r="AL17" s="44" t="n">
-        <v>820</v>
+        <v>754</v>
       </c>
       <c r="AM17" s="44" t="n">
         <v>500</v>
@@ -19653,12 +19656,12 @@
       </c>
       <c r="CI17" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,560,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
+          <t>*RPBD* OVERVIEW: ~754-820 MW natural-gas COMBINED-CYCLE unit approved with Franklin Farms to support Meta's Hyperion load; paired with proposed Waterford 6 (754 MW, ~Jul 2030, LPSC vote Dec 16, 2026) - ~$3.75B WF5+6 program, 700+ construction jobs 2026-2030. TECHNOLOGY &amp; EQUIPMENT: 1x1 combined cycle - Mitsubishi Power M501JAC gas turbine, HRSG, steam turbine (EIA: 2 generators, 820 MW nameplate). SITE: BROWNFIELD - existing Entergy Waterford generating complex at Killona/Taft, St. Charles Parish, on the Mississippi River (home to Waterford 1 &amp; 2 gas/oil units and Waterford 3 nuclear); soft soils require ~100,000 truckloads of surcharge fill (site prep since Nov 2025). INTERCONNECTION: Waterford 500 kV substation via ~0.25-mile 500 kV gen-tie (MISO E0029). OWNERSHIP/EPC: Entergy Louisiana; EPC TSL Power Partners (TIC + Sargent &amp; Lundy) per LPSC Waterford 6 filing. Main construction late 2026; COD 2029. Cost ~ $1.2B implied. INVESTMENT: Total project investment ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed; est. W&amp;C value $6,032,000 ($8/kW). W&amp;C NEEDS (combined cycle): MV power cable (5-35 kV) from unit auxiliary/station service transformers to plant MV switchgear and large motors (boiler feed pumps, condensate &amp; circulating water pumps, cooling tower/ACC fans, gas compressors); 600V power &amp; TC-ER tray cable for MCCs, HRSG/steam-turbine auxiliaries, BOP and water treatment; shielded instrumentation &amp; control cable (DCS, turbine controls, CEMS); bare copper grounding grid; switchyard control/relay cable; lighting, building wire and fire-alarm in admin/warehouse/control buildings. Plus 500 kV gen-tie; bundle Waterford 5 + 6 as one cable package. Ref: https://www.entergylouisiana.com/waterford5-6 | https://www.interconnection.fyi/project/miso-e0029 | https://www.entergy.com/blog/the-dirt-on-dirt-from-digging-soil-to-boosting-louisianas-economy</t>
         </is>
       </c>
       <c r="CJ17" s="38" t="inlineStr">
         <is>
-          <t>*RPBD* Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. Est. W&amp;C value: $6,560,000 ($8/kW).</t>
+          <t>*RPBD* Total project investment: ~$1.2B implied (similar to each Franklin Farms unit); Yes Energy $1.75B not confirmed. Est. W&amp;C value: $6,032,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19761,7 @@
         </is>
       </c>
       <c r="AI18" s="49">
-        <f>AL18*1000*8</f>
+        <f>AL18*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ18" s="50" t="n"/>
@@ -20051,7 +20054,7 @@
         </is>
       </c>
       <c r="AI19" s="49">
-        <f>AL19*1000*8</f>
+        <f>AL19*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ19" s="50" t="n"/>
@@ -20059,7 +20062,7 @@
         <v>46053</v>
       </c>
       <c r="AL19" s="44" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AM19" s="44" t="n">
         <v>345</v>
@@ -20246,7 +20249,7 @@
       </c>
       <c r="CJ19" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$1.2B. Est. W&amp;C value: $7,520,000 ($8/kW).</t>
+          <t>Total project investment: ~$1.2B. Est. W&amp;C value: $7,600,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20349,7 @@
         </is>
       </c>
       <c r="AI20" s="49">
-        <f>AL20*1000*8</f>
+        <f>AL20*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ20" s="50" t="n"/>
@@ -20631,7 +20634,7 @@
         </is>
       </c>
       <c r="AI21" s="49">
-        <f>AL21*1000*8</f>
+        <f>AL21*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ21" s="50" t="n"/>
@@ -20916,7 +20919,7 @@
         </is>
       </c>
       <c r="AI22" s="49">
-        <f>AL22*1000*8</f>
+        <f>AL22*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ22" s="50" t="n"/>
@@ -20924,7 +20927,7 @@
         <v>46752</v>
       </c>
       <c r="AL22" s="44" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="AM22" s="43" t="n"/>
       <c r="AN22" s="37" t="inlineStr">
@@ -21090,7 +21093,7 @@
       <c r="CF22" s="39" t="n"/>
       <c r="CG22" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Kiewit on site since Oct 2025, HRSG delivery Sep-Oct 2026, first GT set Oct 2026, first power late 2027/early 2028 -&gt; main power-block cable POs very likely placed; remaining releases/change orders through Q1 2027. Bigger long-tail: Amazon 36-building data-center campus plan (construction from Dec 2026, build-out to 2036; tabled by county Sep 2026). Other contacts: Brian Reinhart (VP, Kiewit Power Constructors); press@homercityredevelopment.com.</t>
+          <t>AWARD (PO) DATE BASIS: Kiewit on site since Oct 2025, HRSG delivery Sep-Oct 2026, first GT set Oct 2026, first power late 2027/early 2028 -&gt; main power-block cable POs very likely placed; remaining releases/change orders through Q1 2027. Bigger long-tail: Amazon 36-building data-center campus plan (construction from Dec 2026, build-out to 2036; tabled by county Sep 2026). Other contacts: Brian Reinhart (VP, Kiewit Power Constructors); Kiewit vendor inbox HomerCity.Info@Kiewit.com; press@homercityredevelopment.com.</t>
         </is>
       </c>
       <c r="CH22" s="38" t="inlineStr">
@@ -21105,7 +21108,7 @@
       </c>
       <c r="CJ22" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: &gt;$10B initial capital for power infrastructure and site readiness. Est. W&amp;C value: $36,000,000 ($8/kW).</t>
+          <t>Total project investment: &gt;$10B initial capital for power infrastructure and site readiness. Est. W&amp;C value: $35,200,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -21205,7 +21208,7 @@
         </is>
       </c>
       <c r="AI23" s="49">
-        <f>AL23*1000*8</f>
+        <f>AL23*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ23" s="50" t="n"/>
@@ -21391,7 +21394,7 @@
       <c r="CF23" s="39" t="n"/>
       <c r="CG23" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Gemma EPC Feb 2025, NTP Apr 2025, completion 2028 -&gt; cable window Dec 2026-Dec 2027, target ~Q1 2027. RISK: Xebec bio says project sold Apr 2026 (buyer unknown) - confirm owner/schedule. Luminant link only historical (old Sandow coal plant) - merge CRM Luminant duplicates. Other contact: Charles E. Collins IV (CEO, Gemma).</t>
+          <t>AWARD (PO) DATE BASIS: Gemma EPC Feb 2025, NTP Apr 2025, completion 2028 -&gt; cable window Dec 2026-Dec 2027, target ~Q1 2027. RISK: Xebec bio says project sold Apr 2026 (buyer unknown) - confirm owner/schedule. Luminant link only historical (old Sandow coal plant) - merge CRM Luminant duplicates. Other contacts: Tommy Hodges (COO, SL Energy Power Plant I LLC - tommyh@slenergyco.com, TCEQ 2025 filing); Charles E. Collins IV (CEO, Gemma).</t>
         </is>
       </c>
       <c r="CH23" s="38" t="inlineStr">
@@ -21506,7 +21509,7 @@
         </is>
       </c>
       <c r="AI24" s="49">
-        <f>AL24*1000*8</f>
+        <f>AL24*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ24" s="50" t="n"/>
@@ -21514,7 +21517,7 @@
         <v>46934</v>
       </c>
       <c r="AL24" s="44" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="AM24" s="43" t="n"/>
       <c r="AN24" s="37" t="inlineStr">
@@ -21599,7 +21602,11 @@
           <t>Kindle Energy / Blackstone</t>
         </is>
       </c>
-      <c r="BF24" s="39" t="n"/>
+      <c r="BF24" s="38" t="inlineStr">
+        <is>
+          <t>Kindle Energy EPCM (four principal contractors - names not published)</t>
+        </is>
+      </c>
       <c r="BG24" s="36" t="inlineStr">
         <is>
           <t>Kindle Energy</t>
@@ -21676,22 +21683,22 @@
       <c r="CF24" s="39" t="n"/>
       <c r="CG24" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: FID Nov 2025, groundbreaking Apr 2026, concrete pours mid-2026, COD 2028 -&gt; cable window open now, target Dec 2026-Mar 2027 (if COD 2027 per ENR, act immediately). EPC not public - top discovery item. CRM 579 MW not supported; sources say ~600-625 MW. Project contact: info@wolf-summit.com, (304) 576-8717. Other: Chris Cosby (CEO, ODEC); Bilal Khan (SMD, Blackstone).</t>
+          <t>AWARD (PO) DATE BASIS: FID Nov 2025, groundbreaking Apr 2026, concrete pours mid-2026, COD 2028 -&gt; cable window open now, target Dec 2026-Mar 2027 (if COD 2027 per ENR, act immediately). Delivered as Kindle EPCM with four principal contractors (names not published) - identify the electrical contractor. CRM 579 MW not supported; sources say ~600-625 MW (610 MW used). Project contact: info@wolf-summit.com, (304) 576-8717. Other: Chris Cosby (CEO, ODEC); Bilal Khan (SMD, Blackstone).</t>
         </is>
       </c>
       <c r="CH24" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC via Kindle Energy / project line (304) 576-8717 / WV Building Trades; position MV, control &amp; I&amp;C cable before bulk electrical buy.</t>
+          <t>Ask Kindle (EPCM) which principal contractor holds electrical; use Kindle Energy / project line (304) 576-8717 / WV Building Trades; position MV, control &amp; I&amp;C cable before bulk electrical buy.</t>
         </is>
       </c>
       <c r="CI24" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: ~600 MW natural-gas combined-cycle plant - West Virginia's first gas power plant - backed by $1.2B from Blackstone Energy Transition Partners, developed/operated by Kindle Energy, fully contracted to Old Dominion Electric Cooperative; ~500 construction jobs. TECHNOLOGY &amp; EQUIPMENT: GE Vernova 7HA.02 gas turbine in combined cycle (likely 1x1 with HRSG and steam turbine - inferred); GE Vernova Financial Services also financing. SITE: Pinnickinnick Hill area near Clarksburg/Wolf Summit, Harrison County (PILOT/lease Jan 2025); acreage not published. INTERCONNECTION: PJM grid sale to ODEC; substation/voltage not published. OWNERSHIP/STATUS: FID Nov 2025; groundbreaking Apr 22, 2026; site prep and roadwork Jun 2026; COD 2028. EPC not public. INVESTMENT: $1.2B. W&amp;C NEEDS (combined cycle): MV power cable to aux transformers, MV switchgear and large motors; 600V power &amp; TC-ER tray cable for HRSG/ST auxiliaries and BOP; shielded I&amp;C cable; bare copper grounding; switchyard control cable; building wire. Ref: https://www.businesswire.com/news/home/20260422186042/en/Kindle-Energy-Breaks-Ground-on-Blackstone-Backed-$1.2-Billion-Natural-Gas-Power-Generation-Facility-in-West-Virginia | https://wolf-summit.com/ | https://www.powermag.com/blackstone-investing-1-2-billion-for-600-mw-gas-fired-plant-in-west-virginia/</t>
+          <t>OVERVIEW: ~600 MW natural-gas combined-cycle plant - West Virginia's first gas power plant - backed by $1.2B from Blackstone Energy Transition Partners, developed/operated by Kindle Energy, fully contracted to Old Dominion Electric Cooperative; ~500 construction jobs. TECHNOLOGY &amp; EQUIPMENT: GE Vernova 7HA.02 gas turbine in combined cycle (likely 1x1 with HRSG and steam turbine - inferred); GE Vernova Financial Services also financing. SITE: Pinnickinnick Hill area near Clarksburg/Wolf Summit, Harrison County (PILOT/lease Jan 2025); acreage not published. INTERCONNECTION: PJM grid sale to ODEC; substation/voltage not published. OWNERSHIP/STATUS: FID Nov 2025; groundbreaking Apr 22, 2026; site prep and roadwork Jun 2026; COD 2028. Kindle EPCM with four principal contractors (not published). INVESTMENT: $1.2B. W&amp;C NEEDS (combined cycle): MV power cable to aux transformers, MV switchgear and large motors; 600V power &amp; TC-ER tray cable for HRSG/ST auxiliaries and BOP; shielded I&amp;C cable; bare copper grounding; switchyard control cable; building wire. Ref: https://www.businesswire.com/news/home/20260422186042/en/Kindle-Energy-Breaks-Ground-on-Blackstone-Backed-$1.2-Billion-Natural-Gas-Power-Generation-Facility-in-West-Virginia | https://wolf-summit.com/ | https://www.powermag.com/blackstone-investing-1-2-billion-for-600-mw-gas-fired-plant-in-west-virginia/</t>
         </is>
       </c>
       <c r="CJ24" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: $1.2B (Blackstone). Est. W&amp;C value: $4,800,000 ($8/kW).</t>
+          <t>Total project investment: $1.2B (Blackstone). Est. W&amp;C value: $4,880,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21798,7 @@
         </is>
       </c>
       <c r="AI25" s="49">
-        <f>AL25*1000*8</f>
+        <f>AL25*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ25" s="50" t="n"/>
@@ -21961,7 +21968,7 @@
       <c r="CF25" s="39" t="n"/>
       <c r="CG25" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: TEF loan closed Q3 2025, under construction, COD mid-2028 (NRG) -&gt; cable window Jul 2026-Jul 2027, target Nov 2026-Feb 2027. EPC not public (NRG GE Vernova/Kiewit venture is for 7HA units, not this Mitsubishi unit). CRM correction: 689 MW (NRG) vs 721 MW (state), Mitsubishi not GE, COD mid-2028 not 2029.</t>
+          <t>AWARD (PO) DATE BASIS: TEF loan closed Q3 2025, under construction, COD mid-2028 (NRG) -&gt; cable window Jul 2026-Jul 2027, target Nov 2026-Feb 2027. EPC not public (NRG GE Vernova/Kiewit venture is for 7HA units, not this Mitsubishi unit). CRM correction: 689 MW (NRG) vs 721 MW (state), Mitsubishi not GE, COD mid-2028 not 2029. Owner contact on 2026 TDLR project registration: Dudley D. Zahn (NRG / Cedar Bayou 5 LLC, 713-537-3290; email historical).</t>
         </is>
       </c>
       <c r="CH25" s="38" t="inlineStr">
@@ -22076,7 +22083,7 @@
         </is>
       </c>
       <c r="AI26" s="49">
-        <f>AL26*1000*8</f>
+        <f>AL26*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ26" s="50" t="n"/>
@@ -22375,7 +22382,7 @@
         </is>
       </c>
       <c r="AI27" s="49">
-        <f>AL27*1000*8</f>
+        <f>AL27*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ27" s="50" t="n"/>
@@ -22383,7 +22390,7 @@
         <v>48213</v>
       </c>
       <c r="AL27" s="44" t="n">
-        <v>2060</v>
+        <v>2100</v>
       </c>
       <c r="AM27" s="44" t="n">
         <v>500</v>
@@ -22572,7 +22579,7 @@
       </c>
       <c r="CJ27" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: ~$3B-$3.3B. Est. W&amp;C value: $16,480,000 ($8/kW).</t>
+          <t>Total project investment: ~$3B-$3.3B. Est. W&amp;C value: $16,800,000 ($8/kW).</t>
         </is>
       </c>
     </row>
@@ -22668,7 +22675,7 @@
         </is>
       </c>
       <c r="AI28" s="49">
-        <f>AL28*1000*8</f>
+        <f>AL28*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ28" s="50" t="n"/>
@@ -22955,7 +22962,7 @@
         </is>
       </c>
       <c r="AI29" s="49">
-        <f>AL29*1000*8</f>
+        <f>AL29*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ29" s="50" t="n"/>
@@ -23246,7 +23253,7 @@
         </is>
       </c>
       <c r="AI30" s="49">
-        <f>AL30*1000*8</f>
+        <f>AL30*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ30" s="50" t="n"/>
@@ -23343,10 +23350,14 @@
           <t>Energy Forge One LLC (Chevron)</t>
         </is>
       </c>
-      <c r="BF30" s="39" t="n"/>
+      <c r="BF30" s="38" t="inlineStr">
+        <is>
+          <t>Bechtel (Kilby job 26776 - procurement/early works published; full NTP to confirm)</t>
+        </is>
+      </c>
       <c r="BG30" s="38" t="inlineStr">
         <is>
-          <t>Chevron New Energies + Joulent (Engine No. 1; National Grid Ventures 35% of Joulent)</t>
+          <t>Energy Forge One LLC - Chevron / Joulent 50:50 JV (Joulent: Engine No. 1; National Grid Ventures 35%)</t>
         </is>
       </c>
       <c r="BH30" s="39" t="n"/>
@@ -23420,17 +23431,17 @@
       <c r="CF30" s="39" t="n"/>
       <c r="CG30" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: PPA signed Jun 2026, FID targeted end-2026, first power 2028 with phased ramp to ~2.67 GW (~2029-30) -&gt; award window Jun 2026-Jun 2027, target ~Q1 2027 (early-power Titan 130 units drive first packages). CRM COD 6/30/2027 corrected to 2028. EPC capacity reportedly reserved but unnamed. Other contacts: Jeff Gustavson (President, Chevron New Energies); Chris James (Founder &amp; CEO, Engine No. 1 / Joulent).</t>
+          <t>AWARD (PO) DATE BASIS: PPA signed Jun 2026, FID targeted end-2026, first power 2028 with phased ramp to ~2.67 GW (~2029-30) -&gt; award window Jun 2026-Jun 2027, target ~Q1 2027 (early-power Titan 130 units drive first packages). CRM COD 6/30/2027 corrected to 2028. Bechtel May 2026 Project Opportunity Report lists Kilby job 26776 with procurement (Birju Vasani, bvasani@bechtel.com) and subcontracts (Mark Bingaman, mabingam@bechtel.com, 713-235-1662) prequalification contacts; full NTP not confirmed. Full capacity 2031 per kilby.com. Other contacts: Jeff Gustavson (President, Chevron New Energies); Chris James (Founder &amp; CEO, Engine No. 1 / Joulent).</t>
         </is>
       </c>
       <c r="CH30" s="38" t="inlineStr">
         <is>
-          <t>Identify EPC now and get specified before FID (Dec 2026); engage Chevron Power Solutions (Daniel Droog).</t>
+          <t>Prequalify with Bechtel now: Birju Vasani (procurement) and Mark Bingaman (subcontracts) for Kilby job 26776; get specified before FID (Dec 2026); engage Chevron Power Solutions (Daniel Droog).</t>
         </is>
       </c>
       <c r="CI30" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: ~2.67 GW (permit ~2.87 GW, possible scale to 5 GW) off-grid natural-gas power plant dedicated to Microsoft's up-to-2 GW Pecos AI data-center campus under a 20-year PPA (Jun 22, 2026); developed by Chevron (Energy Forge One) with Engine No. 1's Joulent and National Grid Ventures ($1.75B for 35% of Joulent). TECHNOLOGY &amp; EQUIPMENT: ~46 gas turbines - GE Vernova 7HA (7 reserved; permit analysis 5x 7HA.02) plus Solar Turbines Titan 350 (12) and Titan 130 (29, added Dec 2025 for early power); SCR and oxidation catalysts; combined/simple-cycle split not confirmed. SITE: GREENFIELD - Reeves County, SE of Pecos near Verhalen (Pecos TX 79780), off US-285 / FM 112; Microsoft campus ~7,000 acres (tracker, unverified). INTERCONNECTION: behind-the-meter, co-located with Microsoft campus (ERCOT region, no grid export disclosed). OWNERSHIP/STATUS: pre-FID; TCEQ air permit draft Apr 2026, public meeting Jun 10, 2026, pending; FID end-2026; first power 2028. INVESTMENT: ~$7-9B (analyst estimates). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Very large scope: 46 turbine packages plus data-center campus feeders. Ref: https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/181895-pls-english.pdf | https://blogs.microsoft.com/blog/2026/06/22/powering-the-next-wave-of-ai-expanding-capacity-with-our-new-datacenter-in-pecos/</t>
+          <t>OVERVIEW: ~2.67 GW (permit ~2.87 GW, possible scale to 5 GW) off-grid natural-gas power plant dedicated to Microsoft's up-to-2 GW Pecos AI data-center campus under a 20-year PPA (Jun 22, 2026); developed by Chevron (Energy Forge One) with Engine No. 1's Joulent and National Grid Ventures ($1.75B for 35% of Joulent). TECHNOLOGY &amp; EQUIPMENT: ~46 gas turbines - GE Vernova 7HA (7 reserved; permit analysis 5x 7HA.02) plus Solar Turbines Titan 350 (12) and Titan 130 (29, added Dec 2025 for early power); SCR and oxidation catalysts; combined/simple-cycle split not confirmed. SITE: GREENFIELD - Reeves County, SE of Pecos near Verhalen (Pecos TX 79780), off US-285 / FM 112; Microsoft campus ~7,000 acres (tracker, unverified). INTERCONNECTION: behind-the-meter, co-located with Microsoft campus (ERCOT region, no grid export disclosed). OWNERSHIP/STATUS: Energy Forge One LLC (Chevron/Joulent 50:50); EPC Bechtel (job 26776, procurement/early works); pre-FID; TCEQ air permit draft Apr 2026, public meeting Jun 10, 2026, pending; FID end-2026; first power 2028. INVESTMENT: ~$7-9B (analyst estimates). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Very large scope: 46 turbine packages plus data-center campus feeders. Ref: https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center | https://www.tceq.texas.gov/downloads/permitting/air/bilingual/pending-permit-notices/181895-pls-english.pdf | https://blogs.microsoft.com/blog/2026/06/22/powering-the-next-wave-of-ai-expanding-capacity-with-our-new-datacenter-in-pecos/</t>
         </is>
       </c>
       <c r="CJ30" s="38" t="inlineStr">
@@ -23535,7 +23546,7 @@
         </is>
       </c>
       <c r="AI31" s="49">
-        <f>AL31*1000*8</f>
+        <f>AL31*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ31" s="50" t="n"/>
@@ -23543,7 +23554,7 @@
         <v>47208</v>
       </c>
       <c r="AL31" s="44" t="n">
-        <v>2700</v>
+        <v>2550</v>
       </c>
       <c r="AM31" s="44" t="n">
         <v>345</v>
@@ -23632,7 +23643,7 @@
       </c>
       <c r="BF31" s="38" t="inlineStr">
         <is>
-          <t>Frontier Group (self-performs permitting, engineering and construction)</t>
+          <t>Frontier Group (self-performs); Wood - owner's engineer; construction package contractors to confirm</t>
         </is>
       </c>
       <c r="BG31" s="36" t="inlineStr">
@@ -23643,7 +23654,7 @@
       <c r="BH31" s="39" t="n"/>
       <c r="BI31" s="38" t="inlineStr">
         <is>
-          <t>3x existing GE steam turbine-generators (refurbished); new gas turbines (OEM not disclosed)</t>
+          <t>Existing Foster Wheeler boilers / 3x GE steam turbine-generators (refurbished); new gas turbines (OEM not disclosed)</t>
         </is>
       </c>
       <c r="BJ31" s="39" t="n"/>
@@ -23711,7 +23722,7 @@
       <c r="CF31" s="39" t="n"/>
       <c r="CG31" s="38" t="inlineStr">
         <is>
-          <t>AWARD (PO) DATE BASIS: Frontier targets PJM approval mid-2028 and units online early 2029 with ~3-year construction -&gt; award window Mar 2027-Mar 2028, target ~Q2 2027. CRM COD 12/31/2030 updated to early 2029. Capacity conflicts: 2,550 MW export / 2.7 GW conversion + 900 MW Phase I = 3.6 GW. Aligned Data Centers broke ground on 2 GW Project Phoenix (~$10B) Sep 10, 2026 next door. Other contacts: David Franjoine (Founder &amp; CEO); Robert Zuchlewski (COO).</t>
+          <t>AWARD (PO) DATE BASIS: Frontier targets PJM approval mid-2028 and units online early 2029 with ~3-year construction -&gt; award window Mar 2027-Mar 2028, target ~Q2 2027. CRM COD 12/31/2030 updated to early 2029. Capacity conflicts: 2,550 MW export / 2.7 GW conversion + 900 MW Phase I = 3.6 GW. Aligned Data Centers broke ground on 2 GW Project Phoenix (~$10B) Sep 10, 2026 next door. Other contacts: David Franjoine (Founder &amp; CEO); Robert Zuchlewski (COO); Anthony Basil (Project Manager) and Peter Violante (Dir. Logistics &amp; BD) - Shippingport assignment not confirmed. Owner's engineer: Wood.</t>
         </is>
       </c>
       <c r="CH31" s="38" t="inlineStr">
@@ -23721,25 +23732,29 @@
       </c>
       <c r="CI31" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: conversion of the former 2.5-2.7 GW Bruce Mansfield coal plant (operated 1976-2019) into a natural-gas power station; Phase I adds ~900 MW new simple-cycle gas turbines + switchyard, Phase II (this record) converts the coal units (~2.7 GW) - up to ~3.6 GW total available to the park; EQT gas supply ~800 MMcf/d via new 7.2-mile National Fuel lateral. TECHNOLOGY &amp; EQUIPMENT: refurbish 3x existing GE steam turbine-generators (~850 MW each) re-powered with new gas turbines (repowering), new cooling towers, transformers and switchgear, on-site gas receiving station and 34.5 kV substation; coal handling demolished. SITE: BROWNFIELD - former Bruce Mansfield coal plant in the 660-acre Shippingport Industrial Park, Shippingport Borough, Beaver County; 14.5-acre gas fuel yard. Aligned Data Centers' 2 GW Project Phoenix campus under construction on site. INTERCONNECTION: PJM Cycle 01 (existing Bruce Mansfield 345 kV substation, Penn Power/FirstEnergy) plus behind-the-meter supply to the park. OWNERSHIP/STATUS: Frontier Group (self-performs engineering and construction); permitting underway; PJM approval mid-2028; units online early 2029; &gt;1,500 construction workers. INVESTMENT: &gt;$1.8B. W&amp;C NEEDS (repowered steam units + new GTs): MV power cable for new GT/aux transformers, cooling-tower fans and pumps, 34.5 kV substation feeders; 600V power &amp; TC-ER tray cable; shielded I&amp;C cable for new controls/DCS; grounding; switchyard control cable; data-center park MV distribution. Ref: https://frontier-companies.com/shippingport-power-station-featured-in-energy-oil-gas-magazine/ | https://www.businesswire.com/news/home/20250715103342/en/The-Frontier-Group-of-Companies-to-Transform-Bruce-Mansfield-Power-Plant-into-State-of-the-Art-Natural-Gas-Power-Plant-Supporting-Americas-Energy-Goals-and-Pennsylvanias-Economic-Growth | https://aligneddc.com/press-release/project-phoenix-data-center-shippingport-pa/</t>
+          <t>OVERVIEW: conversion of the former 2.5-2.7 GW Bruce Mansfield coal plant (operated 1976-2019) into a natural-gas power station; Phase I adds ~900 MW new simple-cycle gas turbines + switchyard, Phase II (this record) converts the coal units (~2.7 GW) - up to ~3.6 GW total available to the park; EQT gas supply ~800 MMcf/d via new 7.2-mile National Fuel lateral. TECHNOLOGY &amp; EQUIPMENT: refurbish 3x existing GE steam turbine-generators (~850 MW each) re-powered with new gas turbines (repowering), new cooling towers, transformers and switchgear, on-site gas receiving station and 34.5 kV substation; coal handling demolished. SITE: BROWNFIELD - former Bruce Mansfield coal plant in the 660-acre Shippingport Industrial Park, Shippingport Borough, Beaver County; 14.5-acre gas fuel yard. Aligned Data Centers' 2 GW Project Phoenix campus under construction on site. INTERCONNECTION: PJM Cycle 01 (existing Bruce Mansfield 345 kV substation, Penn Power/FirstEnergy) plus behind-the-meter supply to the park. OWNERSHIP/STATUS: Frontier Group (self-performs engineering and construction; Wood owner's engineer); permitting underway; PJM approval mid-2028; units online early 2029; &gt;1,500 construction workers. INVESTMENT: &gt;$1.8B. W&amp;C NEEDS (repowered steam units + new GTs): MV power cable for new GT/aux transformers, cooling-tower fans and pumps, 34.5 kV substation feeders; 600V power &amp; TC-ER tray cable; shielded I&amp;C cable for new controls/DCS; grounding; switchyard control cable; data-center park MV distribution. Ref: https://frontier-companies.com/shippingport-power-station-featured-in-energy-oil-gas-magazine/ | https://www.businesswire.com/news/home/20250715103342/en/The-Frontier-Group-of-Companies-to-Transform-Bruce-Mansfield-Power-Plant-into-State-of-the-Art-Natural-Gas-Power-Plant-Supporting-Americas-Energy-Goals-and-Pennsylvanias-Economic-Growth | https://aligneddc.com/press-release/project-phoenix-data-center-shippingport-pa/</t>
         </is>
       </c>
       <c r="CJ31" s="38" t="inlineStr">
         <is>
-          <t>Total project investment: &gt;$1.8B (Frontier Oct 2026; other Frontier pages cite $1.6B+ to ~$3.2B for full conversion). Est. W&amp;C value: $21,600,000 ($8/kW).</t>
+          <t>Total project investment: &gt;$1.8B (Frontier Oct 2026; other Frontier pages cite $1.6B+ to ~$3.2B for full conversion). Est. W&amp;C value: $20,400,000 ($8/kW).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="36" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="B32" s="39" t="n"/>
+          <t>Siffin</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>VPN 4420 LLC</t>
+          <t>Maefield Development / VPN 4420 LLC</t>
         </is>
       </c>
       <c r="D32" s="37" t="inlineStr">
@@ -23760,7 +23775,7 @@
       <c r="G32" s="40" t="n"/>
       <c r="H32" s="36" t="inlineStr">
         <is>
-          <t>Developer contact</t>
+          <t>CEO / project business contact</t>
         </is>
       </c>
       <c r="I32" s="37" t="inlineStr">
@@ -23773,9 +23788,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="K32" s="39" t="n"/>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>+1 347-703-0093</t>
+        </is>
+      </c>
       <c r="L32" s="39" t="n"/>
-      <c r="M32" s="39" t="n"/>
+      <c r="M32" s="36" t="inlineStr">
+        <is>
+          <t>siffin@maefield.com</t>
+        </is>
+      </c>
       <c r="N32" s="39" t="n"/>
       <c r="O32" s="37" t="inlineStr">
         <is>
@@ -23822,7 +23845,7 @@
         </is>
       </c>
       <c r="AI32" s="49">
-        <f>AL32*1000*8</f>
+        <f>AL32*1000*Guide!$B$81</f>
         <v/>
       </c>
       <c r="AJ32" s="50" t="n"/>
@@ -23918,7 +23941,7 @@
       <c r="BF32" s="39" t="n"/>
       <c r="BG32" s="38" t="inlineStr">
         <is>
-          <t>VPN 4420 LLC (Maefield Development link not confirmed)</t>
+          <t>VPN 4420 LLC / Maefield Development (link per Chapter 313 filings)</t>
         </is>
       </c>
       <c r="BH32" s="39" t="n"/>
@@ -23988,7 +24011,7 @@
       <c r="CF32" s="39" t="n"/>
       <c r="CG32" s="38" t="inlineStr">
         <is>
-          <t>LOW PROBABILITY: Chapter 313 agreement executed Dec 19, 2022 ($1B, 10 jobs); 2023 report showed no jobs/investment; no TCEQ air permit found; Maefield Development link not found publicly. Tentative award 6/30/2029. Same county has stronger leads: Project Kilby (Chevron/Microsoft), Prometheus Hyperscale + Istmo (1.5-2.5 GW, Aug 2026), LandBridge/NRG (1.1 GW), LandBridge/PowerBridge (2 GW).</t>
+          <t>LOW PROBABILITY: Chapter 313 agreement executed Dec 19, 2022 ($1B, 10 jobs); 2023 report showed no jobs/investment; no TCEQ air permit found. Maefield link established via Chapter 313 filings (2024 compliance report posted 2026 lists Mark Siffin). Tentative award 6/30/2029. Same county has stronger leads: Project Kilby (Chevron/Microsoft), Prometheus Hyperscale + Istmo (1.5-2.5 GW, Aug 2026), LandBridge/NRG (1.1 GW), LandBridge/PowerBridge (2 GW).</t>
         </is>
       </c>
       <c r="CH32" s="38" t="inlineStr">
@@ -23998,7 +24021,7 @@
       </c>
       <c r="CI32" s="38" t="inlineStr">
         <is>
-          <t>OVERVIEW: proposed Phase 1 technology campus (~6 million sq ft of data centers and semiconductor manufacturing) in Reeves County powered by up to three on-site natural-gas trigeneration plants (power, heating, cooling) totaling ~1.54 GW with CO2 capture equipment. TECHNOLOGY &amp; EQUIPMENT: on-site gas trigeneration plants with CO2 capture (OEMs not published). SITE: GREENFIELD - Pecos-Barstow-Toyah ISD area, Reeves County (acreage not published). INTERCONNECTION: on-site / behind the meter. OWNERSHIP/STATUS: VPN 4420 LLC; Chapter 313 agreement Dec 2022; no reported investment or permits as of latest filings - likely stalled. INVESTMENT: $1B qualified investment (313). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Ref: https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993 | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-agmt.pdf</t>
+          <t>OVERVIEW: proposed Phase 1 technology campus (~6 million sq ft of data centers and semiconductor manufacturing) in Reeves County powered by up to three on-site natural-gas trigeneration plants (power, heating, cooling) totaling ~1.54 GW with CO2 capture equipment. TECHNOLOGY &amp; EQUIPMENT: on-site gas trigeneration plants with CO2 capture (OEMs not published). SITE: GREENFIELD - Pecos-Barstow-Toyah ISD area, Reeves County (acreage not published). INTERCONNECTION: on-site / behind the meter. OWNERSHIP/STATUS: VPN 4420 LLC / Maefield Development (Mark Siffin); Chapter 313 agreement Dec 2022; no reported investment or permits as of latest filings - likely stalled. INVESTMENT: $1B qualified investment (313). W&amp;C NEEDS (behind-the-meter / on-site generation): MV power cable (5-35 kV) collecting many turbine/engine units to on-site switching and plant substations and feeders to the data-center campus; 600V power &amp; TC-ER tray cable for unit packages, MCCs, gas conditioning/compression, BESS and cooling; shielded instrumentation &amp; control cable (unit controls, microgrid/SCADA); extensive bare copper grounding; switchgear/substation control cable; building wire for control and admin buildings. High unit count = high cable density per MW. Ref: https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993 | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-agmt.pdf</t>
         </is>
       </c>
       <c r="CJ32" s="38" t="inlineStr">
@@ -40611,7 +40634,7 @@
       </c>
       <c r="C50" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $2,755,200</t>
+          <t>MV power cable: 42% of W&amp;C = $2,533,440</t>
         </is>
       </c>
     </row>
@@ -40628,7 +40651,7 @@
       </c>
       <c r="C51" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $2,820,800</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $2,593,760</t>
         </is>
       </c>
     </row>
@@ -40645,7 +40668,7 @@
       </c>
       <c r="C52" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $656,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $603,200</t>
         </is>
       </c>
     </row>
@@ -40662,7 +40685,7 @@
       </c>
       <c r="C53" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $328,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $301,600</t>
         </is>
       </c>
     </row>
@@ -40764,7 +40787,7 @@
       </c>
       <c r="C59" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $3,158,400</t>
+          <t>MV power cable: 42% of W&amp;C = $3,192,000</t>
         </is>
       </c>
     </row>
@@ -40781,7 +40804,7 @@
       </c>
       <c r="C60" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $3,233,600</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $3,268,000</t>
         </is>
       </c>
     </row>
@@ -40798,7 +40821,7 @@
       </c>
       <c r="C61" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $752,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $760,000</t>
         </is>
       </c>
     </row>
@@ -40815,7 +40838,7 @@
       </c>
       <c r="C62" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $376,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $380,000</t>
         </is>
       </c>
     </row>
@@ -40968,7 +40991,7 @@
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $15,120,000</t>
+          <t>MV power cable: 42% of W&amp;C = $14,784,000</t>
         </is>
       </c>
     </row>
@@ -40985,7 +41008,7 @@
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $15,480,000</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $15,136,000</t>
         </is>
       </c>
     </row>
@@ -41002,7 +41025,7 @@
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $3,600,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $3,520,000</t>
         </is>
       </c>
     </row>
@@ -41019,7 +41042,7 @@
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $1,800,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $1,760,000</t>
         </is>
       </c>
     </row>
@@ -41121,7 +41144,7 @@
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $2,016,000</t>
+          <t>MV power cable: 42% of W&amp;C = $2,049,600</t>
         </is>
       </c>
     </row>
@@ -41138,7 +41161,7 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $2,064,000</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $2,098,400</t>
         </is>
       </c>
     </row>
@@ -41155,7 +41178,7 @@
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $480,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $488,000</t>
         </is>
       </c>
     </row>
@@ -41172,7 +41195,7 @@
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $240,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $244,000</t>
         </is>
       </c>
     </row>
@@ -41342,7 +41365,7 @@
       </c>
       <c r="C93" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $6,921,600</t>
+          <t>MV power cable: 42% of W&amp;C = $7,056,000</t>
         </is>
       </c>
     </row>
@@ -41359,7 +41382,7 @@
       </c>
       <c r="C94" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $7,086,400</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $7,224,000</t>
         </is>
       </c>
     </row>
@@ -41376,7 +41399,7 @@
       </c>
       <c r="C95" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $1,648,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $1,680,000</t>
         </is>
       </c>
     </row>
@@ -41393,7 +41416,7 @@
       </c>
       <c r="C96" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $824,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $840,000</t>
         </is>
       </c>
     </row>
@@ -41631,7 +41654,7 @@
       </c>
       <c r="C110" s="52" t="inlineStr">
         <is>
-          <t>MV power cable: 42% of W&amp;C = $9,072,000</t>
+          <t>MV power cable: 42% of W&amp;C = $8,568,000</t>
         </is>
       </c>
     </row>
@@ -41648,7 +41671,7 @@
       </c>
       <c r="C111" s="52" t="inlineStr">
         <is>
-          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $9,288,000</t>
+          <t>Tray cable (TC) - control &amp; instrumentation: 43% of W&amp;C = $8,772,000</t>
         </is>
       </c>
     </row>
@@ -41665,7 +41688,7 @@
       </c>
       <c r="C112" s="52" t="inlineStr">
         <is>
-          <t>PV / LV single-conductor power: 10% of W&amp;C = $2,160,000</t>
+          <t>PV / LV single-conductor power: 10% of W&amp;C = $2,040,000</t>
         </is>
       </c>
     </row>
@@ -41682,7 +41705,7 @@
       </c>
       <c r="C113" s="52" t="inlineStr">
         <is>
-          <t>Other - substation / switchyard: 5% of W&amp;C = $1,080,000</t>
+          <t>Other - substation / switchyard: 5% of W&amp;C = $1,020,000</t>
         </is>
       </c>
     </row>
@@ -49021,9 +49044,19 @@
       <c r="F80" s="2" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
-      <c r="C81" s="2" t="n"/>
+      <c r="A81" s="57" t="inlineStr">
+        <is>
+          <t>Whole-plant cable benchmark ($/kW)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Change this one cell to update every Amount ($) on Projects and Leads.</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n"/>
@@ -49911,7 +49944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -51103,6 +51136,450 @@
       <c r="B99" s="55" t="inlineStr">
         <is>
           <t>https://s201.q4cdn.com/714390239/files/doc_presentations/2026/Jun/09/Entergy-2026-Investor-Day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B100" s="55" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/how-do-we-source/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Vast Sands Power I (Vistra Permian Basin expansion)</t>
+        </is>
+      </c>
+      <c r="B101" s="55" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/faq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B102" s="55" t="inlineStr">
+        <is>
+          <t>https://d18rn0p25nwr6d.cloudfront.net/CIK-0000092122/32961fa3-bbf4-4ea2-8851-611fe309e97e.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B103" s="55" t="inlineStr">
+        <is>
+          <t>https://cdn.bfldr.com/E1EVDN8O/at/bz4ct6npstkxw48b6n9zm9j8/Oracle_Cloud_Azure_MFA_Registration_Step_Guide_19Jun2024.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B104" s="55" t="inlineStr">
+        <is>
+          <t>https://www.bv.com/en-US/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B105" s="55" t="inlineStr">
+        <is>
+          <t>https://www.bv.com/en-US/suppliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B106" s="55" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AES Petersburg Unit 4 Repowered</t>
+        </is>
+      </c>
+      <c r="B107" s="55" t="inlineStr">
+        <is>
+          <t>https://www.aesindiana.com/pike-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AES Petersburg Unit 4 Repowered</t>
+        </is>
+      </c>
+      <c r="B108" s="55" t="inlineStr">
+        <is>
+          <t>https://www.babcock.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center</t>
+        </is>
+      </c>
+      <c r="B109" s="55" t="inlineStr">
+        <is>
+          <t>https://www.trumbullenergycenter.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center</t>
+        </is>
+      </c>
+      <c r="B110" s="55" t="inlineStr">
+        <is>
+          <t>https://org-www.hanwha.com/newsroom/news/press-releases/hanwha-power-enters-us-market-with-successful-commissioning-of-trumbull-energy-center-combined-cycle-gas-turbine-power-plant.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Socrates South Power Generation</t>
+        </is>
+      </c>
+      <c r="B111" s="55" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Socrates South Power Generation</t>
+        </is>
+      </c>
+      <c r="B112" s="55" t="inlineStr">
+        <is>
+          <t>https://investor.williams.com/static-files/dde1b8eb-5802-4e4c-aa89-84c4d8611d56</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Homer City Energy Campus</t>
+        </is>
+      </c>
+      <c r="B113" s="55" t="inlineStr">
+        <is>
+          <t>https://www.homercityredevelopment.com/faq</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B114" s="55" t="inlineStr">
+        <is>
+          <t>https://slectx.com/argan-inc-gemma-electrify-tx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B115" s="55" t="inlineStr">
+        <is>
+          <t>https://xebecrealty.com/leadership/gretchen-kendrick/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B116" s="55" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/hearings/notices/2025/2025-04-24-sl-energy-power-plant-i-177380-pm.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B117" s="55" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/agendas/backup/2025/2025-1310-air-picr.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Wolf Summit Energy Center</t>
+        </is>
+      </c>
+      <c r="B118" s="55" t="inlineStr">
+        <is>
+          <t>https://kindle-energy.com/case-studies/wolf-summit</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Cedar Bayou Unit 5</t>
+        </is>
+      </c>
+      <c r="B119" s="55" t="inlineStr">
+        <is>
+          <t>https://investors.nrg.com/static-files/166760ef-79e6-4985-b776-09660ed84ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Cedar Bayou Unit 5</t>
+        </is>
+      </c>
+      <c r="B120" s="55" t="inlineStr">
+        <is>
+          <t>https://www.tdlr.texas.gov/TABS/Search/Print/TABS2026016466</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Cedar Bayou Unit 5</t>
+        </is>
+      </c>
+      <c r="B121" s="55" t="inlineStr">
+        <is>
+          <t>https://www.nrg.com/assets/documents/case-studies/elbow-battery/2021-operation-phase-annual-report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch Energy Center</t>
+        </is>
+      </c>
+      <c r="B122" s="55" t="inlineStr">
+        <is>
+          <t>https://cpv.com/2025/10/30/cpv-basin-ranch-and-texas-energy-fund-ink-deal-for-1350-mw-ercot-project/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch Energy Center</t>
+        </is>
+      </c>
+      <c r="B123" s="55" t="inlineStr">
+        <is>
+          <t>https://www.gemmapower.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch Energy Center</t>
+        </is>
+      </c>
+      <c r="B124" s="55" t="inlineStr">
+        <is>
+          <t>https://cpv.com/contact-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CPV Clean Energy Future - Oregon (Oregon Energy Center)</t>
+        </is>
+      </c>
+      <c r="B125" s="55" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1611005/000117891326001842/zk2634883.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CPV Clean Energy Future - Oregon (Oregon Energy Center)</t>
+        </is>
+      </c>
+      <c r="B126" s="55" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1611005/000117891325003891/exhibit_99-1.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Lincoln Land Energy Center (LLEC)</t>
+        </is>
+      </c>
+      <c r="B127" s="55" t="inlineStr">
+        <is>
+          <t>https://www.thriveinspi.org/resources/a6e96b79-67aa-448a-8fd1-54b1f1430d3a/llec%20fact%20sheet.pdf?trackid=llec+fact+sheet.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Lincoln Land Energy Center (LLEC)</t>
+        </is>
+      </c>
+      <c r="B128" s="55" t="inlineStr">
+        <is>
+          <t>https://emberclear.com/about-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B129" s="55" t="inlineStr">
+        <is>
+          <t>https://kilby.com/project/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B130" s="55" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B131" s="55" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/shippingport-industrial-park/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B132" s="55" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/frontier-group-of-companies-welcomes-senator-dave-mccormick-to-shippingport-industrial-park/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B133" s="55" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VPN 4420 Natural Gas Generation Component</t>
+        </is>
+      </c>
+      <c r="B134" s="55" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/dat/ch313/1993/01993-772-2024-0812-MCA-195901-PBT.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VPN 4420 Natural Gas Generation Component</t>
+        </is>
+      </c>
+      <c r="B135" s="55" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-app.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B136" s="55" t="inlineStr">
+        <is>
+          <t>https://kilby.com/contact/</t>
         </is>
       </c>
     </row>
@@ -51206,6 +51683,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51217,7 +51731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -53359,9 +53873,17 @@
       </c>
       <c r="I40" s="54" t="n"/>
       <c r="J40" s="54" t="n"/>
-      <c r="K40" s="54" t="n"/>
+      <c r="K40" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L40" s="54" t="n"/>
-      <c r="M40" s="54" t="n"/>
+      <c r="M40" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="54" t="inlineStr">
@@ -53402,9 +53924,17 @@
       </c>
       <c r="I41" s="54" t="n"/>
       <c r="J41" s="54" t="n"/>
-      <c r="K41" s="54" t="n"/>
+      <c r="K41" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L41" s="54" t="n"/>
-      <c r="M41" s="54" t="n"/>
+      <c r="M41" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="54" t="inlineStr">
@@ -53445,9 +53975,17 @@
       </c>
       <c r="I42" s="54" t="n"/>
       <c r="J42" s="54" t="n"/>
-      <c r="K42" s="54" t="n"/>
+      <c r="K42" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L42" s="54" t="n"/>
-      <c r="M42" s="54" t="n"/>
+      <c r="M42" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="54" t="inlineStr">
@@ -53488,9 +54026,17 @@
       </c>
       <c r="I43" s="54" t="n"/>
       <c r="J43" s="54" t="n"/>
-      <c r="K43" s="54" t="n"/>
+      <c r="K43" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L43" s="54" t="n"/>
-      <c r="M43" s="54" t="n"/>
+      <c r="M43" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="54" t="inlineStr">
@@ -53531,9 +54077,17 @@
       </c>
       <c r="I44" s="54" t="n"/>
       <c r="J44" s="54" t="n"/>
-      <c r="K44" s="54" t="n"/>
+      <c r="K44" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L44" s="54" t="n"/>
-      <c r="M44" s="54" t="n"/>
+      <c r="M44" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="54" t="inlineStr">
@@ -53574,9 +54128,17 @@
       </c>
       <c r="I45" s="54" t="n"/>
       <c r="J45" s="54" t="n"/>
-      <c r="K45" s="54" t="n"/>
+      <c r="K45" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L45" s="54" t="n"/>
-      <c r="M45" s="54" t="n"/>
+      <c r="M45" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="54" t="inlineStr">
@@ -53621,9 +54183,17 @@
       </c>
       <c r="I46" s="54" t="n"/>
       <c r="J46" s="54" t="n"/>
-      <c r="K46" s="54" t="n"/>
+      <c r="K46" s="54" t="inlineStr">
+        <is>
+          <t>Executive target; use separately labeled Socrates project outreach. Original general line is not personal.</t>
+        </is>
+      </c>
       <c r="L46" s="54" t="n"/>
-      <c r="M46" s="54" t="n"/>
+      <c r="M46" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="54" t="inlineStr">
@@ -53668,9 +54238,17 @@
       </c>
       <c r="I47" s="54" t="n"/>
       <c r="J47" s="54" t="n"/>
-      <c r="K47" s="54" t="n"/>
+      <c r="K47" s="54" t="inlineStr">
+        <is>
+          <t>Corey Hessen is owner CEO; press mailbox in original text is media-only, not his direct email. Construction vendor route added below.</t>
+        </is>
+      </c>
       <c r="L47" s="54" t="n"/>
-      <c r="M47" s="54" t="n"/>
+      <c r="M47" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="54" t="inlineStr">
@@ -53711,9 +54289,17 @@
       </c>
       <c r="I48" s="54" t="n"/>
       <c r="J48" s="54" t="n"/>
-      <c r="K48" s="54" t="n"/>
+      <c r="K48" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L48" s="54" t="n"/>
-      <c r="M48" s="54" t="n"/>
+      <c r="M48" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="54" t="inlineStr">
@@ -53754,9 +54340,17 @@
       </c>
       <c r="I49" s="54" t="n"/>
       <c r="J49" s="54" t="n"/>
-      <c r="K49" s="54" t="n"/>
+      <c r="K49" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L49" s="54" t="n"/>
-      <c r="M49" s="54" t="n"/>
+      <c r="M49" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="54" t="inlineStr">
@@ -53796,10 +54390,26 @@
         </is>
       </c>
       <c r="I50" s="54" t="n"/>
-      <c r="J50" s="54" t="n"/>
-      <c r="K50" s="54" t="n"/>
-      <c r="L50" s="54" t="n"/>
-      <c r="M50" s="54" t="n"/>
+      <c r="J50" s="54" t="inlineStr">
+        <is>
+          <t>+1 512-887-4719</t>
+        </is>
+      </c>
+      <c r="K50" s="54" t="inlineStr">
+        <is>
+          <t>Named applicant EVP; TCEQ public-meeting notice, March 2025.</t>
+        </is>
+      </c>
+      <c r="L50" s="56" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/hearings/notices/2025/2025-04-24-sl-energy-power-plant-i-177380-pm.pdf</t>
+        </is>
+      </c>
+      <c r="M50" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="54" t="inlineStr">
@@ -53840,9 +54450,17 @@
       </c>
       <c r="I51" s="54" t="n"/>
       <c r="J51" s="54" t="n"/>
-      <c r="K51" s="54" t="n"/>
+      <c r="K51" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L51" s="54" t="n"/>
-      <c r="M51" s="54" t="n"/>
+      <c r="M51" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="54" t="inlineStr">
@@ -53883,9 +54501,17 @@
       </c>
       <c r="I52" s="54" t="n"/>
       <c r="J52" s="54" t="n"/>
-      <c r="K52" s="54" t="n"/>
+      <c r="K52" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L52" s="54" t="n"/>
-      <c r="M52" s="54" t="n"/>
+      <c r="M52" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="54" t="inlineStr">
@@ -53928,11 +54554,31 @@
           <t>Official website</t>
         </is>
       </c>
-      <c r="I53" s="54" t="n"/>
-      <c r="J53" s="54" t="n"/>
-      <c r="K53" s="54" t="n"/>
-      <c r="L53" s="54" t="n"/>
-      <c r="M53" s="54" t="n"/>
+      <c r="I53" s="54" t="inlineStr">
+        <is>
+          <t>info@wolf-summit.com</t>
+        </is>
+      </c>
+      <c r="J53" s="54" t="inlineStr">
+        <is>
+          <t>+1 304-576-8717</t>
+        </is>
+      </c>
+      <c r="K53" s="54" t="inlineStr">
+        <is>
+          <t>Current shared project contact; not Lee Davis direct.</t>
+        </is>
+      </c>
+      <c r="L53" s="56" t="inlineStr">
+        <is>
+          <t>https://wolf-summit.com/</t>
+        </is>
+      </c>
+      <c r="M53" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="54" t="inlineStr">
@@ -53973,9 +54619,17 @@
       </c>
       <c r="I54" s="54" t="n"/>
       <c r="J54" s="54" t="n"/>
-      <c r="K54" s="54" t="n"/>
+      <c r="K54" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L54" s="54" t="n"/>
-      <c r="M54" s="54" t="n"/>
+      <c r="M54" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="54" t="inlineStr">
@@ -54016,9 +54670,17 @@
       </c>
       <c r="I55" s="54" t="n"/>
       <c r="J55" s="54" t="n"/>
-      <c r="K55" s="54" t="n"/>
+      <c r="K55" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L55" s="54" t="n"/>
-      <c r="M55" s="54" t="n"/>
+      <c r="M55" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="54" t="inlineStr">
@@ -54059,9 +54721,17 @@
       </c>
       <c r="I56" s="54" t="n"/>
       <c r="J56" s="54" t="n"/>
-      <c r="K56" s="54" t="n"/>
+      <c r="K56" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L56" s="54" t="n"/>
-      <c r="M56" s="54" t="n"/>
+      <c r="M56" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="54" t="inlineStr">
@@ -54102,9 +54772,17 @@
       </c>
       <c r="I57" s="54" t="n"/>
       <c r="J57" s="54" t="n"/>
-      <c r="K57" s="54" t="n"/>
+      <c r="K57" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L57" s="54" t="n"/>
-      <c r="M57" s="54" t="n"/>
+      <c r="M57" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="54" t="inlineStr">
@@ -54145,9 +54823,17 @@
       </c>
       <c r="I58" s="54" t="n"/>
       <c r="J58" s="54" t="n"/>
-      <c r="K58" s="54" t="n"/>
+      <c r="K58" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L58" s="54" t="n"/>
-      <c r="M58" s="54" t="n"/>
+      <c r="M58" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="54" t="inlineStr">
@@ -54192,9 +54878,17 @@
       </c>
       <c r="I59" s="54" t="n"/>
       <c r="J59" s="54" t="n"/>
-      <c r="K59" s="54" t="n"/>
+      <c r="K59" s="54" t="inlineStr">
+        <is>
+          <t>Corporate/IR contact from announcement; not a verified project purchasing contact.</t>
+        </is>
+      </c>
       <c r="L59" s="54" t="n"/>
-      <c r="M59" s="54" t="n"/>
+      <c r="M59" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="54" t="inlineStr">
@@ -54235,9 +54929,17 @@
       </c>
       <c r="I60" s="54" t="n"/>
       <c r="J60" s="54" t="n"/>
-      <c r="K60" s="54" t="n"/>
+      <c r="K60" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L60" s="54" t="n"/>
-      <c r="M60" s="54" t="n"/>
+      <c r="M60" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="54" t="inlineStr">
@@ -54278,9 +54980,17 @@
       </c>
       <c r="I61" s="54" t="n"/>
       <c r="J61" s="54" t="n"/>
-      <c r="K61" s="54" t="n"/>
+      <c r="K61" s="54" t="inlineStr">
+        <is>
+          <t>Municipal contact; not CPV procurement.</t>
+        </is>
+      </c>
       <c r="L61" s="54" t="n"/>
-      <c r="M61" s="54" t="n"/>
+      <c r="M61" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="54" t="inlineStr">
@@ -54319,11 +55029,31 @@
           <t>Developer presentation (dated)</t>
         </is>
       </c>
-      <c r="I62" s="54" t="n"/>
-      <c r="J62" s="54" t="n"/>
-      <c r="K62" s="54" t="n"/>
-      <c r="L62" s="54" t="n"/>
-      <c r="M62" s="54" t="n"/>
+      <c r="I62" s="54" t="inlineStr">
+        <is>
+          <t>jkinnamon@emberclear.com</t>
+        </is>
+      </c>
+      <c r="J62" s="54" t="inlineStr">
+        <is>
+          <t>+1 405-285-0220</t>
+        </is>
+      </c>
+      <c r="K62" s="54" t="inlineStr">
+        <is>
+          <t>Historical developer fact-sheet contact; current role corroborated, channel validity not tested.</t>
+        </is>
+      </c>
+      <c r="L62" s="56" t="inlineStr">
+        <is>
+          <t>https://www.thriveinspi.org/resources/a6e96b79-67aa-448a-8fd1-54b1f1430d3a/llec%20fact%20sheet.pdf?trackid=llec+fact+sheet.pdf | https://emberclear.com/about-us/</t>
+        </is>
+      </c>
+      <c r="M62" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="54" t="inlineStr">
@@ -54364,9 +55094,17 @@
       </c>
       <c r="I63" s="54" t="n"/>
       <c r="J63" s="54" t="n"/>
-      <c r="K63" s="54" t="n"/>
+      <c r="K63" s="54" t="inlineStr">
+        <is>
+          <t>Regulator/media contact; not project procurement.</t>
+        </is>
+      </c>
       <c r="L63" s="54" t="n"/>
-      <c r="M63" s="54" t="n"/>
+      <c r="M63" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="54" t="inlineStr">
@@ -54407,9 +55145,17 @@
       </c>
       <c r="I64" s="54" t="n"/>
       <c r="J64" s="54" t="n"/>
-      <c r="K64" s="54" t="n"/>
+      <c r="K64" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L64" s="54" t="n"/>
-      <c r="M64" s="54" t="n"/>
+      <c r="M64" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="54" t="inlineStr">
@@ -54450,9 +55196,17 @@
       </c>
       <c r="I65" s="54" t="n"/>
       <c r="J65" s="54" t="n"/>
-      <c r="K65" s="54" t="n"/>
+      <c r="K65" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L65" s="54" t="n"/>
-      <c r="M65" s="54" t="n"/>
+      <c r="M65" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="54" t="inlineStr">
@@ -54493,9 +55247,17 @@
       </c>
       <c r="I66" s="54" t="n"/>
       <c r="J66" s="54" t="n"/>
-      <c r="K66" s="54" t="n"/>
+      <c r="K66" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L66" s="54" t="n"/>
-      <c r="M66" s="54" t="n"/>
+      <c r="M66" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="54" t="inlineStr">
@@ -54536,9 +55298,17 @@
       </c>
       <c r="I67" s="54" t="n"/>
       <c r="J67" s="54" t="n"/>
-      <c r="K67" s="54" t="n"/>
+      <c r="K67" s="54" t="inlineStr">
+        <is>
+          <t>VP Power Generation role corroborated by owner release; direct email/phone not found.</t>
+        </is>
+      </c>
       <c r="L67" s="54" t="n"/>
-      <c r="M67" s="54" t="n"/>
+      <c r="M67" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="54" t="inlineStr">
@@ -54579,9 +55349,17 @@
       </c>
       <c r="I68" s="54" t="n"/>
       <c r="J68" s="54" t="n"/>
-      <c r="K68" s="54" t="n"/>
+      <c r="K68" s="54" t="inlineStr">
+        <is>
+          <t>Original suggested contact; direct email/phone and current project buying authority not verified unless specified below.</t>
+        </is>
+      </c>
       <c r="L68" s="54" t="n"/>
-      <c r="M68" s="54" t="n"/>
+      <c r="M68" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="54" t="inlineStr">
@@ -54622,9 +55400,17 @@
       </c>
       <c r="I69" s="54" t="n"/>
       <c r="J69" s="54" t="n"/>
-      <c r="K69" s="54" t="n"/>
+      <c r="K69" s="54" t="inlineStr">
+        <is>
+          <t>COO role corroborated by owner release; direct email/phone not found.</t>
+        </is>
+      </c>
       <c r="L69" s="54" t="n"/>
-      <c r="M69" s="54" t="n"/>
+      <c r="M69" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="54" t="inlineStr">
@@ -54755,6 +55541,1184 @@
         </is>
       </c>
       <c r="M71" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="54" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center</t>
+        </is>
+      </c>
+      <c r="B72" s="54" t="inlineStr">
+        <is>
+          <t>Plant office</t>
+        </is>
+      </c>
+      <c r="C72" s="54" t="inlineStr">
+        <is>
+          <t>Office contact</t>
+        </is>
+      </c>
+      <c r="D72" s="54" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center</t>
+        </is>
+      </c>
+      <c r="E72" s="54" t="inlineStr">
+        <is>
+          <t>Shared project office</t>
+        </is>
+      </c>
+      <c r="F72" s="54" t="inlineStr">
+        <is>
+          <t>trumbullamc@trumbullamc.com; +1 724-591-5549</t>
+        </is>
+      </c>
+      <c r="G72" s="56" t="inlineStr">
+        <is>
+          <t>https://www.trumbullenergycenter.com/</t>
+        </is>
+      </c>
+      <c r="H72" s="54" t="inlineStr">
+        <is>
+          <t>Shared project office</t>
+        </is>
+      </c>
+      <c r="I72" s="54" t="inlineStr">
+        <is>
+          <t>trumbullamc@trumbullamc.com</t>
+        </is>
+      </c>
+      <c r="J72" s="54" t="inlineStr">
+        <is>
+          <t>+1 724-591-5549</t>
+        </is>
+      </c>
+      <c r="K72" s="54" t="inlineStr">
+        <is>
+          <t>Shared project office</t>
+        </is>
+      </c>
+      <c r="L72" s="56" t="inlineStr">
+        <is>
+          <t>https://www.trumbullenergycenter.com/</t>
+        </is>
+      </c>
+      <c r="M72" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="54" t="inlineStr">
+        <is>
+          <t>Socrates South / North</t>
+        </is>
+      </c>
+      <c r="B73" s="54" t="inlineStr">
+        <is>
+          <t>Project outreach</t>
+        </is>
+      </c>
+      <c r="C73" s="54" t="inlineStr">
+        <is>
+          <t>Project inquiries</t>
+        </is>
+      </c>
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="E73" s="54" t="inlineStr">
+        <is>
+          <t>Shared project outreach; request procurement introduction</t>
+        </is>
+      </c>
+      <c r="F73" s="54" t="inlineStr">
+        <is>
+          <t>outreach@williams.com; +1 888-275-9084</t>
+        </is>
+      </c>
+      <c r="G73" s="56" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/</t>
+        </is>
+      </c>
+      <c r="H73" s="54" t="inlineStr">
+        <is>
+          <t>Shared project outreach; request procurement introduction</t>
+        </is>
+      </c>
+      <c r="I73" s="54" t="inlineStr">
+        <is>
+          <t>outreach@williams.com</t>
+        </is>
+      </c>
+      <c r="J73" s="54" t="inlineStr">
+        <is>
+          <t>+1 888-275-9084</t>
+        </is>
+      </c>
+      <c r="K73" s="54" t="inlineStr">
+        <is>
+          <t>Shared project outreach; request procurement introduction</t>
+        </is>
+      </c>
+      <c r="L73" s="56" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/</t>
+        </is>
+      </c>
+      <c r="M73" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="54" t="inlineStr">
+        <is>
+          <t>Homer City Energy Campus</t>
+        </is>
+      </c>
+      <c r="B74" s="54" t="inlineStr">
+        <is>
+          <t>Construction vendor team</t>
+        </is>
+      </c>
+      <c r="C74" s="54" t="inlineStr">
+        <is>
+          <t>Vendor inquiries</t>
+        </is>
+      </c>
+      <c r="D74" s="54" t="inlineStr">
+        <is>
+          <t>Kiewit</t>
+        </is>
+      </c>
+      <c r="E74" s="54" t="inlineStr">
+        <is>
+          <t>Project-specific construction vendor email; phone not found</t>
+        </is>
+      </c>
+      <c r="F74" s="54" t="inlineStr">
+        <is>
+          <t>HomerCity.Info@Kiewit.com</t>
+        </is>
+      </c>
+      <c r="G74" s="56" t="inlineStr">
+        <is>
+          <t>https://www.homercityredevelopment.com/faq</t>
+        </is>
+      </c>
+      <c r="H74" s="54" t="inlineStr">
+        <is>
+          <t>Project-specific construction vendor email; phone not found</t>
+        </is>
+      </c>
+      <c r="I74" s="54" t="inlineStr">
+        <is>
+          <t>HomerCity.Info@Kiewit.com</t>
+        </is>
+      </c>
+      <c r="J74" s="54" t="n"/>
+      <c r="K74" s="54" t="inlineStr">
+        <is>
+          <t>Project-specific construction vendor email; phone not found</t>
+        </is>
+      </c>
+      <c r="L74" s="56" t="inlineStr">
+        <is>
+          <t>https://www.homercityredevelopment.com/faq</t>
+        </is>
+      </c>
+      <c r="M74" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="54" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B75" s="54" t="inlineStr">
+        <is>
+          <t>Tommy Hodges</t>
+        </is>
+      </c>
+      <c r="C75" s="54" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="D75" s="54" t="inlineStr">
+        <is>
+          <t>SL Energy Power Plant I LLC</t>
+        </is>
+      </c>
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>Named applicant representative; 2025 regulatory filing; direct phone not found</t>
+        </is>
+      </c>
+      <c r="F75" s="54" t="inlineStr">
+        <is>
+          <t>tommyh@slenergyco.com</t>
+        </is>
+      </c>
+      <c r="G75" s="56" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/agendas/backup/2025/2025-1310-air-picr.pdf</t>
+        </is>
+      </c>
+      <c r="H75" s="54" t="inlineStr">
+        <is>
+          <t>Named applicant representative; 2025 regulatory filing; direct phone not found</t>
+        </is>
+      </c>
+      <c r="I75" s="54" t="inlineStr">
+        <is>
+          <t>tommyh@slenergyco.com</t>
+        </is>
+      </c>
+      <c r="J75" s="54" t="n"/>
+      <c r="K75" s="54" t="inlineStr">
+        <is>
+          <t>Named applicant representative; 2025 regulatory filing; direct phone not found</t>
+        </is>
+      </c>
+      <c r="L75" s="56" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/agendas/backup/2025/2025-1310-air-picr.pdf</t>
+        </is>
+      </c>
+      <c r="M75" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="54" t="inlineStr">
+        <is>
+          <t>Cedar Bayou Unit 5</t>
+        </is>
+      </c>
+      <c r="B76" s="54" t="inlineStr">
+        <is>
+          <t>Dudley D. Zahn</t>
+        </is>
+      </c>
+      <c r="C76" s="54" t="inlineStr">
+        <is>
+          <t>Owner contact — project building registration</t>
+        </is>
+      </c>
+      <c r="D76" s="54" t="inlineStr">
+        <is>
+          <t>NRG / Cedar Bayou 5 LLC</t>
+        </is>
+      </c>
+      <c r="E76" s="54" t="inlineStr">
+        <is>
+          <t>2026 project phone; HISTORICAL EMAIL — reconfirm</t>
+        </is>
+      </c>
+      <c r="F76" s="54" t="inlineStr">
+        <is>
+          <t>Dudley.Zahn@nrg.com; +1 713-537-3290</t>
+        </is>
+      </c>
+      <c r="G76" s="56" t="inlineStr">
+        <is>
+          <t>https://www.tdlr.texas.gov/TABS/Search/Print/TABS2026016466 | https://www.nrg.com/assets/documents/case-studies/elbow-battery/2021-operation-phase-annual-report.pdf</t>
+        </is>
+      </c>
+      <c r="H76" s="54" t="inlineStr">
+        <is>
+          <t>2026 project phone; HISTORICAL EMAIL — reconfirm</t>
+        </is>
+      </c>
+      <c r="I76" s="54" t="inlineStr">
+        <is>
+          <t>Dudley.Zahn@nrg.com</t>
+        </is>
+      </c>
+      <c r="J76" s="54" t="inlineStr">
+        <is>
+          <t>+1 713-537-3290</t>
+        </is>
+      </c>
+      <c r="K76" s="54" t="inlineStr">
+        <is>
+          <t>2026 project phone; HISTORICAL EMAIL — reconfirm</t>
+        </is>
+      </c>
+      <c r="L76" s="56" t="inlineStr">
+        <is>
+          <t>https://www.tdlr.texas.gov/TABS/Search/Print/TABS2026016466 | https://www.nrg.com/assets/documents/case-studies/elbow-battery/2021-operation-phase-annual-report.pdf</t>
+        </is>
+      </c>
+      <c r="M76" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="54" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch / Shay / Oregon</t>
+        </is>
+      </c>
+      <c r="B77" s="54" t="inlineStr">
+        <is>
+          <t>Sam Loftus</t>
+        </is>
+      </c>
+      <c r="C77" s="54" t="inlineStr">
+        <is>
+          <t>Director, Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D77" s="54" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="E77" s="54" t="inlineStr">
+        <is>
+          <t>MEDIA / communications only; not project procurement</t>
+        </is>
+      </c>
+      <c r="F77" s="54" t="inlineStr">
+        <is>
+          <t>sloftus@cpv.com; +1 617-347-8094</t>
+        </is>
+      </c>
+      <c r="G77" s="56" t="inlineStr">
+        <is>
+          <t>https://cpv.com/2026/08/12/cpv-secures-10-year-gas-netback-with-eqt-to-supply-2-gw-cpv-shay-energy-center/ | https://cpv.com/2025/10/30/cpv-basin-ranch-and-texas-energy-fund-ink-deal-for-1350-mw-ercot-project/</t>
+        </is>
+      </c>
+      <c r="H77" s="54" t="inlineStr">
+        <is>
+          <t>MEDIA / communications only; not project procurement</t>
+        </is>
+      </c>
+      <c r="I77" s="54" t="inlineStr">
+        <is>
+          <t>sloftus@cpv.com</t>
+        </is>
+      </c>
+      <c r="J77" s="54" t="inlineStr">
+        <is>
+          <t>+1 617-347-8094</t>
+        </is>
+      </c>
+      <c r="K77" s="54" t="inlineStr">
+        <is>
+          <t>MEDIA / communications only; not project procurement</t>
+        </is>
+      </c>
+      <c r="L77" s="56" t="inlineStr">
+        <is>
+          <t>https://cpv.com/2026/08/12/cpv-secures-10-year-gas-netback-with-eqt-to-supply-2-gw-cpv-shay-energy-center/ | https://cpv.com/2025/10/30/cpv-basin-ranch-and-texas-energy-fund-ink-deal-for-1350-mw-ercot-project/</t>
+        </is>
+      </c>
+      <c r="M77" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="54" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B78" s="54" t="inlineStr">
+        <is>
+          <t>Birju Vasani</t>
+        </is>
+      </c>
+      <c r="C78" s="54" t="inlineStr">
+        <is>
+          <t>Procurement prequalification contact</t>
+        </is>
+      </c>
+      <c r="D78" s="54" t="inlineStr">
+        <is>
+          <t>Bechtel</t>
+        </is>
+      </c>
+      <c r="E78" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 procurement; May 18, 2026 report; phone not published</t>
+        </is>
+      </c>
+      <c r="F78" s="54" t="inlineStr">
+        <is>
+          <t>bvasani@bechtel.com</t>
+        </is>
+      </c>
+      <c r="G78" s="56" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="H78" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 procurement; May 18, 2026 report; phone not published</t>
+        </is>
+      </c>
+      <c r="I78" s="54" t="inlineStr">
+        <is>
+          <t>bvasani@bechtel.com</t>
+        </is>
+      </c>
+      <c r="J78" s="54" t="n"/>
+      <c r="K78" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 procurement; May 18, 2026 report; phone not published</t>
+        </is>
+      </c>
+      <c r="L78" s="56" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="M78" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="54" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B79" s="54" t="inlineStr">
+        <is>
+          <t>Mark Bingaman</t>
+        </is>
+      </c>
+      <c r="C79" s="54" t="inlineStr">
+        <is>
+          <t>Subcontracts prequalification contact</t>
+        </is>
+      </c>
+      <c r="D79" s="54" t="inlineStr">
+        <is>
+          <t>Bechtel</t>
+        </is>
+      </c>
+      <c r="E79" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 subcontracts; May 18, 2026 report</t>
+        </is>
+      </c>
+      <c r="F79" s="54" t="inlineStr">
+        <is>
+          <t>mabingam@bechtel.com; +1 713-235-1662</t>
+        </is>
+      </c>
+      <c r="G79" s="56" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="H79" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 subcontracts; May 18, 2026 report</t>
+        </is>
+      </c>
+      <c r="I79" s="54" t="inlineStr">
+        <is>
+          <t>mabingam@bechtel.com</t>
+        </is>
+      </c>
+      <c r="J79" s="54" t="inlineStr">
+        <is>
+          <t>+1 713-235-1662</t>
+        </is>
+      </c>
+      <c r="K79" s="54" t="inlineStr">
+        <is>
+          <t>Kilby job 26776 subcontracts; May 18, 2026 report</t>
+        </is>
+      </c>
+      <c r="L79" s="56" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="M79" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="54" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B80" s="54" t="inlineStr">
+        <is>
+          <t>Kilby project team</t>
+        </is>
+      </c>
+      <c r="C80" s="54" t="inlineStr">
+        <is>
+          <t>General project inquiries</t>
+        </is>
+      </c>
+      <c r="D80" s="54" t="inlineStr">
+        <is>
+          <t>Energy Forge One LLC</t>
+        </is>
+      </c>
+      <c r="E80" s="54" t="inlineStr">
+        <is>
+          <t>Shared project email; procurement contacts listed separately</t>
+        </is>
+      </c>
+      <c r="F80" s="54" t="inlineStr">
+        <is>
+          <t>Info@kilby.com</t>
+        </is>
+      </c>
+      <c r="G80" s="56" t="inlineStr">
+        <is>
+          <t>https://kilby.com/contact/</t>
+        </is>
+      </c>
+      <c r="H80" s="54" t="inlineStr">
+        <is>
+          <t>Shared project email; procurement contacts listed separately</t>
+        </is>
+      </c>
+      <c r="I80" s="54" t="inlineStr">
+        <is>
+          <t>Info@kilby.com</t>
+        </is>
+      </c>
+      <c r="J80" s="54" t="n"/>
+      <c r="K80" s="54" t="inlineStr">
+        <is>
+          <t>Shared project email; procurement contacts listed separately</t>
+        </is>
+      </c>
+      <c r="L80" s="56" t="inlineStr">
+        <is>
+          <t>https://kilby.com/contact/</t>
+        </is>
+      </c>
+      <c r="M80" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="54" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B81" s="54" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="C81" s="54" t="inlineStr">
+        <is>
+          <t>Company inquiries</t>
+        </is>
+      </c>
+      <c r="D81" s="54" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="E81" s="54" t="inlineStr">
+        <is>
+          <t>Shared office route; request project-specific buyer</t>
+        </is>
+      </c>
+      <c r="F81" s="54" t="inlineStr">
+        <is>
+          <t>inquiries@fic-services.com; +1 716-447-7587</t>
+        </is>
+      </c>
+      <c r="G81" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H81" s="54" t="inlineStr">
+        <is>
+          <t>Shared office route; request project-specific buyer</t>
+        </is>
+      </c>
+      <c r="I81" s="54" t="inlineStr">
+        <is>
+          <t>inquiries@fic-services.com</t>
+        </is>
+      </c>
+      <c r="J81" s="54" t="inlineStr">
+        <is>
+          <t>+1 716-447-7587</t>
+        </is>
+      </c>
+      <c r="K81" s="54" t="inlineStr">
+        <is>
+          <t>Shared office route; request project-specific buyer</t>
+        </is>
+      </c>
+      <c r="L81" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M81" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="54" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B82" s="54" t="inlineStr">
+        <is>
+          <t>Peter Violante</t>
+        </is>
+      </c>
+      <c r="C82" s="54" t="inlineStr">
+        <is>
+          <t>Director, Logistics &amp; Business Development</t>
+        </is>
+      </c>
+      <c r="D82" s="54" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="E82" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="F82" s="54" t="inlineStr">
+        <is>
+          <t>pviolante@fic-services.com; +1 716-523-2813</t>
+        </is>
+      </c>
+      <c r="G82" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H82" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="I82" s="54" t="inlineStr">
+        <is>
+          <t>pviolante@fic-services.com</t>
+        </is>
+      </c>
+      <c r="J82" s="54" t="inlineStr">
+        <is>
+          <t>+1 716-523-2813</t>
+        </is>
+      </c>
+      <c r="K82" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="L82" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M82" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="54" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B83" s="54" t="inlineStr">
+        <is>
+          <t>Anthony Basil</t>
+        </is>
+      </c>
+      <c r="C83" s="54" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="D83" s="54" t="inlineStr">
+        <is>
+          <t>Frontier</t>
+        </is>
+      </c>
+      <c r="E83" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="F83" s="54" t="inlineStr">
+        <is>
+          <t>abasil@fic-services.com; +1 304-914-7716</t>
+        </is>
+      </c>
+      <c r="G83" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H83" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="I83" s="54" t="inlineStr">
+        <is>
+          <t>abasil@fic-services.com</t>
+        </is>
+      </c>
+      <c r="J83" s="54" t="inlineStr">
+        <is>
+          <t>+1 304-914-7716</t>
+        </is>
+      </c>
+      <c r="K83" s="54" t="inlineStr">
+        <is>
+          <t>Published company business contact; Shippingport assignment not confirmed</t>
+        </is>
+      </c>
+      <c r="L83" s="56" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M83" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="54" t="inlineStr">
+        <is>
+          <t>VPN 4420 Natural Gas Generation Component</t>
+        </is>
+      </c>
+      <c r="B84" s="54" t="inlineStr">
+        <is>
+          <t>Mark Siffin</t>
+        </is>
+      </c>
+      <c r="C84" s="54" t="inlineStr">
+        <is>
+          <t>CEO / project business contact</t>
+        </is>
+      </c>
+      <c r="D84" s="54" t="inlineStr">
+        <is>
+          <t>Maefield Development / VPN 4420 LLC</t>
+        </is>
+      </c>
+      <c r="E84" s="54" t="inlineStr">
+        <is>
+          <t>2024 compliance report posted 2026; current project status to confirm</t>
+        </is>
+      </c>
+      <c r="F84" s="54" t="inlineStr">
+        <is>
+          <t>siffin@maefield.com; +1 347-703-0093</t>
+        </is>
+      </c>
+      <c r="G84" s="56" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/dat/ch313/1993/01993-772-2024-0812-MCA-195901-PBT.pdf | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-app.pdf | https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993</t>
+        </is>
+      </c>
+      <c r="H84" s="54" t="inlineStr">
+        <is>
+          <t>2024 compliance report posted 2026; current project status to confirm</t>
+        </is>
+      </c>
+      <c r="I84" s="54" t="inlineStr">
+        <is>
+          <t>siffin@maefield.com</t>
+        </is>
+      </c>
+      <c r="J84" s="54" t="inlineStr">
+        <is>
+          <t>+1 347-703-0093</t>
+        </is>
+      </c>
+      <c r="K84" s="54" t="inlineStr">
+        <is>
+          <t>2024 compliance report posted 2026; current project status to confirm</t>
+        </is>
+      </c>
+      <c r="L84" s="56" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/dat/ch313/1993/01993-772-2024-0812-MCA-195901-PBT.pdf | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-app.pdf | https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993</t>
+        </is>
+      </c>
+      <c r="M84" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="54" t="inlineStr">
+        <is>
+          <t>Sandow Lakes / Basin Ranch / Trumbull</t>
+        </is>
+      </c>
+      <c r="B85" s="54" t="inlineStr">
+        <is>
+          <t>Business office</t>
+        </is>
+      </c>
+      <c r="C85" s="54" t="inlineStr">
+        <is>
+          <t>General business inquiries</t>
+        </is>
+      </c>
+      <c r="D85" s="54" t="inlineStr">
+        <is>
+          <t>Gemma Power Systems</t>
+        </is>
+      </c>
+      <c r="E85" s="54" t="inlineStr">
+        <is>
+          <t>Main office only; email not found; contact form available</t>
+        </is>
+      </c>
+      <c r="F85" s="54" t="inlineStr">
+        <is>
+          <t>+1 860-659-0509</t>
+        </is>
+      </c>
+      <c r="G85" s="56" t="inlineStr">
+        <is>
+          <t>https://www.gemmapower.com/contact/</t>
+        </is>
+      </c>
+      <c r="H85" s="54" t="inlineStr">
+        <is>
+          <t>Main office only; email not found; contact form available</t>
+        </is>
+      </c>
+      <c r="I85" s="54" t="n"/>
+      <c r="J85" s="54" t="inlineStr">
+        <is>
+          <t>+1 860-659-0509</t>
+        </is>
+      </c>
+      <c r="K85" s="54" t="inlineStr">
+        <is>
+          <t>Main office only; email not found; contact form available</t>
+        </is>
+      </c>
+      <c r="L85" s="56" t="inlineStr">
+        <is>
+          <t>https://www.gemmapower.com/contact/</t>
+        </is>
+      </c>
+      <c r="M85" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="54" t="inlineStr">
+        <is>
+          <t>Plant Yates Unit 9 (Yates CT Units 8-10)</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="inlineStr">
+        <is>
+          <t>Supplier portal support</t>
+        </is>
+      </c>
+      <c r="C86" s="54" t="inlineStr">
+        <is>
+          <t>Supplier access support</t>
+        </is>
+      </c>
+      <c r="D86" s="54" t="inlineStr">
+        <is>
+          <t>Black &amp; Veatch</t>
+        </is>
+      </c>
+      <c r="E86" s="54" t="inlineStr">
+        <is>
+          <t>Email is portal support; phone is main office; neither is Rick Anderson direct</t>
+        </is>
+      </c>
+      <c r="F86" s="54" t="inlineStr">
+        <is>
+          <t>BVAPSUPPMAINT@bv.com; +1 913-458-2000</t>
+        </is>
+      </c>
+      <c r="G86" s="56" t="inlineStr">
+        <is>
+          <t>https://cdn.bfldr.com/E1EVDN8O/at/bz4ct6npstkxw48b6n9zm9j8/Oracle_Cloud_Azure_MFA_Registration_Step_Guide_19Jun2024.pdf | https://www.bv.com/en-US/contact-us | https://www.bv.com/en-US/suppliers</t>
+        </is>
+      </c>
+      <c r="H86" s="54" t="inlineStr">
+        <is>
+          <t>Email is portal support; phone is main office; neither is Rick Anderson direct</t>
+        </is>
+      </c>
+      <c r="I86" s="54" t="inlineStr">
+        <is>
+          <t>BVAPSUPPMAINT@bv.com</t>
+        </is>
+      </c>
+      <c r="J86" s="54" t="inlineStr">
+        <is>
+          <t>+1 913-458-2000</t>
+        </is>
+      </c>
+      <c r="K86" s="54" t="inlineStr">
+        <is>
+          <t>Email is portal support; phone is main office; neither is Rick Anderson direct</t>
+        </is>
+      </c>
+      <c r="L86" s="56" t="inlineStr">
+        <is>
+          <t>https://cdn.bfldr.com/E1EVDN8O/at/bz4ct6npstkxw48b6n9zm9j8/Oracle_Cloud_Azure_MFA_Registration_Step_Guide_19Jun2024.pdf | https://www.bv.com/en-US/contact-us | https://www.bv.com/en-US/suppliers</t>
+        </is>
+      </c>
+      <c r="M86" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="54" t="inlineStr">
+        <is>
+          <t>Person County Combined Cycle 1 (CC1)</t>
+        </is>
+      </c>
+      <c r="B87" s="54" t="inlineStr">
+        <is>
+          <t>Business office / procurement registration</t>
+        </is>
+      </c>
+      <c r="C87" s="54" t="inlineStr">
+        <is>
+          <t>Supplier routing</t>
+        </is>
+      </c>
+      <c r="D87" s="54" t="inlineStr">
+        <is>
+          <t>Zachry Group</t>
+        </is>
+      </c>
+      <c r="E87" s="54" t="inlineStr">
+        <is>
+          <t>Main office phone; use procurement registration form; buyer email missing</t>
+        </is>
+      </c>
+      <c r="F87" s="54" t="inlineStr">
+        <is>
+          <t>+1 210-588-5000</t>
+        </is>
+      </c>
+      <c r="G87" s="56" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/procurement | https://zachrygroup.com/about</t>
+        </is>
+      </c>
+      <c r="H87" s="54" t="inlineStr">
+        <is>
+          <t>Main office phone; use procurement registration form; buyer email missing</t>
+        </is>
+      </c>
+      <c r="I87" s="54" t="n"/>
+      <c r="J87" s="54" t="inlineStr">
+        <is>
+          <t>+1 210-588-5000</t>
+        </is>
+      </c>
+      <c r="K87" s="54" t="inlineStr">
+        <is>
+          <t>Main office phone; use procurement registration form; buyer email missing</t>
+        </is>
+      </c>
+      <c r="L87" s="56" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/procurement | https://zachrygroup.com/about</t>
+        </is>
+      </c>
+      <c r="M87" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="54" t="inlineStr">
+        <is>
+          <t>AES Petersburg Unit 4 Repowered</t>
+        </is>
+      </c>
+      <c r="B88" s="54" t="inlineStr">
+        <is>
+          <t>B&amp;W Construction office</t>
+        </is>
+      </c>
+      <c r="C88" s="54" t="inlineStr">
+        <is>
+          <t>Business office</t>
+        </is>
+      </c>
+      <c r="D88" s="54" t="inlineStr">
+        <is>
+          <t>BWCC</t>
+        </is>
+      </c>
+      <c r="E88" s="54" t="inlineStr">
+        <is>
+          <t>Business office, not a named Petersburg buyer; email missing</t>
+        </is>
+      </c>
+      <c r="F88" s="54" t="inlineStr">
+        <is>
+          <t>+1 330-753-9750</t>
+        </is>
+      </c>
+      <c r="G88" s="56" t="inlineStr">
+        <is>
+          <t>https://www.babcock.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H88" s="54" t="inlineStr">
+        <is>
+          <t>Business office, not a named Petersburg buyer; email missing</t>
+        </is>
+      </c>
+      <c r="I88" s="54" t="n"/>
+      <c r="J88" s="54" t="inlineStr">
+        <is>
+          <t>+1 330-753-9750</t>
+        </is>
+      </c>
+      <c r="K88" s="54" t="inlineStr">
+        <is>
+          <t>Business office, not a named Petersburg buyer; email missing</t>
+        </is>
+      </c>
+      <c r="L88" s="56" t="inlineStr">
+        <is>
+          <t>https://www.babcock.com/contact-us</t>
+        </is>
+      </c>
+      <c r="M88" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="54" t="inlineStr">
+        <is>
+          <t>Lincoln Land Energy Center (LLEC)</t>
+        </is>
+      </c>
+      <c r="B89" s="54" t="inlineStr">
+        <is>
+          <t>EmberClear office</t>
+        </is>
+      </c>
+      <c r="C89" s="54" t="inlineStr">
+        <is>
+          <t>Company inquiries</t>
+        </is>
+      </c>
+      <c r="D89" s="54" t="inlineStr">
+        <is>
+          <t>EmberClear</t>
+        </is>
+      </c>
+      <c r="E89" s="54" t="inlineStr">
+        <is>
+          <t>Current shared Houston office route; historical Kinnamon details separately labeled</t>
+        </is>
+      </c>
+      <c r="F89" s="54" t="inlineStr">
+        <is>
+          <t>contact@emberclear.com; +1 888-582-4460</t>
+        </is>
+      </c>
+      <c r="G89" s="56" t="inlineStr">
+        <is>
+          <t>https://emberclear.com/lincoln-land-2/</t>
+        </is>
+      </c>
+      <c r="H89" s="54" t="inlineStr">
+        <is>
+          <t>Current shared Houston office route; historical Kinnamon details separately labeled</t>
+        </is>
+      </c>
+      <c r="I89" s="54" t="inlineStr">
+        <is>
+          <t>contact@emberclear.com</t>
+        </is>
+      </c>
+      <c r="J89" s="54" t="inlineStr">
+        <is>
+          <t>+1 888-582-4460</t>
+        </is>
+      </c>
+      <c r="K89" s="54" t="inlineStr">
+        <is>
+          <t>Current shared Houston office route; historical Kinnamon details separately labeled</t>
+        </is>
+      </c>
+      <c r="L89" s="56" t="inlineStr">
+        <is>
+          <t>https://emberclear.com/lincoln-land-2/</t>
+        </is>
+      </c>
+      <c r="M89" s="54" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
@@ -54815,29 +56779,68 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54849,7 +56852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -54862,90 +56865,97 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
-        <is>
-          <t>Stephan Hardt | Power Generation — Verification • 29 October 2026</t>
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>Stephan Hardt | Power Generation — Research review • 29 October 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11 records reviewed • 9 have a published email + phone route (direct, shared project or supplier support); 2 still need a suitable contact pair.</t>
+          <t>26 project records reviewed, including 15 additions • Sources, capacity differences, contact gaps and follow-up actions are documented below.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Publication checks only; no calls or emails sent. Exact unsupported commissioning dates cleared. Close dates, cable values and buying windows remain sales assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="53" t="n"/>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="53" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="53" t="n"/>
-      <c r="J4" s="53" t="n"/>
-    </row>
+          <t>Publication checks only; contacts not called or emailed. Targets are not guaranteed CODs. Close/award dates and $8/kW cable values remain sales assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Verified status</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Timing / precision</t>
         </is>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Capacity reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Facts checked</t>
         </is>
       </c>
-      <c r="F5" s="54" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>Required follow-up</t>
         </is>
       </c>
-      <c r="G5" s="54" t="inlineStr">
+      <c r="G5" s="53" t="inlineStr">
         <is>
           <t>Primary source</t>
         </is>
       </c>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>Contact route</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="J5" s="53" t="inlineStr">
         <is>
           <t>Phone</t>
+        </is>
+      </c>
+      <c r="K5" s="53" t="inlineStr">
+        <is>
+          <t>Contact source(s)</t>
+        </is>
+      </c>
+      <c r="L5" s="53" t="inlineStr">
+        <is>
+          <t>Contact qualification / gap</t>
+        </is>
+      </c>
+      <c r="M5" s="53" t="inlineStr">
+        <is>
+          <t>Checked on</t>
         </is>
       </c>
     </row>
@@ -54987,7 +56997,7 @@
       </c>
       <c r="H6" s="54" t="inlineStr">
         <is>
-          <t>Daniel Birmingham — published business contact; Wisconsin DNR listing is for another Invenergy project</t>
+          <t>Daniel Birmingham — published business contact (cross-project DNR filing)</t>
         </is>
       </c>
       <c r="I6" s="54" t="inlineStr">
@@ -54998,6 +57008,21 @@
       <c r="J6" s="54" t="inlineStr">
         <is>
           <t>+1 312-582-1094</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://apps.dnr.wi.gov/warp_ext/am_permittracking2.aspx?id=38822</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Published direct business details; qualify project role</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55039,7 +57064,7 @@
       </c>
       <c r="H7" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I7" s="54" t="inlineStr">
@@ -55050,6 +57075,21 @@
       <c r="J7" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55091,7 +57131,7 @@
       </c>
       <c r="H8" s="54" t="inlineStr">
         <is>
-          <t>Vistra supply chain email / supplier-diversity phone — shared routing, not Jim Burke</t>
+          <t>Vistra supply chain email / supplier-diversity phone</t>
         </is>
       </c>
       <c r="I8" s="54" t="inlineStr">
@@ -55102,6 +57142,21 @@
       <c r="J8" s="54" t="inlineStr">
         <is>
           <t>+1 214-812-8000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://vistracorp.com/supply-chain/how-do-we-source/ | https://vistracorp.com/supply-chain/faq/</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Two shared departments; named buyer missing</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55118,17 +57173,17 @@
       </c>
       <c r="C9" s="54" t="inlineStr">
         <is>
-          <t>By end 2027 for all 3 units; Unit 9 day unverified</t>
+          <t>Q2 2027 Unit 9 target in Southern Company Q2 2026 filing; not an exact commissioning day.</t>
         </is>
       </c>
       <c r="D9" s="54" t="inlineStr">
         <is>
-          <t>482.8 MW retained as input nameplate; owner release reports approximately 1300 MW across 3 units. Basis needs reconciliation.</t>
+          <t>482.8 MW input nameplate retained provisionally. Southern filing lists 442 MW per new unit; reconcile gross/nameplate versus planning basis before sizing.</t>
         </is>
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Georgia Power confirms Unit 9 turbine/generator delivery in December 2025. Units 8–10 use Mitsubishi M501JAC simple-cycle turbines.</t>
+          <t>Georgia Power confirms Unit 9 turbine/generator delivery in December 2025. Units 8–10 are Mitsubishi M501JAC simple-cycle units; the Southern filing schedules Unit 8 in Q4 2026, Unit 9 in Q2 2027 and Unit 10 in Q3 2027. EPC: Black &amp; Veatch and Mitsubishi.</t>
         </is>
       </c>
       <c r="F9" s="54" t="inlineStr">
@@ -55138,16 +57193,39 @@
       </c>
       <c r="G9" s="55" t="inlineStr">
         <is>
-          <t>https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html</t>
+          <t>https://www.georgiapower.com/news-hub/press-releases/turbine-generator-unit-9-plant-yates.html | https://d18rn0p25nwr6d.cloudfront.net/CIK-0000092122/32961fa3-bbf4-4ea2-8851-611fe309e97e.pdf</t>
         </is>
       </c>
       <c r="H9" s="54" t="inlineStr">
         <is>
-          <t>Not found — action required</t>
-        </is>
-      </c>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="54" t="n"/>
+          <t>Black &amp; Veatch supplier portal support (email) / main office (phone)</t>
+        </is>
+      </c>
+      <c r="I9" s="54" t="inlineStr">
+        <is>
+          <t>BVAPSUPPMAINT@bv.com</t>
+        </is>
+      </c>
+      <c r="J9" s="54" t="inlineStr">
+        <is>
+          <t>+1 913-458-2000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://cdn.bfldr.com/E1EVDN8O/at/bz4ct6npstkxw48b6n9zm9j8/Oracle_Cloud_Azure_MFA_Registration_Step_Guide_19Jun2024.pdf | https://www.bv.com/en-US/contact-us | https://www.bv.com/en-US/suppliers</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Support only; request Yates buyer</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="54" t="inlineStr">
@@ -55187,7 +57265,7 @@
       </c>
       <c r="H10" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I10" s="54" t="inlineStr">
@@ -55198,6 +57276,21 @@
       <c r="J10" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55239,11 +57332,30 @@
       </c>
       <c r="H11" s="54" t="inlineStr">
         <is>
-          <t>Not found — action required</t>
+          <t>Zachry procurement registration / main office</t>
         </is>
       </c>
       <c r="I11" s="54" t="n"/>
-      <c r="J11" s="54" t="n"/>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>+1 210-588-5000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://zachrygroup.com/procurement | https://zachrygroup.com/about</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MISSING EMAIL — use procurement form</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="54" t="inlineStr">
@@ -55283,7 +57395,7 @@
       </c>
       <c r="H12" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I12" s="54" t="inlineStr">
@@ -55294,6 +57406,21 @@
       <c r="J12" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55335,7 +57462,7 @@
       </c>
       <c r="H13" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I13" s="54" t="inlineStr">
@@ -55346,6 +57473,21 @@
       <c r="J13" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55387,7 +57529,7 @@
       </c>
       <c r="H14" s="54" t="inlineStr">
         <is>
-          <t>Sycamore project team — shared, not John Niland</t>
+          <t>Sycamore project team — shared project contact</t>
         </is>
       </c>
       <c r="I14" s="54" t="inlineStr">
@@ -55398,6 +57540,21 @@
       <c r="J14" s="54" t="inlineStr">
         <is>
           <t>+1 800-341-2319</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://sycamoreriverside.invenergy.com/contact-us</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Shared project route; qualify buyer</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55439,7 +57596,7 @@
       </c>
       <c r="H15" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I15" s="54" t="inlineStr">
@@ -55450,6 +57607,21 @@
       <c r="J15" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55491,7 +57663,7 @@
       </c>
       <c r="H16" s="54" t="inlineStr">
         <is>
-          <t>Entergy supplier support — shared, not named lead</t>
+          <t>Entergy supplier support — shared registration/help route</t>
         </is>
       </c>
       <c r="I16" s="54" t="inlineStr">
@@ -55502,6 +57674,1014 @@
       <c r="J16" s="54" t="inlineStr">
         <is>
           <t>+1 844-387-9675</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://supplier.entergy.com/psc/supprd/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_FAQ_CMP_FL.GBL</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Shared support; project buyer missing</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>AES Petersburg Unit 4 Repowered</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Fuel conversion under construction</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
+        <is>
+          <t>Owner: December 2026; contractor's Nov 2024 release: Q1 2027. Reconfirm handover.</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>526 MW input retained provisionally; unit-4 gross/net basis not substantiated. B&amp;W quotes 1,160 MW for the two-unit conversion together.</t>
+        </is>
+      </c>
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>AES Petersburg Units 3 and 4 are existing steam units undergoing coal-to-gas boiler conversion. B&amp;W received full notice to proceed in November 2024; BWCC handles construction and B&amp;W FPS supplies burners, ignitors and controls. This is not a new gas-turbine combined-cycle plant.</t>
+        </is>
+      </c>
+      <c r="F17" s="54" t="inlineStr">
+        <is>
+          <t>Request the Unit 4 remaining electrical package list and current handover date from B&amp;W/BWCC. Confirm unit capacity before sizing. A whole-plant $8/kW benchmark does not measure the retrofit cable scope.</t>
+        </is>
+      </c>
+      <c r="G17" s="55" t="inlineStr">
+        <is>
+          <t>https://www.aesindiana.com/pike-county | https://www.babcock.com/home/about/corporate/news/babcock-and-wilcox-receives-full-notice-to-proceed-on-246-million-contract-for-indiana-power-plant-coal-to-gas-fuel-switching-project</t>
+        </is>
+      </c>
+      <c r="H17" s="54" t="inlineStr">
+        <is>
+          <t>B&amp;W Construction — business office / online inquiry form</t>
+        </is>
+      </c>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>+1 330-753-9750</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.babcock.com/contact-us</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MISSING EMAIL — named project buyer needed</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>Operating; commissioning confirmed</t>
+        </is>
+      </c>
+      <c r="C18" s="54" t="inlineStr">
+        <is>
+          <t>Commissioning/opening announced June 24, 2026; exact commercial-service date not established.</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>Updated 940 input to 950 MW maximum design capacity published by owner and EPC. Confirm seasonal net output separately.</t>
+        </is>
+      </c>
+      <c r="E18" s="54" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center is a combined-cycle facility in Lordstown, Trumbull County, Ohio. The owner describes two Siemens SGT6-8000H turbines, two HRSGs and one steam turbine. Gemma was EPC. Hanwha announced successful commissioning in June 2026.</t>
+        </is>
+      </c>
+      <c r="F18" s="54" t="inlineStr">
+        <is>
+          <t>Qualify operations, spares and outage work through the plant office; do not treat the full construction benchmark as remaining sales. January 2026 COD was not independently established.</t>
+        </is>
+      </c>
+      <c r="G18" s="55" t="inlineStr">
+        <is>
+          <t>https://www.trumbullenergycenter.com/ | https://org-www.hanwha.com/newsroom/news/press-releases/hanwha-power-enters-us-market-with-successful-commissioning-of-trumbull-energy-center-combined-cycle-gas-turbine-power-plant.do</t>
+        </is>
+      </c>
+      <c r="H18" s="54" t="inlineStr">
+        <is>
+          <t>Trumbull Energy Center office — shared</t>
+        </is>
+      </c>
+      <c r="I18" s="54" t="inlineStr">
+        <is>
+          <t>trumbullamc@trumbullamc.com</t>
+        </is>
+      </c>
+      <c r="J18" s="54" t="inlineStr">
+        <is>
+          <t>+1 724-591-5549</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://www.trumbullenergycenter.com/</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Published shared office; operations buyer needed</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>Socrates South Power Generation</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>Operating; Phase 1 in service</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>Phase 1 in service per Williams Q2 2026 results; exact day not confirmed.</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>200 MW South; 400 MW across South and North. Avoid counting the total twice.</t>
+        </is>
+      </c>
+      <c r="E19" s="54" t="inlineStr">
+        <is>
+          <t>Williams' Socrates South is one of two 200 MW behind-the-meter power facilities in the New Albany, Ohio area. Williams confirms Phase 1 was placed in service. The published project outreach email and hotline serve both facilities.</t>
+        </is>
+      </c>
+      <c r="F19" s="54" t="inlineStr">
+        <is>
+          <t>Ask the project team for the operations/electrical buyer and any unfinished scope. Keep North's new-build opportunity separate from South's operations opportunity.</t>
+        </is>
+      </c>
+      <c r="G19" s="55" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/ | https://www.williams.com/wp-content/uploads/sites/14/2026/02/Socrates-North-and-South-Fact-Sheet-1.pdf | https://investor.williams.com/static-files/dde1b8eb-5802-4e4c-aa89-84c4d8611d56</t>
+        </is>
+      </c>
+      <c r="H19" s="54" t="inlineStr">
+        <is>
+          <t>Williams Socrates project outreach — shared</t>
+        </is>
+      </c>
+      <c r="I19" s="54" t="inlineStr">
+        <is>
+          <t>outreach@williams.com</t>
+        </is>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>+1 888-275-9084</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Published project outreach; qualify buyer</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>Socrates North Power Generation</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Under construction / completion target</t>
+        </is>
+      </c>
+      <c r="C20" s="54" t="inlineStr">
+        <is>
+          <t>Q4 2026 expected for Phase 2 per Williams Q2 results; not verified as operating on review date.</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>200 MW North; 400 MW across both Socrates facilities.</t>
+        </is>
+      </c>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>Socrates North is the second 200 MW behind-the-meter power facility in Williams' Socrates development near New Albany, Ohio. The Q2 results retain a fourth-quarter 2026 service target for Phase 2.</t>
+        </is>
+      </c>
+      <c r="F20" s="54" t="inlineStr">
+        <is>
+          <t>Request the current commissioning milestone, electrical contractor and remaining cable releases from project outreach. A service target does not establish that purchase orders remain open.</t>
+        </is>
+      </c>
+      <c r="G20" s="55" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/ | https://www.williams.com/wp-content/uploads/sites/14/2026/02/Socrates-North-and-South-Fact-Sheet-1.pdf | https://investor.williams.com/static-files/dde1b8eb-5802-4e4c-aa89-84c4d8611d56</t>
+        </is>
+      </c>
+      <c r="H20" s="54" t="inlineStr">
+        <is>
+          <t>Williams Socrates project outreach — shared</t>
+        </is>
+      </c>
+      <c r="I20" s="54" t="inlineStr">
+        <is>
+          <t>outreach@williams.com</t>
+        </is>
+      </c>
+      <c r="J20" s="54" t="inlineStr">
+        <is>
+          <t>+1 888-275-9084</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.williams.com/expansion-project/socrates-power-solution-facilities/</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Published project outreach; qualify buyer</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Homer City Energy Campus</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>Construction; phased power delivery</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>Initial power targeted in 2027; this is not a verified full-campus COD.</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Updated 4,500 MW announcement figure to current owner FAQ: up to 4,400 MW. Approximate project scope, not a net dependable rating.</t>
+        </is>
+      </c>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>The Homer City redevelopment uses seven GE Vernova 7HA.02 gas turbines with Kiewit Power Constructors as EPC. The owner's current FAQ describes up to 4.4 GW and phased initial power. It publishes a Kiewit email specifically for construction vendors.</t>
+        </is>
+      </c>
+      <c r="F21" s="54" t="inlineStr">
+        <is>
+          <t>Use the construction-vendor email to obtain the project procurement contact and remaining electrical bid packages. Confirm full buildout schedule and any named data-center tenant directly; do not equate first power with full completion.</t>
+        </is>
+      </c>
+      <c r="G21" s="55" t="inlineStr">
+        <is>
+          <t>https://www.homercityredevelopment.com/faq</t>
+        </is>
+      </c>
+      <c r="H21" s="54" t="inlineStr">
+        <is>
+          <t>Kiewit Homer City construction vendors</t>
+        </is>
+      </c>
+      <c r="I21" s="54" t="inlineStr">
+        <is>
+          <t>HomerCity.Info@Kiewit.com</t>
+        </is>
+      </c>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.homercityredevelopment.com/faq</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MISSING PHONE — project vendor email verified</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Station</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>EPC execution / construction</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>2028 completion target; precise month/day unverified.</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>1,200 MW planned combined-cycle facility confirmed.</t>
+        </is>
+      </c>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>Sandow Lakes Energy Company's Lee County, Texas project is being delivered by Gemma; the April 2025 announcement confirms the 1.2 GW project. Xebec's April 2026 transaction concerned land and does not establish a sale of the power project. TCEQ identifies Ned Ross and COO Tommy Hodges as applicant representatives.</t>
+        </is>
+      </c>
+      <c r="F22" s="54" t="inlineStr">
+        <is>
+          <t>Contact Tommy Hodges by published business email or Ned Ross at the TCEQ-published number; request Gemma purchasing introductions. Reconfirm current permits and construction milestone. The input 12.2-mile transmission estimate is not a verified line scope.</t>
+        </is>
+      </c>
+      <c r="G22" s="55" t="inlineStr">
+        <is>
+          <t>https://slectx.com/argan-inc-gemma-electrify-tx/ | https://xebecrealty.com/leadership/gretchen-kendrick/ | https://www.tceq.texas.gov/downloads/agency/decisions/hearings/notices/2025/2025-04-24-sl-energy-power-plant-i-177380-pm.pdf | https://www.tceq.texas.gov/downloads/agency/decisions/agendas/backup/2025/2025-1310-air-picr.pdf</t>
+        </is>
+      </c>
+      <c r="H22" s="54" t="inlineStr">
+        <is>
+          <t>Tommy Hodges, COO (email) / Ned Ross, EVP (phone) — different people</t>
+        </is>
+      </c>
+      <c r="I22" s="54" t="inlineStr">
+        <is>
+          <t>tommyh@slenergyco.com</t>
+        </is>
+      </c>
+      <c r="J22" s="54" t="inlineStr">
+        <is>
+          <t>+1 512-887-4719</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.tceq.texas.gov/downloads/agency/decisions/agendas/backup/2025/2025-1310-air-picr.pdf | https://www.tceq.texas.gov/downloads/agency/decisions/hearings/notices/2025/2025-04-24-sl-energy-power-plant-i-177380-pm.pdf</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Split named contacts; request buyer introduction</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>Wolf Summit Energy Center</t>
+        </is>
+      </c>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>Under construction; EPCM delivery</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>December 2028 developer target.</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>Updated rounded 600 MW to Kindle's 610 MW case-study figure; project website still rounds to 600 MW.</t>
+        </is>
+      </c>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>Wolf Summit is a natural-gas combined-cycle project in Harrison County, West Virginia. Kindle reports financial close in November 2025 and an EPC management structure using its own procurement team and four key contractors. It is not awaiting a single conventional EPC award.</t>
+        </is>
+      </c>
+      <c r="F23" s="54" t="inlineStr">
+        <is>
+          <t>Route inquiries through the Wolf Summit project email/phone and ask for Kindle EPCM procurement and electrical package owners; the four contractors are not named in the case study.</t>
+        </is>
+      </c>
+      <c r="G23" s="55" t="inlineStr">
+        <is>
+          <t>https://kindle-energy.com/case-studies/wolf-summit | https://wolf-summit.com/</t>
+        </is>
+      </c>
+      <c r="H23" s="54" t="inlineStr">
+        <is>
+          <t>Wolf Summit project team — shared</t>
+        </is>
+      </c>
+      <c r="I23" s="54" t="inlineStr">
+        <is>
+          <t>info@wolf-summit.com</t>
+        </is>
+      </c>
+      <c r="J23" s="54" t="inlineStr">
+        <is>
+          <t>+1 304-576-8717</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://wolf-summit.com/</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Published project route; request Kindle procurement</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>Cedar Bayou Unit 5</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>Under construction; owner confirms progress</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="inlineStr">
+        <is>
+          <t>Mid-2028 owner target in Q2 2026 investor presentation.</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>689 MW operating capacity retained; NRG also reports 721 MW nameplate. These are different capacity bases.</t>
+        </is>
+      </c>
+      <c r="E24" s="54" t="inlineStr">
+        <is>
+          <t>NRG's Cedar Bayou 5 combined-cycle project uses a Mitsubishi M501JAC turbine. NRG's Q2 2026 materials retain the mid-2028 schedule. A March 2026 Texas building registration names Dudley D. Zahn as owner contact for the project's admin/control/warehouse work.</t>
+        </is>
+      </c>
+      <c r="F24" s="54" t="inlineStr">
+        <is>
+          <t>Dudley Zahn is a published project owner contact; reconfirm his email from a 2022 NRG filing and ask for the procurement lead. The building registration's cost and completion date apply only to the building, not the entire plant. EPC and open cable packages still need confirmation.</t>
+        </is>
+      </c>
+      <c r="G24" s="55" t="inlineStr">
+        <is>
+          <t>https://investors.nrg.com/static-files/166760ef-79e6-4985-b776-09660ed84ae9 | https://www.tdlr.texas.gov/TABS/Search/Print/TABS2026016466 | https://www.nrg.com/assets/documents/case-studies/elbow-battery/2021-operation-phase-annual-report.pdf</t>
+        </is>
+      </c>
+      <c r="H24" s="54" t="inlineStr">
+        <is>
+          <t>Dudley D. Zahn — project owner contact; email from 2022 filing</t>
+        </is>
+      </c>
+      <c r="I24" s="54" t="inlineStr">
+        <is>
+          <t>Dudley.Zahn@nrg.com</t>
+        </is>
+      </c>
+      <c r="J24" s="54" t="inlineStr">
+        <is>
+          <t>+1 713-537-3290</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.tdlr.texas.gov/TABS/Search/Print/TABS2026016466 | https://www.nrg.com/assets/documents/case-studies/elbow-battery/2021-operation-phase-annual-report.pdf</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026 project phone; HISTORICAL EMAIL — reconfirm</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch Energy Center</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>Under construction</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>2029 commercial operation target, not the input 2028 date.</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>1,350 MW confirmed by CPV.</t>
+        </is>
+      </c>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>CPV Basin Ranch is a 1,350 MW combined-cycle project in Ward County, Texas, using two GE Vernova 7HA.03 turbines in a 2x1 configuration. CPV identifies Gemma as EPC and publishes 2029 as the operational target.</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="inlineStr">
+        <is>
+          <t>Request Gemma's project purchasing contact and electrical bid schedule. CPV's Sam Loftus is a communications contact only; obtain a procurement introduction instead of treating him as the buyer.</t>
+        </is>
+      </c>
+      <c r="G25" s="55" t="inlineStr">
+        <is>
+          <t>https://cpv.com/our-fleet/cpv-basin-ranch-energy-center/ | https://cpv.com/2025/10/30/cpv-basin-ranch-and-texas-energy-fund-ink-deal-for-1350-mw-ercot-project/</t>
+        </is>
+      </c>
+      <c r="H25" s="54" t="inlineStr">
+        <is>
+          <t>Gemma business office / CPV project inquiry form</t>
+        </is>
+      </c>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="inlineStr">
+        <is>
+          <t>+1 860-659-0509</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.gemmapower.com/contact/ | https://cpv.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MISSING BUYER EMAIL — media contact in Named Contacts</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>CPV Shay Energy Center</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t>Development; construction planned</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="inlineStr">
+        <is>
+          <t>Construction expected in 2027. Input 2031 COD not corroborated in sources reviewed.</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Updated 2,060 MW from older FAQ to 2,100 MW current CPV headline/project facts and August 2026 release; approximate scope.</t>
+        </is>
+      </c>
+      <c r="E26" s="54" t="inlineStr">
+        <is>
+          <t>CPV Shay is a planned West Virginia combined-cycle project using three GE Vernova 7HA.03 turbines. In August 2026 CPV announced a ten-year gas supply arrangement with EQT. Current project materials identify approximately 2.1 GW.</t>
+        </is>
+      </c>
+      <c r="F26" s="54" t="inlineStr">
+        <is>
+          <t>Obtain the current EPC selection, financing/FID, permit status and commissioning schedule from CPV. A gas supply announcement does not confirm project construction or cable procurement.</t>
+        </is>
+      </c>
+      <c r="G26" s="55" t="inlineStr">
+        <is>
+          <t>https://cpv.com/our-fleet/cpv-shay-energy-center/ | https://cpv.com/2026/08/12/cpv-secures-10-year-gas-netback-with-eqt-to-supply-2-gw-cpv-shay-energy-center/</t>
+        </is>
+      </c>
+      <c r="H26" s="54" t="inlineStr">
+        <is>
+          <t>Sam Loftus — CPV communications ONLY; request project routing</t>
+        </is>
+      </c>
+      <c r="I26" s="54" t="inlineStr">
+        <is>
+          <t>sloftus@cpv.com</t>
+        </is>
+      </c>
+      <c r="J26" s="54" t="inlineStr">
+        <is>
+          <t>+1 617-347-8094</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://cpv.com/2026/08/12/cpv-secures-10-year-gas-netback-with-eqt-to-supply-2-gw-cpv-shay-energy-center/ | https://cpv.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MEDIA ONLY — procurement contact still missing</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>CPV Clean Energy Future - Oregon (Oregon Energy Center)</t>
+        </is>
+      </c>
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>Early development; grid route unresolved</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>No current commercial-operation date verified.</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>1,475 MW revised project scope in March 2026 parent filing; older Ohio certificate covered 955 MW.</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>Kenon's March 2026 annual filing still lists Oregon as a 1,475 MW early-development CPV project. The November 2025 filing says CPV did not pursue the accelerated PJM RRI route and was considering alternatives. Withdrawal from that route is not evidence of complete project cancellation.</t>
+        </is>
+      </c>
+      <c r="F27" s="54" t="inlineStr">
+        <is>
+          <t>Kept as Delayed/stalled: PJM queue reportedly withdrawn (Aurora Feb 2026) and OPSB certificate may have lapsed - confirm with CPV.</t>
+        </is>
+      </c>
+      <c r="G27" s="55" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1611005/000117891326001842/zk2634883.htm | https://www.sec.gov/Archives/edgar/data/1611005/000117891325003891/exhibit_99-1.htm</t>
+        </is>
+      </c>
+      <c r="H27" s="54" t="inlineStr">
+        <is>
+          <t>Sam Loftus — CPV communications ONLY; request project routing</t>
+        </is>
+      </c>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>sloftus@cpv.com</t>
+        </is>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>+1 617-347-8094</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://cpv.com/2026/08/12/cpv-secures-10-year-gas-netback-with-eqt-to-supply-2-gw-cpv-shay-energy-center/ | https://cpv.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MEDIA ONLY — procurement contact still missing</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>Lincoln Land Energy Center (LLEC)</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>Development; schedule and sponsorship need refresh</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="inlineStr">
+        <is>
+          <t>Developer webpage still shows 2027; treat as stale. July 2026 reporting cites a January 1, 2027 permit deadline; verify with developer/IEPA.</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>1,190 MW developer figure retained.</t>
+        </is>
+      </c>
+      <c r="E28" s="54" t="inlineStr">
+        <is>
+          <t>EmberClear's Lincoln Land project page describes a 1,190 MW combined-cycle development near Pawnee, Illinois. Its current team page identifies John H. Kinnamon in project development. A developer fact sheet publishes his direct business email and phone, but the document is historical.</t>
+        </is>
+      </c>
+      <c r="F28" s="54" t="inlineStr">
+        <is>
+          <t>Reconfirm Kinnamon's contact details, current sponsor, permit deadline, financing/offtake and EPC before pursuing a package. The input claim that an offtaker withdrew is not verified here; no committed project COD established.</t>
+        </is>
+      </c>
+      <c r="G28" s="55" t="inlineStr">
+        <is>
+          <t>https://emberclear.com/lincoln-land-2/ | https://www.thriveinspi.org/resources/a6e96b79-67aa-448a-8fd1-54b1f1430d3a/llec%20fact%20sheet.pdf?trackid=llec+fact+sheet.pdf | https://emberclear.com/about-us/ | https://www.illinoistimes.com/news/data-center-development-linked-to-power-plant-construction/</t>
+        </is>
+      </c>
+      <c r="H28" s="54" t="inlineStr">
+        <is>
+          <t>John H. Kinnamon — project development; historical fact-sheet details</t>
+        </is>
+      </c>
+      <c r="I28" s="54" t="inlineStr">
+        <is>
+          <t>jkinnamon@emberclear.com</t>
+        </is>
+      </c>
+      <c r="J28" s="54" t="inlineStr">
+        <is>
+          <t>+1 405-285-0220</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.thriveinspi.org/resources/a6e96b79-67aa-448a-8fd1-54b1f1430d3a/llec%20fact%20sheet.pdf?trackid=llec+fact+sheet.pdf | https://emberclear.com/about-us/</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HISTORICAL EMAIL + PHONE — reconfirm</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>Project Kilby (Chevron West Texas Power)</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>Pre-FID / early works; procurement contacts published</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="inlineStr">
+        <is>
+          <t>First power 2028; full capacity 2031 per project website. FID targeted by end-2026 in Chevron June release.</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>2,670 MW project capacity confirmed; do not equate first-power capacity with full buildout.</t>
+        </is>
+      </c>
+      <c r="E29" s="54" t="inlineStr">
+        <is>
+          <t>Chevron announced a twenty-year Microsoft power agreement for Project Kilby in Reeves County, Texas. The current project site describes Energy Forge One as a 50/50 Chevron-Joulent joint venture. Bechtel's May 2026 opportunity report lists Kilby job 26776, EPC scope, and named procurement/subcontract contacts.</t>
+        </is>
+      </c>
+      <c r="F29" s="54" t="inlineStr">
+        <is>
+          <t>Contact Birju Vasani for procurement and Mark Bingaman for subcontracts; confirm package scope, supplier qualification and full notice-to-proceed status. The public report supports Bechtel involvement but does not prove an unrestricted EPC NTP.</t>
+        </is>
+      </c>
+      <c r="G29" s="55" t="inlineStr">
+        <is>
+          <t>https://kilby.com/project/ | https://www.chevron.com/newsroom/2026/q2/chevron-signs-20-year-power-agreement-with-microsoft-for-west-texas-data-center | https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="H29" s="54" t="inlineStr">
+        <is>
+          <t>Mark Bingaman — Bechtel Kilby subcontract prequalification</t>
+        </is>
+      </c>
+      <c r="I29" s="54" t="inlineStr">
+        <is>
+          <t>mabingam@bechtel.com</t>
+        </is>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>+1 713-235-1662</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.bechtel.com/wp-content/uploads/2026/05/5.18.26-Project-Opportunity-Report.pdf</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Published project contact; procurement alternative in Named Contacts</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station Phase II</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>Development; existing steam-plant fuel conversion</t>
+        </is>
+      </c>
+      <c r="C30" s="54" t="inlineStr">
+        <is>
+          <t>Owner targets conversion completion Q4 2028/Q1 2029 and PJM interconnection in 2029; conditional milestones.</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Updated 2,700 MW input to owner's 2,550 MW firm output (three 850 MW units); historical gross ratings differ.</t>
+        </is>
+      </c>
+      <c r="E30" s="54" t="inlineStr">
+        <is>
+          <t>Shippingport Power Station is a planned conversion of the former Bruce Mansfield station. The owner describes gas conversion of three Foster Wheeler boilers and refurbishment of the existing GE steam turbines; Wood is owner's engineer. This scope is not replacement with new gas turbines.</t>
+        </is>
+      </c>
+      <c r="F30" s="54" t="inlineStr">
+        <is>
+          <t>Confirm whether this record represents the whole three-unit conversion or a specific phase; do not duplicate the full 2,550 MW across phases. Request retrofit electrical scope through Frontier and Wood. Do not apply greenfield cable quantities to reused equipment.</t>
+        </is>
+      </c>
+      <c r="G30" s="55" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/shippingport-industrial-park/ | https://frontier-companies.com/frontier-group-of-companies-welcomes-senator-dave-mccormick-to-shippingport-industrial-park/</t>
+        </is>
+      </c>
+      <c r="H30" s="54" t="inlineStr">
+        <is>
+          <t>Frontier general inquiries — shared business route</t>
+        </is>
+      </c>
+      <c r="I30" s="54" t="inlineStr">
+        <is>
+          <t>inquiries@fic-services.com</t>
+        </is>
+      </c>
+      <c r="J30" s="54" t="inlineStr">
+        <is>
+          <t>+1 716-447-7587</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://frontier-companies.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Published office route; request Shippingport electrical buyer</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="inlineStr">
+        <is>
+          <t>VPN 4420 Natural Gas Generation Component</t>
+        </is>
+      </c>
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>Proposed; present execution status unconfirmed</t>
+        </is>
+      </c>
+      <c r="C31" s="54" t="inlineStr">
+        <is>
+          <t>No current construction or COD verified. Latest posted compliance data describes reporting year 2024.</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>1,540 MW input retained as proposed scope; original multi-plant wording requires capacity reconciliation. Do not multiply by three without confirmation.</t>
+        </is>
+      </c>
+      <c r="E31" s="54" t="inlineStr">
+        <is>
+          <t>Texas Comptroller Chapter 313 agreement 1993 identifies VPN 4420 LLC and Maefield Development CEO Mark Siffin as the business contact. The latest posted 2024 compliance report, uploaded January 2026, repeats his phone/email and reports zero qualified investment through 2024. It does not establish investment or construction status in October 2026.</t>
+        </is>
+      </c>
+      <c r="F31" s="54" t="inlineStr">
+        <is>
+          <t>Contact Mark Siffin to confirm whether generation is advancing, aggregate capacity, land control, air permits, offtake and EPC. No supported current award schedule; retain as an unqualified development lead rather than a booked project.</t>
+        </is>
+      </c>
+      <c r="G31" s="55" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/dat/ch313/1993/01993-772-2024-0812-MCA-195901-PBT.pdf | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-app.pdf | https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993</t>
+        </is>
+      </c>
+      <c r="H31" s="54" t="inlineStr">
+        <is>
+          <t>Mark Siffin — CEO / VPN 4420 business contact</t>
+        </is>
+      </c>
+      <c r="I31" s="54" t="inlineStr">
+        <is>
+          <t>siffin@maefield.com</t>
+        </is>
+      </c>
+      <c r="J31" s="54" t="inlineStr">
+        <is>
+          <t>+1 347-703-0093</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://assets.comptroller.texas.gov/dat/ch313/1993/01993-772-2024-0812-MCA-195901-PBT.pdf | https://assets.comptroller.texas.gov/ch313/1993/1993-pecos-vpn-app.pdf | https://comptroller.texas.gov/economy/development/prop-tax/ch313/agreement-docs-details.php?id=1993</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2024 compliance report posted 2026; current project status to confirm</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -55518,6 +58698,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
+++ b/Projects_and_Leads_Gas_Leads_2026-10-29.xlsx
@@ -2470,7 +2470,7 @@
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D10" s="38" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C11" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" s="38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D12" s="38" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C13" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D13" s="38" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D14" s="38" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D16" s="38" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D18" s="38" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D21" s="38" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D22" s="38" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D24" s="38" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D26" s="38" t="inlineStr">
